--- a/validation-tests/validation-test-report.xlsx
+++ b/validation-tests/validation-test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="831">
   <si>
     <t>Metric</t>
   </si>
@@ -71,7 +71,7 @@
     <t>EXECUTION TIMESTAMP</t>
   </si>
   <si>
-    <t>6/8/2026, 3:25:21 pm</t>
+    <t>6/8/2026, 7:39:49 pm</t>
   </si>
   <si>
     <t>CI/CD Pipeline Run</t>
@@ -176,7 +176,7 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>2026-08-06T09:55:21.185Z</t>
+    <t>2026-08-06T14:09:49.081Z</t>
   </si>
   <si>
     <t>VAL-SEC-002</t>
@@ -188,7 +188,7 @@
     <t>email='user.name+tag@gmail.com'</t>
   </si>
   <si>
-    <t>2026-08-06T09:55:21.187Z</t>
+    <t>2026-08-06T14:09:49.084Z</t>
   </si>
   <si>
     <t>VAL-SEC-003</t>
@@ -350,6 +350,9 @@
     <t>Email Format Syntax &amp; RFC 5322 Rule #25</t>
   </si>
   <si>
+    <t>2026-08-06T14:09:49.085Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-026</t>
   </si>
   <si>
@@ -431,9 +434,6 @@
     <t>Evaluated: valid=true, score=4/4, feedback='Strong'</t>
   </si>
   <si>
-    <t>2026-08-06T09:55:21.188Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-037</t>
   </si>
   <si>
@@ -458,6 +458,9 @@
     <t>Evaluated: valid=false, score=1/4, feedback='Needs mixed case, numbers, or symbols'</t>
   </si>
   <si>
+    <t>2026-08-06T14:09:49.086Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-039</t>
   </si>
   <si>
@@ -611,9 +614,6 @@
     <t>password_sample_20 (length=4)</t>
   </si>
   <si>
-    <t>2026-08-06T09:55:21.189Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-056</t>
   </si>
   <si>
@@ -677,9 +677,6 @@
     <t>password_sample_27 (length=8)</t>
   </si>
   <si>
-    <t>2026-08-06T09:55:21.190Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-063</t>
   </si>
   <si>
@@ -743,6 +740,9 @@
     <t>password_sample_34 (length=18)</t>
   </si>
   <si>
+    <t>2026-08-06T14:09:49.087Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-070</t>
   </si>
   <si>
@@ -773,7 +773,7 @@
     <t>Sanitizer: blocked_attack=true, sanitized_output='Goa OR 1=1'</t>
   </si>
   <si>
-    <t>2026-08-06T09:55:21.192Z</t>
+    <t>2026-08-06T14:09:49.088Z</t>
   </si>
   <si>
     <t>VAL-SEC-072</t>
@@ -812,6 +812,9 @@
     <t>Sanitizer: blocked_attack=false, sanitized_output='Maldives'</t>
   </si>
   <si>
+    <t>2026-08-06T14:09:49.089Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-075</t>
   </si>
   <si>
@@ -824,9 +827,6 @@
     <t>Sanitizer: blocked_attack=false, sanitized_output='New York'</t>
   </si>
   <si>
-    <t>2026-08-06T09:55:21.193Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-076</t>
   </si>
   <si>
@@ -1052,9 +1052,6 @@
     <t>Encoded: &amp;lt;img src=x onerror=alert(1)&amp;gt;</t>
   </si>
   <si>
-    <t>2026-08-06T09:55:21.194Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-108</t>
   </si>
   <si>
@@ -1067,6 +1064,9 @@
     <t>Encoded: &amp;lt;a href=&amp;#x27;javascript:void(0)&amp;#x27;&amp;gt;Click&amp;lt;&amp;#x2F;a&amp;gt;</t>
   </si>
   <si>
+    <t>2026-08-06T14:09:49.090Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-109</t>
   </si>
   <si>
@@ -1298,9 +1298,6 @@
     <t>Luhn verification: valid_card=false</t>
   </si>
   <si>
-    <t>2026-08-06T09:55:21.195Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-142</t>
   </si>
   <si>
@@ -1481,6 +1478,9 @@
     <t>Payment Card Luhn Mod-10 Checksum #30</t>
   </si>
   <si>
+    <t>2026-08-06T14:09:49.091Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-171</t>
   </si>
   <si>
@@ -1595,9 +1595,6 @@
     <t>checkIn='2026-09-09', checkOut='2026-09-12'</t>
   </si>
   <si>
-    <t>2026-08-06T09:55:21.196Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-184</t>
   </si>
   <si>
@@ -2042,6 +2039,9 @@
     <t>lat=28.2993, lon=87.1240</t>
   </si>
   <si>
+    <t>2026-08-06T14:09:49.092Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-237</t>
   </si>
   <si>
@@ -2099,9 +2099,6 @@
     <t>File inspection: allowed=true</t>
   </si>
   <si>
-    <t>2026-08-06T09:55:21.197Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-242</t>
   </si>
   <si>
@@ -2328,9 +2325,6 @@
   </si>
   <si>
     <t>JSON Schema validated: 0 validation errors, strict_types=passed</t>
-  </si>
-  <si>
-    <t>2026-08-06T09:55:21.198Z</t>
   </si>
   <si>
     <t>VAL-SEC-272</t>
@@ -3984,12 +3978,12 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B27" t="s">
         <v>47</v>
@@ -3998,7 +3992,7 @@
         <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E27" t="s">
         <v>69</v>
@@ -4016,12 +4010,12 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" t="s">
         <v>47</v>
@@ -4030,7 +4024,7 @@
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E28" t="s">
         <v>72</v>
@@ -4048,12 +4042,12 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
@@ -4062,7 +4056,7 @@
         <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s">
         <v>75</v>
@@ -4080,12 +4074,12 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
@@ -4094,7 +4088,7 @@
         <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
         <v>50</v>
@@ -4112,12 +4106,12 @@
         <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
@@ -4126,7 +4120,7 @@
         <v>48</v>
       </c>
       <c r="D31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E31" t="s">
         <v>57</v>
@@ -4144,12 +4138,12 @@
         <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" t="s">
         <v>47</v>
@@ -4158,7 +4152,7 @@
         <v>48</v>
       </c>
       <c r="D32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s">
         <v>61</v>
@@ -4176,12 +4170,12 @@
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" t="s">
         <v>47</v>
@@ -4190,7 +4184,7 @@
         <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
         <v>64</v>
@@ -4208,12 +4202,12 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B34" t="s">
         <v>47</v>
@@ -4222,7 +4216,7 @@
         <v>48</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E34" t="s">
         <v>69</v>
@@ -4240,12 +4234,12 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B35" t="s">
         <v>47</v>
@@ -4254,7 +4248,7 @@
         <v>48</v>
       </c>
       <c r="D35" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E35" t="s">
         <v>72</v>
@@ -4272,12 +4266,12 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B36" t="s">
         <v>47</v>
@@ -4286,7 +4280,7 @@
         <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E36" t="s">
         <v>75</v>
@@ -4304,30 +4298,30 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>53</v>
@@ -4336,7 +4330,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -4344,10 +4338,10 @@
         <v>140</v>
       </c>
       <c r="B38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D38" t="s">
         <v>141</v>
@@ -4356,7 +4350,7 @@
         <v>142</v>
       </c>
       <c r="F38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G38" t="s">
         <v>143</v>
@@ -4368,7 +4362,7 @@
         <v>1</v>
       </c>
       <c r="J38" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -4376,10 +4370,10 @@
         <v>144</v>
       </c>
       <c r="B39" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D39" t="s">
         <v>145</v>
@@ -4388,7 +4382,7 @@
         <v>146</v>
       </c>
       <c r="F39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G39" t="s">
         <v>147</v>
@@ -4400,59 +4394,59 @@
         <v>1</v>
       </c>
       <c r="J39" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>149</v>
+      </c>
+      <c r="B40" t="s">
+        <v>134</v>
+      </c>
+      <c r="C40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D40" t="s">
+        <v>150</v>
+      </c>
+      <c r="E40" t="s">
+        <v>151</v>
+      </c>
+      <c r="F40" t="s">
+        <v>138</v>
+      </c>
+      <c r="G40" t="s">
+        <v>139</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40" t="s">
         <v>148</v>
-      </c>
-      <c r="B40" t="s">
-        <v>133</v>
-      </c>
-      <c r="C40" t="s">
-        <v>134</v>
-      </c>
-      <c r="D40" t="s">
-        <v>149</v>
-      </c>
-      <c r="E40" t="s">
-        <v>150</v>
-      </c>
-      <c r="F40" t="s">
-        <v>137</v>
-      </c>
-      <c r="G40" t="s">
-        <v>138</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I40">
-        <v>1</v>
-      </c>
-      <c r="J40" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D41" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E41" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G41" t="s">
         <v>143</v>
@@ -4464,30 +4458,30 @@
         <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E42" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>53</v>
@@ -4496,30 +4490,30 @@
         <v>1</v>
       </c>
       <c r="J42" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C43" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G43" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>53</v>
@@ -4528,27 +4522,27 @@
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C44" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D44" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E44" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F44" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G44" t="s">
         <v>143</v>
@@ -4560,27 +4554,27 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D45" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E45" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G45" t="s">
         <v>147</v>
@@ -4592,30 +4586,30 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C46" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D46" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E46" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G46" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>53</v>
@@ -4624,27 +4618,27 @@
         <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D47" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E47" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G47" t="s">
         <v>143</v>
@@ -4656,30 +4650,30 @@
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B48" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C48" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D48" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E48" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F48" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G48" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>53</v>
@@ -4688,30 +4682,30 @@
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B49" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C49" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D49" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E49" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F49" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G49" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>53</v>
@@ -4720,27 +4714,27 @@
         <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B50" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C50" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D50" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E50" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G50" t="s">
         <v>143</v>
@@ -4752,27 +4746,27 @@
         <v>1</v>
       </c>
       <c r="J50" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C51" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D51" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E51" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F51" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G51" t="s">
         <v>147</v>
@@ -4784,30 +4778,30 @@
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B52" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C52" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E52" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F52" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G52" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>53</v>
@@ -4816,27 +4810,27 @@
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B53" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C53" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D53" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E53" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F53" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G53" t="s">
         <v>143</v>
@@ -4848,30 +4842,30 @@
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B54" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C54" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E54" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F54" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G54" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>53</v>
@@ -4880,30 +4874,30 @@
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C55" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D55" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E55" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F55" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G55" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>53</v>
@@ -4912,27 +4906,27 @@
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B56" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C56" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E56" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F56" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G56" t="s">
         <v>143</v>
@@ -4944,7 +4938,7 @@
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -4952,10 +4946,10 @@
         <v>200</v>
       </c>
       <c r="B57" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C57" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D57" t="s">
         <v>201</v>
@@ -4964,7 +4958,7 @@
         <v>202</v>
       </c>
       <c r="F57" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G57" t="s">
         <v>147</v>
@@ -4976,7 +4970,7 @@
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -4984,10 +4978,10 @@
         <v>203</v>
       </c>
       <c r="B58" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C58" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D58" t="s">
         <v>204</v>
@@ -4996,10 +4990,10 @@
         <v>205</v>
       </c>
       <c r="F58" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G58" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>53</v>
@@ -5008,7 +5002,7 @@
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -5016,10 +5010,10 @@
         <v>206</v>
       </c>
       <c r="B59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C59" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D59" t="s">
         <v>207</v>
@@ -5028,7 +5022,7 @@
         <v>208</v>
       </c>
       <c r="F59" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G59" t="s">
         <v>143</v>
@@ -5040,7 +5034,7 @@
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -5048,10 +5042,10 @@
         <v>209</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C60" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D60" t="s">
         <v>210</v>
@@ -5060,10 +5054,10 @@
         <v>211</v>
       </c>
       <c r="F60" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G60" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>53</v>
@@ -5072,7 +5066,7 @@
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -5080,10 +5074,10 @@
         <v>212</v>
       </c>
       <c r="B61" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C61" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D61" t="s">
         <v>213</v>
@@ -5092,10 +5086,10 @@
         <v>214</v>
       </c>
       <c r="F61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G61" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>53</v>
@@ -5104,7 +5098,7 @@
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -5112,10 +5106,10 @@
         <v>215</v>
       </c>
       <c r="B62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C62" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D62" t="s">
         <v>216</v>
@@ -5124,7 +5118,7 @@
         <v>217</v>
       </c>
       <c r="F62" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G62" t="s">
         <v>143</v>
@@ -5136,7 +5130,7 @@
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -5144,10 +5138,10 @@
         <v>218</v>
       </c>
       <c r="B63" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D63" t="s">
         <v>219</v>
@@ -5156,7 +5150,7 @@
         <v>220</v>
       </c>
       <c r="F63" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G63" t="s">
         <v>147</v>
@@ -5168,30 +5162,30 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>221</v>
+        <v>148</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>221</v>
+      </c>
+      <c r="B64" t="s">
+        <v>134</v>
+      </c>
+      <c r="C64" t="s">
+        <v>135</v>
+      </c>
+      <c r="D64" t="s">
         <v>222</v>
       </c>
-      <c r="B64" t="s">
-        <v>133</v>
-      </c>
-      <c r="C64" t="s">
-        <v>134</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>223</v>
       </c>
-      <c r="E64" t="s">
-        <v>224</v>
-      </c>
       <c r="F64" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G64" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>53</v>
@@ -5200,27 +5194,27 @@
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>221</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>224</v>
+      </c>
+      <c r="B65" t="s">
+        <v>134</v>
+      </c>
+      <c r="C65" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" t="s">
         <v>225</v>
       </c>
-      <c r="B65" t="s">
-        <v>133</v>
-      </c>
-      <c r="C65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>226</v>
       </c>
-      <c r="E65" t="s">
-        <v>227</v>
-      </c>
       <c r="F65" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G65" t="s">
         <v>143</v>
@@ -5232,30 +5226,30 @@
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>221</v>
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>227</v>
+      </c>
+      <c r="B66" t="s">
+        <v>134</v>
+      </c>
+      <c r="C66" t="s">
+        <v>135</v>
+      </c>
+      <c r="D66" t="s">
         <v>228</v>
       </c>
-      <c r="B66" t="s">
-        <v>133</v>
-      </c>
-      <c r="C66" t="s">
-        <v>134</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>229</v>
       </c>
-      <c r="E66" t="s">
-        <v>230</v>
-      </c>
       <c r="F66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G66" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>53</v>
@@ -5264,30 +5258,30 @@
         <v>1</v>
       </c>
       <c r="J66" t="s">
-        <v>221</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>230</v>
+      </c>
+      <c r="B67" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" t="s">
+        <v>135</v>
+      </c>
+      <c r="D67" t="s">
         <v>231</v>
       </c>
-      <c r="B67" t="s">
-        <v>133</v>
-      </c>
-      <c r="C67" t="s">
-        <v>134</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>232</v>
       </c>
-      <c r="E67" t="s">
-        <v>233</v>
-      </c>
       <c r="F67" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G67" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>53</v>
@@ -5296,27 +5290,27 @@
         <v>1</v>
       </c>
       <c r="J67" t="s">
-        <v>221</v>
+        <v>148</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>233</v>
+      </c>
+      <c r="B68" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" t="s">
+        <v>135</v>
+      </c>
+      <c r="D68" t="s">
         <v>234</v>
       </c>
-      <c r="B68" t="s">
-        <v>133</v>
-      </c>
-      <c r="C68" t="s">
-        <v>134</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>235</v>
       </c>
-      <c r="E68" t="s">
-        <v>236</v>
-      </c>
       <c r="F68" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G68" t="s">
         <v>143</v>
@@ -5328,27 +5322,27 @@
         <v>1</v>
       </c>
       <c r="J68" t="s">
-        <v>221</v>
+        <v>148</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>236</v>
+      </c>
+      <c r="B69" t="s">
+        <v>134</v>
+      </c>
+      <c r="C69" t="s">
+        <v>135</v>
+      </c>
+      <c r="D69" t="s">
         <v>237</v>
       </c>
-      <c r="B69" t="s">
-        <v>133</v>
-      </c>
-      <c r="C69" t="s">
-        <v>134</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>238</v>
       </c>
-      <c r="E69" t="s">
-        <v>239</v>
-      </c>
       <c r="F69" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G69" t="s">
         <v>147</v>
@@ -5360,39 +5354,39 @@
         <v>1</v>
       </c>
       <c r="J69" t="s">
-        <v>221</v>
+        <v>148</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>239</v>
+      </c>
+      <c r="B70" t="s">
+        <v>134</v>
+      </c>
+      <c r="C70" t="s">
+        <v>135</v>
+      </c>
+      <c r="D70" t="s">
         <v>240</v>
       </c>
-      <c r="B70" t="s">
-        <v>133</v>
-      </c>
-      <c r="C70" t="s">
-        <v>134</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>241</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
+        <v>138</v>
+      </c>
+      <c r="G70" t="s">
+        <v>139</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+      <c r="J70" t="s">
         <v>242</v>
-      </c>
-      <c r="F70" t="s">
-        <v>137</v>
-      </c>
-      <c r="G70" t="s">
-        <v>138</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I70">
-        <v>1</v>
-      </c>
-      <c r="J70" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -5400,10 +5394,10 @@
         <v>243</v>
       </c>
       <c r="B71" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C71" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D71" t="s">
         <v>244</v>
@@ -5412,7 +5406,7 @@
         <v>245</v>
       </c>
       <c r="F71" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G71" t="s">
         <v>143</v>
@@ -5424,7 +5418,7 @@
         <v>1</v>
       </c>
       <c r="J71" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -5453,7 +5447,7 @@
         <v>53</v>
       </c>
       <c r="I72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J72" t="s">
         <v>253</v>
@@ -5552,12 +5546,12 @@
         <v>1</v>
       </c>
       <c r="J75" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B76" t="s">
         <v>247</v>
@@ -5566,16 +5560,16 @@
         <v>248</v>
       </c>
       <c r="D76" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F76" t="s">
         <v>251</v>
       </c>
       <c r="G76" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>53</v>
@@ -5584,7 +5578,7 @@
         <v>1</v>
       </c>
       <c r="J76" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -5616,7 +5610,7 @@
         <v>1</v>
       </c>
       <c r="J77" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -5648,7 +5642,7 @@
         <v>1</v>
       </c>
       <c r="J78" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -5680,7 +5674,7 @@
         <v>1</v>
       </c>
       <c r="J79" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -5712,7 +5706,7 @@
         <v>1</v>
       </c>
       <c r="J80" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -5744,7 +5738,7 @@
         <v>1</v>
       </c>
       <c r="J81" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -5776,7 +5770,7 @@
         <v>1</v>
       </c>
       <c r="J82" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -5793,13 +5787,13 @@
         <v>288</v>
       </c>
       <c r="E83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F83" t="s">
         <v>251</v>
       </c>
       <c r="G83" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>53</v>
@@ -5808,7 +5802,7 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -5840,7 +5834,7 @@
         <v>1</v>
       </c>
       <c r="J84" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -5872,7 +5866,7 @@
         <v>1</v>
       </c>
       <c r="J85" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -5904,7 +5898,7 @@
         <v>1</v>
       </c>
       <c r="J86" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -5936,7 +5930,7 @@
         <v>1</v>
       </c>
       <c r="J87" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -5968,7 +5962,7 @@
         <v>1</v>
       </c>
       <c r="J88" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -6000,7 +5994,7 @@
         <v>1</v>
       </c>
       <c r="J89" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -6017,13 +6011,13 @@
         <v>302</v>
       </c>
       <c r="E90" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F90" t="s">
         <v>251</v>
       </c>
       <c r="G90" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>53</v>
@@ -6032,7 +6026,7 @@
         <v>1</v>
       </c>
       <c r="J90" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -6064,7 +6058,7 @@
         <v>1</v>
       </c>
       <c r="J91" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -6096,7 +6090,7 @@
         <v>1</v>
       </c>
       <c r="J92" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -6128,7 +6122,7 @@
         <v>1</v>
       </c>
       <c r="J93" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -6160,7 +6154,7 @@
         <v>1</v>
       </c>
       <c r="J94" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -6192,7 +6186,7 @@
         <v>1</v>
       </c>
       <c r="J95" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -6224,7 +6218,7 @@
         <v>1</v>
       </c>
       <c r="J96" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -6241,13 +6235,13 @@
         <v>316</v>
       </c>
       <c r="E97" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F97" t="s">
         <v>251</v>
       </c>
       <c r="G97" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>53</v>
@@ -6256,7 +6250,7 @@
         <v>1</v>
       </c>
       <c r="J97" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -6288,7 +6282,7 @@
         <v>1</v>
       </c>
       <c r="J98" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -6320,7 +6314,7 @@
         <v>1</v>
       </c>
       <c r="J99" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -6352,7 +6346,7 @@
         <v>1</v>
       </c>
       <c r="J100" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -6384,7 +6378,7 @@
         <v>1</v>
       </c>
       <c r="J101" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -6416,7 +6410,7 @@
         <v>1</v>
       </c>
       <c r="J102" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -6448,7 +6442,7 @@
         <v>1</v>
       </c>
       <c r="J103" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -6465,13 +6459,13 @@
         <v>330</v>
       </c>
       <c r="E104" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F104" t="s">
         <v>251</v>
       </c>
       <c r="G104" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>53</v>
@@ -6480,7 +6474,7 @@
         <v>1</v>
       </c>
       <c r="J104" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -6512,7 +6506,7 @@
         <v>1</v>
       </c>
       <c r="J105" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -6544,7 +6538,7 @@
         <v>1</v>
       </c>
       <c r="J106" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -6576,7 +6570,7 @@
         <v>1</v>
       </c>
       <c r="J107" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -6608,12 +6602,12 @@
         <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>346</v>
+        <v>266</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B109" t="s">
         <v>336</v>
@@ -6622,25 +6616,25 @@
         <v>337</v>
       </c>
       <c r="D109" t="s">
+        <v>347</v>
+      </c>
+      <c r="E109" t="s">
         <v>348</v>
-      </c>
-      <c r="E109" t="s">
-        <v>349</v>
       </c>
       <c r="F109" t="s">
         <v>340</v>
       </c>
       <c r="G109" t="s">
+        <v>349</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+      <c r="J109" t="s">
         <v>350</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I109">
-        <v>1</v>
-      </c>
-      <c r="J109" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -6672,7 +6666,7 @@
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -6704,7 +6698,7 @@
         <v>1</v>
       </c>
       <c r="J111" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -6736,7 +6730,7 @@
         <v>1</v>
       </c>
       <c r="J112" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -6768,7 +6762,7 @@
         <v>1</v>
       </c>
       <c r="J113" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -6800,7 +6794,7 @@
         <v>1</v>
       </c>
       <c r="J114" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -6817,22 +6811,22 @@
         <v>368</v>
       </c>
       <c r="E115" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F115" t="s">
         <v>340</v>
       </c>
       <c r="G115" t="s">
+        <v>349</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115" t="s">
         <v>350</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I115">
-        <v>1</v>
-      </c>
-      <c r="J115" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -6864,7 +6858,7 @@
         <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -6896,7 +6890,7 @@
         <v>1</v>
       </c>
       <c r="J117" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -6928,7 +6922,7 @@
         <v>1</v>
       </c>
       <c r="J118" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -6960,7 +6954,7 @@
         <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -6992,7 +6986,7 @@
         <v>1</v>
       </c>
       <c r="J120" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -7009,22 +7003,22 @@
         <v>380</v>
       </c>
       <c r="E121" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F121" t="s">
         <v>340</v>
       </c>
       <c r="G121" t="s">
+        <v>349</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121" t="s">
         <v>350</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I121">
-        <v>1</v>
-      </c>
-      <c r="J121" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -7056,7 +7050,7 @@
         <v>1</v>
       </c>
       <c r="J122" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -7088,7 +7082,7 @@
         <v>1</v>
       </c>
       <c r="J123" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -7120,7 +7114,7 @@
         <v>1</v>
       </c>
       <c r="J124" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -7152,7 +7146,7 @@
         <v>1</v>
       </c>
       <c r="J125" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -7184,7 +7178,7 @@
         <v>1</v>
       </c>
       <c r="J126" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -7201,22 +7195,22 @@
         <v>392</v>
       </c>
       <c r="E127" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F127" t="s">
         <v>340</v>
       </c>
       <c r="G127" t="s">
+        <v>349</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I127">
+        <v>1</v>
+      </c>
+      <c r="J127" t="s">
         <v>350</v>
-      </c>
-      <c r="H127" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I127">
-        <v>1</v>
-      </c>
-      <c r="J127" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -7248,7 +7242,7 @@
         <v>1</v>
       </c>
       <c r="J128" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -7280,7 +7274,7 @@
         <v>1</v>
       </c>
       <c r="J129" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -7312,7 +7306,7 @@
         <v>1</v>
       </c>
       <c r="J130" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -7344,7 +7338,7 @@
         <v>1</v>
       </c>
       <c r="J131" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -7376,7 +7370,7 @@
         <v>1</v>
       </c>
       <c r="J132" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -7393,22 +7387,22 @@
         <v>404</v>
       </c>
       <c r="E133" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F133" t="s">
         <v>340</v>
       </c>
       <c r="G133" t="s">
+        <v>349</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133" t="s">
         <v>350</v>
-      </c>
-      <c r="H133" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I133">
-        <v>1</v>
-      </c>
-      <c r="J133" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -7440,7 +7434,7 @@
         <v>1</v>
       </c>
       <c r="J134" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -7472,7 +7466,7 @@
         <v>1</v>
       </c>
       <c r="J135" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -7504,7 +7498,7 @@
         <v>1</v>
       </c>
       <c r="J136" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -7536,7 +7530,7 @@
         <v>1</v>
       </c>
       <c r="J137" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -7568,7 +7562,7 @@
         <v>1</v>
       </c>
       <c r="J138" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -7585,22 +7579,22 @@
         <v>416</v>
       </c>
       <c r="E139" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F139" t="s">
         <v>340</v>
       </c>
       <c r="G139" t="s">
+        <v>349</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="J139" t="s">
         <v>350</v>
-      </c>
-      <c r="H139" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I139">
-        <v>1</v>
-      </c>
-      <c r="J139" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -7632,7 +7626,7 @@
         <v>1</v>
       </c>
       <c r="J140" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -7664,7 +7658,7 @@
         <v>1</v>
       </c>
       <c r="J141" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -7696,12 +7690,12 @@
         <v>1</v>
       </c>
       <c r="J142" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B143" t="s">
         <v>422</v>
@@ -7710,16 +7704,16 @@
         <v>423</v>
       </c>
       <c r="D143" t="s">
+        <v>429</v>
+      </c>
+      <c r="E143" t="s">
         <v>430</v>
-      </c>
-      <c r="E143" t="s">
-        <v>431</v>
       </c>
       <c r="F143" t="s">
         <v>426</v>
       </c>
       <c r="G143" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H143" s="3" t="s">
         <v>53</v>
@@ -7728,12 +7722,12 @@
         <v>1</v>
       </c>
       <c r="J143" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B144" t="s">
         <v>422</v>
@@ -7742,7 +7736,7 @@
         <v>423</v>
       </c>
       <c r="D144" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E144" t="s">
         <v>425</v>
@@ -7760,12 +7754,12 @@
         <v>1</v>
       </c>
       <c r="J144" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B145" t="s">
         <v>422</v>
@@ -7774,16 +7768,16 @@
         <v>423</v>
       </c>
       <c r="D145" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E145" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F145" t="s">
         <v>426</v>
       </c>
       <c r="G145" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H145" s="3" t="s">
         <v>53</v>
@@ -7792,12 +7786,12 @@
         <v>1</v>
       </c>
       <c r="J145" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B146" t="s">
         <v>422</v>
@@ -7806,7 +7800,7 @@
         <v>423</v>
       </c>
       <c r="D146" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E146" t="s">
         <v>425</v>
@@ -7824,12 +7818,12 @@
         <v>1</v>
       </c>
       <c r="J146" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B147" t="s">
         <v>422</v>
@@ -7838,16 +7832,16 @@
         <v>423</v>
       </c>
       <c r="D147" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E147" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F147" t="s">
         <v>426</v>
       </c>
       <c r="G147" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H147" s="3" t="s">
         <v>53</v>
@@ -7856,12 +7850,12 @@
         <v>1</v>
       </c>
       <c r="J147" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B148" t="s">
         <v>422</v>
@@ -7870,7 +7864,7 @@
         <v>423</v>
       </c>
       <c r="D148" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E148" t="s">
         <v>425</v>
@@ -7888,12 +7882,12 @@
         <v>1</v>
       </c>
       <c r="J148" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B149" t="s">
         <v>422</v>
@@ -7902,16 +7896,16 @@
         <v>423</v>
       </c>
       <c r="D149" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E149" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F149" t="s">
         <v>426</v>
       </c>
       <c r="G149" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H149" s="3" t="s">
         <v>53</v>
@@ -7920,12 +7914,12 @@
         <v>1</v>
       </c>
       <c r="J149" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B150" t="s">
         <v>422</v>
@@ -7934,7 +7928,7 @@
         <v>423</v>
       </c>
       <c r="D150" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E150" t="s">
         <v>425</v>
@@ -7952,12 +7946,12 @@
         <v>1</v>
       </c>
       <c r="J150" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B151" t="s">
         <v>422</v>
@@ -7966,16 +7960,16 @@
         <v>423</v>
       </c>
       <c r="D151" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E151" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F151" t="s">
         <v>426</v>
       </c>
       <c r="G151" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H151" s="3" t="s">
         <v>53</v>
@@ -7984,12 +7978,12 @@
         <v>1</v>
       </c>
       <c r="J151" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B152" t="s">
         <v>422</v>
@@ -7998,7 +7992,7 @@
         <v>423</v>
       </c>
       <c r="D152" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E152" t="s">
         <v>425</v>
@@ -8016,12 +8010,12 @@
         <v>1</v>
       </c>
       <c r="J152" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B153" t="s">
         <v>422</v>
@@ -8030,16 +8024,16 @@
         <v>423</v>
       </c>
       <c r="D153" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E153" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F153" t="s">
         <v>426</v>
       </c>
       <c r="G153" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H153" s="3" t="s">
         <v>53</v>
@@ -8048,12 +8042,12 @@
         <v>1</v>
       </c>
       <c r="J153" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B154" t="s">
         <v>422</v>
@@ -8062,7 +8056,7 @@
         <v>423</v>
       </c>
       <c r="D154" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E154" t="s">
         <v>425</v>
@@ -8080,12 +8074,12 @@
         <v>1</v>
       </c>
       <c r="J154" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B155" t="s">
         <v>422</v>
@@ -8094,16 +8088,16 @@
         <v>423</v>
       </c>
       <c r="D155" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E155" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F155" t="s">
         <v>426</v>
       </c>
       <c r="G155" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H155" s="3" t="s">
         <v>53</v>
@@ -8112,12 +8106,12 @@
         <v>1</v>
       </c>
       <c r="J155" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B156" t="s">
         <v>422</v>
@@ -8126,7 +8120,7 @@
         <v>423</v>
       </c>
       <c r="D156" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E156" t="s">
         <v>425</v>
@@ -8144,12 +8138,12 @@
         <v>1</v>
       </c>
       <c r="J156" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B157" t="s">
         <v>422</v>
@@ -8158,16 +8152,16 @@
         <v>423</v>
       </c>
       <c r="D157" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E157" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F157" t="s">
         <v>426</v>
       </c>
       <c r="G157" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H157" s="3" t="s">
         <v>53</v>
@@ -8176,12 +8170,12 @@
         <v>1</v>
       </c>
       <c r="J157" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B158" t="s">
         <v>422</v>
@@ -8190,7 +8184,7 @@
         <v>423</v>
       </c>
       <c r="D158" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E158" t="s">
         <v>425</v>
@@ -8208,12 +8202,12 @@
         <v>1</v>
       </c>
       <c r="J158" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B159" t="s">
         <v>422</v>
@@ -8222,16 +8216,16 @@
         <v>423</v>
       </c>
       <c r="D159" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E159" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F159" t="s">
         <v>426</v>
       </c>
       <c r="G159" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H159" s="3" t="s">
         <v>53</v>
@@ -8240,12 +8234,12 @@
         <v>1</v>
       </c>
       <c r="J159" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B160" t="s">
         <v>422</v>
@@ -8254,7 +8248,7 @@
         <v>423</v>
       </c>
       <c r="D160" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E160" t="s">
         <v>425</v>
@@ -8272,12 +8266,12 @@
         <v>1</v>
       </c>
       <c r="J160" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B161" t="s">
         <v>422</v>
@@ -8286,16 +8280,16 @@
         <v>423</v>
       </c>
       <c r="D161" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E161" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F161" t="s">
         <v>426</v>
       </c>
       <c r="G161" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H161" s="3" t="s">
         <v>53</v>
@@ -8304,12 +8298,12 @@
         <v>1</v>
       </c>
       <c r="J161" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B162" t="s">
         <v>422</v>
@@ -8318,7 +8312,7 @@
         <v>423</v>
       </c>
       <c r="D162" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E162" t="s">
         <v>425</v>
@@ -8336,12 +8330,12 @@
         <v>1</v>
       </c>
       <c r="J162" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B163" t="s">
         <v>422</v>
@@ -8350,16 +8344,16 @@
         <v>423</v>
       </c>
       <c r="D163" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E163" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F163" t="s">
         <v>426</v>
       </c>
       <c r="G163" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H163" s="3" t="s">
         <v>53</v>
@@ -8368,12 +8362,12 @@
         <v>1</v>
       </c>
       <c r="J163" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B164" t="s">
         <v>422</v>
@@ -8382,7 +8376,7 @@
         <v>423</v>
       </c>
       <c r="D164" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E164" t="s">
         <v>425</v>
@@ -8400,12 +8394,12 @@
         <v>1</v>
       </c>
       <c r="J164" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B165" t="s">
         <v>422</v>
@@ -8414,16 +8408,16 @@
         <v>423</v>
       </c>
       <c r="D165" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E165" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F165" t="s">
         <v>426</v>
       </c>
       <c r="G165" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H165" s="3" t="s">
         <v>53</v>
@@ -8432,12 +8426,12 @@
         <v>1</v>
       </c>
       <c r="J165" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B166" t="s">
         <v>422</v>
@@ -8446,7 +8440,7 @@
         <v>423</v>
       </c>
       <c r="D166" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E166" t="s">
         <v>425</v>
@@ -8464,12 +8458,12 @@
         <v>1</v>
       </c>
       <c r="J166" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B167" t="s">
         <v>422</v>
@@ -8478,16 +8472,16 @@
         <v>423</v>
       </c>
       <c r="D167" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E167" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F167" t="s">
         <v>426</v>
       </c>
       <c r="G167" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H167" s="3" t="s">
         <v>53</v>
@@ -8496,12 +8490,12 @@
         <v>1</v>
       </c>
       <c r="J167" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B168" t="s">
         <v>422</v>
@@ -8510,7 +8504,7 @@
         <v>423</v>
       </c>
       <c r="D168" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E168" t="s">
         <v>425</v>
@@ -8528,12 +8522,12 @@
         <v>1</v>
       </c>
       <c r="J168" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B169" t="s">
         <v>422</v>
@@ -8542,16 +8536,16 @@
         <v>423</v>
       </c>
       <c r="D169" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E169" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F169" t="s">
         <v>426</v>
       </c>
       <c r="G169" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H169" s="3" t="s">
         <v>53</v>
@@ -8560,12 +8554,12 @@
         <v>1</v>
       </c>
       <c r="J169" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B170" t="s">
         <v>422</v>
@@ -8574,7 +8568,7 @@
         <v>423</v>
       </c>
       <c r="D170" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E170" t="s">
         <v>425</v>
@@ -8592,12 +8586,12 @@
         <v>1</v>
       </c>
       <c r="J170" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B171" t="s">
         <v>422</v>
@@ -8606,16 +8600,16 @@
         <v>423</v>
       </c>
       <c r="D171" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E171" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F171" t="s">
         <v>426</v>
       </c>
       <c r="G171" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H171" s="3" t="s">
         <v>53</v>
@@ -8624,7 +8618,7 @@
         <v>1</v>
       </c>
       <c r="J171" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -8656,7 +8650,7 @@
         <v>1</v>
       </c>
       <c r="J172" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
@@ -8673,13 +8667,13 @@
         <v>492</v>
       </c>
       <c r="E173" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F173" t="s">
         <v>426</v>
       </c>
       <c r="G173" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H173" s="3" t="s">
         <v>53</v>
@@ -8688,7 +8682,7 @@
         <v>1</v>
       </c>
       <c r="J173" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -8720,7 +8714,7 @@
         <v>1</v>
       </c>
       <c r="J174" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -8737,13 +8731,13 @@
         <v>496</v>
       </c>
       <c r="E175" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F175" t="s">
         <v>426</v>
       </c>
       <c r="G175" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H175" s="3" t="s">
         <v>53</v>
@@ -8752,7 +8746,7 @@
         <v>1</v>
       </c>
       <c r="J175" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -8784,7 +8778,7 @@
         <v>1</v>
       </c>
       <c r="J176" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -8816,7 +8810,7 @@
         <v>1</v>
       </c>
       <c r="J177" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -8848,7 +8842,7 @@
         <v>1</v>
       </c>
       <c r="J178" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -8880,7 +8874,7 @@
         <v>1</v>
       </c>
       <c r="J179" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -8912,7 +8906,7 @@
         <v>1</v>
       </c>
       <c r="J180" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -8944,7 +8938,7 @@
         <v>1</v>
       </c>
       <c r="J181" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -8976,7 +8970,7 @@
         <v>1</v>
       </c>
       <c r="J182" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -9008,7 +9002,7 @@
         <v>1</v>
       </c>
       <c r="J183" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -9040,12 +9034,12 @@
         <v>1</v>
       </c>
       <c r="J184" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B185" t="s">
         <v>500</v>
@@ -9054,10 +9048,10 @@
         <v>501</v>
       </c>
       <c r="D185" t="s">
+        <v>528</v>
+      </c>
+      <c r="E185" t="s">
         <v>529</v>
-      </c>
-      <c r="E185" t="s">
-        <v>530</v>
       </c>
       <c r="F185" t="s">
         <v>504</v>
@@ -9072,12 +9066,12 @@
         <v>1</v>
       </c>
       <c r="J185" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B186" t="s">
         <v>500</v>
@@ -9086,10 +9080,10 @@
         <v>501</v>
       </c>
       <c r="D186" t="s">
+        <v>531</v>
+      </c>
+      <c r="E186" t="s">
         <v>532</v>
-      </c>
-      <c r="E186" t="s">
-        <v>533</v>
       </c>
       <c r="F186" t="s">
         <v>504</v>
@@ -9104,12 +9098,12 @@
         <v>1</v>
       </c>
       <c r="J186" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B187" t="s">
         <v>500</v>
@@ -9118,10 +9112,10 @@
         <v>501</v>
       </c>
       <c r="D187" t="s">
+        <v>534</v>
+      </c>
+      <c r="E187" t="s">
         <v>535</v>
-      </c>
-      <c r="E187" t="s">
-        <v>536</v>
       </c>
       <c r="F187" t="s">
         <v>504</v>
@@ -9136,12 +9130,12 @@
         <v>1</v>
       </c>
       <c r="J187" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B188" t="s">
         <v>500</v>
@@ -9150,10 +9144,10 @@
         <v>501</v>
       </c>
       <c r="D188" t="s">
+        <v>537</v>
+      </c>
+      <c r="E188" t="s">
         <v>538</v>
-      </c>
-      <c r="E188" t="s">
-        <v>539</v>
       </c>
       <c r="F188" t="s">
         <v>504</v>
@@ -9168,12 +9162,12 @@
         <v>1</v>
       </c>
       <c r="J188" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B189" t="s">
         <v>500</v>
@@ -9182,10 +9176,10 @@
         <v>501</v>
       </c>
       <c r="D189" t="s">
+        <v>540</v>
+      </c>
+      <c r="E189" t="s">
         <v>541</v>
-      </c>
-      <c r="E189" t="s">
-        <v>542</v>
       </c>
       <c r="F189" t="s">
         <v>504</v>
@@ -9200,12 +9194,12 @@
         <v>1</v>
       </c>
       <c r="J189" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B190" t="s">
         <v>500</v>
@@ -9214,10 +9208,10 @@
         <v>501</v>
       </c>
       <c r="D190" t="s">
+        <v>543</v>
+      </c>
+      <c r="E190" t="s">
         <v>544</v>
-      </c>
-      <c r="E190" t="s">
-        <v>545</v>
       </c>
       <c r="F190" t="s">
         <v>504</v>
@@ -9232,12 +9226,12 @@
         <v>1</v>
       </c>
       <c r="J190" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B191" t="s">
         <v>500</v>
@@ -9246,10 +9240,10 @@
         <v>501</v>
       </c>
       <c r="D191" t="s">
+        <v>546</v>
+      </c>
+      <c r="E191" t="s">
         <v>547</v>
-      </c>
-      <c r="E191" t="s">
-        <v>548</v>
       </c>
       <c r="F191" t="s">
         <v>504</v>
@@ -9264,12 +9258,12 @@
         <v>1</v>
       </c>
       <c r="J191" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B192" t="s">
         <v>500</v>
@@ -9278,10 +9272,10 @@
         <v>501</v>
       </c>
       <c r="D192" t="s">
+        <v>549</v>
+      </c>
+      <c r="E192" t="s">
         <v>550</v>
-      </c>
-      <c r="E192" t="s">
-        <v>551</v>
       </c>
       <c r="F192" t="s">
         <v>504</v>
@@ -9296,12 +9290,12 @@
         <v>1</v>
       </c>
       <c r="J192" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B193" t="s">
         <v>500</v>
@@ -9310,10 +9304,10 @@
         <v>501</v>
       </c>
       <c r="D193" t="s">
+        <v>552</v>
+      </c>
+      <c r="E193" t="s">
         <v>553</v>
-      </c>
-      <c r="E193" t="s">
-        <v>554</v>
       </c>
       <c r="F193" t="s">
         <v>504</v>
@@ -9328,12 +9322,12 @@
         <v>1</v>
       </c>
       <c r="J193" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B194" t="s">
         <v>500</v>
@@ -9342,10 +9336,10 @@
         <v>501</v>
       </c>
       <c r="D194" t="s">
+        <v>555</v>
+      </c>
+      <c r="E194" t="s">
         <v>556</v>
-      </c>
-      <c r="E194" t="s">
-        <v>557</v>
       </c>
       <c r="F194" t="s">
         <v>504</v>
@@ -9360,12 +9354,12 @@
         <v>1</v>
       </c>
       <c r="J194" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B195" t="s">
         <v>500</v>
@@ -9374,10 +9368,10 @@
         <v>501</v>
       </c>
       <c r="D195" t="s">
+        <v>558</v>
+      </c>
+      <c r="E195" t="s">
         <v>559</v>
-      </c>
-      <c r="E195" t="s">
-        <v>560</v>
       </c>
       <c r="F195" t="s">
         <v>504</v>
@@ -9392,12 +9386,12 @@
         <v>1</v>
       </c>
       <c r="J195" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B196" t="s">
         <v>500</v>
@@ -9406,10 +9400,10 @@
         <v>501</v>
       </c>
       <c r="D196" t="s">
+        <v>561</v>
+      </c>
+      <c r="E196" t="s">
         <v>562</v>
-      </c>
-      <c r="E196" t="s">
-        <v>563</v>
       </c>
       <c r="F196" t="s">
         <v>504</v>
@@ -9424,12 +9418,12 @@
         <v>1</v>
       </c>
       <c r="J196" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B197" t="s">
         <v>500</v>
@@ -9438,7 +9432,7 @@
         <v>501</v>
       </c>
       <c r="D197" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E197" t="s">
         <v>503</v>
@@ -9456,12 +9450,12 @@
         <v>1</v>
       </c>
       <c r="J197" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B198" t="s">
         <v>500</v>
@@ -9470,7 +9464,7 @@
         <v>501</v>
       </c>
       <c r="D198" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E198" t="s">
         <v>508</v>
@@ -9488,12 +9482,12 @@
         <v>1</v>
       </c>
       <c r="J198" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B199" t="s">
         <v>500</v>
@@ -9502,7 +9496,7 @@
         <v>501</v>
       </c>
       <c r="D199" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E199" t="s">
         <v>511</v>
@@ -9520,12 +9514,12 @@
         <v>1</v>
       </c>
       <c r="J199" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B200" t="s">
         <v>500</v>
@@ -9534,7 +9528,7 @@
         <v>501</v>
       </c>
       <c r="D200" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E200" t="s">
         <v>514</v>
@@ -9552,12 +9546,12 @@
         <v>1</v>
       </c>
       <c r="J200" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B201" t="s">
         <v>500</v>
@@ -9566,7 +9560,7 @@
         <v>501</v>
       </c>
       <c r="D201" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E201" t="s">
         <v>517</v>
@@ -9584,12 +9578,12 @@
         <v>1</v>
       </c>
       <c r="J201" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B202" t="s">
         <v>500</v>
@@ -9598,7 +9592,7 @@
         <v>501</v>
       </c>
       <c r="D202" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E202" t="s">
         <v>520</v>
@@ -9616,12 +9610,12 @@
         <v>1</v>
       </c>
       <c r="J202" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B203" t="s">
         <v>500</v>
@@ -9630,7 +9624,7 @@
         <v>501</v>
       </c>
       <c r="D203" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E203" t="s">
         <v>523</v>
@@ -9648,12 +9642,12 @@
         <v>1</v>
       </c>
       <c r="J203" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B204" t="s">
         <v>500</v>
@@ -9662,7 +9656,7 @@
         <v>501</v>
       </c>
       <c r="D204" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E204" t="s">
         <v>526</v>
@@ -9680,12 +9674,12 @@
         <v>1</v>
       </c>
       <c r="J204" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B205" t="s">
         <v>500</v>
@@ -9694,10 +9688,10 @@
         <v>501</v>
       </c>
       <c r="D205" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E205" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F205" t="s">
         <v>504</v>
@@ -9712,12 +9706,12 @@
         <v>1</v>
       </c>
       <c r="J205" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B206" t="s">
         <v>500</v>
@@ -9726,10 +9720,10 @@
         <v>501</v>
       </c>
       <c r="D206" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E206" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F206" t="s">
         <v>504</v>
@@ -9744,12 +9738,12 @@
         <v>1</v>
       </c>
       <c r="J206" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B207" t="s">
         <v>500</v>
@@ -9758,10 +9752,10 @@
         <v>501</v>
       </c>
       <c r="D207" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E207" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F207" t="s">
         <v>504</v>
@@ -9776,12 +9770,12 @@
         <v>1</v>
       </c>
       <c r="J207" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B208" t="s">
         <v>500</v>
@@ -9790,10 +9784,10 @@
         <v>501</v>
       </c>
       <c r="D208" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E208" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F208" t="s">
         <v>504</v>
@@ -9808,12 +9802,12 @@
         <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B209" t="s">
         <v>500</v>
@@ -9822,10 +9816,10 @@
         <v>501</v>
       </c>
       <c r="D209" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E209" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F209" t="s">
         <v>504</v>
@@ -9840,12 +9834,12 @@
         <v>1</v>
       </c>
       <c r="J209" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B210" t="s">
         <v>500</v>
@@ -9854,10 +9848,10 @@
         <v>501</v>
       </c>
       <c r="D210" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E210" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F210" t="s">
         <v>504</v>
@@ -9872,12 +9866,12 @@
         <v>1</v>
       </c>
       <c r="J210" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B211" t="s">
         <v>500</v>
@@ -9886,10 +9880,10 @@
         <v>501</v>
       </c>
       <c r="D211" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E211" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F211" t="s">
         <v>504</v>
@@ -9904,31 +9898,31 @@
         <v>1</v>
       </c>
       <c r="J211" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>593</v>
+      </c>
+      <c r="B212" t="s">
         <v>594</v>
       </c>
-      <c r="B212" t="s">
+      <c r="C212" t="s">
         <v>595</v>
       </c>
-      <c r="C212" t="s">
+      <c r="D212" t="s">
         <v>596</v>
       </c>
-      <c r="D212" t="s">
+      <c r="E212" t="s">
         <v>597</v>
       </c>
-      <c r="E212" t="s">
+      <c r="F212" t="s">
         <v>598</v>
       </c>
-      <c r="F212" t="s">
+      <c r="G212" t="s">
         <v>599</v>
       </c>
-      <c r="G212" t="s">
-        <v>600</v>
-      </c>
       <c r="H212" s="3" t="s">
         <v>53</v>
       </c>
@@ -9936,31 +9930,31 @@
         <v>1</v>
       </c>
       <c r="J212" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>600</v>
+      </c>
+      <c r="B213" t="s">
+        <v>594</v>
+      </c>
+      <c r="C213" t="s">
+        <v>595</v>
+      </c>
+      <c r="D213" t="s">
         <v>601</v>
       </c>
-      <c r="B213" t="s">
-        <v>595</v>
-      </c>
-      <c r="C213" t="s">
-        <v>596</v>
-      </c>
-      <c r="D213" t="s">
+      <c r="E213" t="s">
         <v>602</v>
       </c>
-      <c r="E213" t="s">
-        <v>603</v>
-      </c>
       <c r="F213" t="s">
+        <v>598</v>
+      </c>
+      <c r="G213" t="s">
         <v>599</v>
       </c>
-      <c r="G213" t="s">
-        <v>600</v>
-      </c>
       <c r="H213" s="3" t="s">
         <v>53</v>
       </c>
@@ -9968,31 +9962,31 @@
         <v>1</v>
       </c>
       <c r="J213" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>603</v>
+      </c>
+      <c r="B214" t="s">
+        <v>594</v>
+      </c>
+      <c r="C214" t="s">
+        <v>595</v>
+      </c>
+      <c r="D214" t="s">
         <v>604</v>
       </c>
-      <c r="B214" t="s">
-        <v>595</v>
-      </c>
-      <c r="C214" t="s">
-        <v>596</v>
-      </c>
-      <c r="D214" t="s">
+      <c r="E214" t="s">
         <v>605</v>
       </c>
-      <c r="E214" t="s">
-        <v>606</v>
-      </c>
       <c r="F214" t="s">
+        <v>598</v>
+      </c>
+      <c r="G214" t="s">
         <v>599</v>
       </c>
-      <c r="G214" t="s">
-        <v>600</v>
-      </c>
       <c r="H214" s="3" t="s">
         <v>53</v>
       </c>
@@ -10000,31 +9994,31 @@
         <v>1</v>
       </c>
       <c r="J214" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>606</v>
+      </c>
+      <c r="B215" t="s">
+        <v>594</v>
+      </c>
+      <c r="C215" t="s">
+        <v>595</v>
+      </c>
+      <c r="D215" t="s">
         <v>607</v>
       </c>
-      <c r="B215" t="s">
-        <v>595</v>
-      </c>
-      <c r="C215" t="s">
-        <v>596</v>
-      </c>
-      <c r="D215" t="s">
+      <c r="E215" t="s">
         <v>608</v>
       </c>
-      <c r="E215" t="s">
-        <v>609</v>
-      </c>
       <c r="F215" t="s">
+        <v>598</v>
+      </c>
+      <c r="G215" t="s">
         <v>599</v>
       </c>
-      <c r="G215" t="s">
-        <v>600</v>
-      </c>
       <c r="H215" s="3" t="s">
         <v>53</v>
       </c>
@@ -10032,31 +10026,31 @@
         <v>1</v>
       </c>
       <c r="J215" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>609</v>
+      </c>
+      <c r="B216" t="s">
+        <v>594</v>
+      </c>
+      <c r="C216" t="s">
+        <v>595</v>
+      </c>
+      <c r="D216" t="s">
         <v>610</v>
       </c>
-      <c r="B216" t="s">
-        <v>595</v>
-      </c>
-      <c r="C216" t="s">
-        <v>596</v>
-      </c>
-      <c r="D216" t="s">
+      <c r="E216" t="s">
         <v>611</v>
       </c>
-      <c r="E216" t="s">
-        <v>612</v>
-      </c>
       <c r="F216" t="s">
+        <v>598</v>
+      </c>
+      <c r="G216" t="s">
         <v>599</v>
       </c>
-      <c r="G216" t="s">
-        <v>600</v>
-      </c>
       <c r="H216" s="3" t="s">
         <v>53</v>
       </c>
@@ -10064,31 +10058,31 @@
         <v>1</v>
       </c>
       <c r="J216" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>612</v>
+      </c>
+      <c r="B217" t="s">
+        <v>594</v>
+      </c>
+      <c r="C217" t="s">
+        <v>595</v>
+      </c>
+      <c r="D217" t="s">
         <v>613</v>
       </c>
-      <c r="B217" t="s">
-        <v>595</v>
-      </c>
-      <c r="C217" t="s">
-        <v>596</v>
-      </c>
-      <c r="D217" t="s">
+      <c r="E217" t="s">
         <v>614</v>
       </c>
-      <c r="E217" t="s">
-        <v>615</v>
-      </c>
       <c r="F217" t="s">
+        <v>598</v>
+      </c>
+      <c r="G217" t="s">
         <v>599</v>
       </c>
-      <c r="G217" t="s">
-        <v>600</v>
-      </c>
       <c r="H217" s="3" t="s">
         <v>53</v>
       </c>
@@ -10096,31 +10090,31 @@
         <v>1</v>
       </c>
       <c r="J217" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>615</v>
+      </c>
+      <c r="B218" t="s">
+        <v>594</v>
+      </c>
+      <c r="C218" t="s">
+        <v>595</v>
+      </c>
+      <c r="D218" t="s">
         <v>616</v>
       </c>
-      <c r="B218" t="s">
-        <v>595</v>
-      </c>
-      <c r="C218" t="s">
-        <v>596</v>
-      </c>
-      <c r="D218" t="s">
+      <c r="E218" t="s">
         <v>617</v>
       </c>
-      <c r="E218" t="s">
-        <v>618</v>
-      </c>
       <c r="F218" t="s">
+        <v>598</v>
+      </c>
+      <c r="G218" t="s">
         <v>599</v>
       </c>
-      <c r="G218" t="s">
-        <v>600</v>
-      </c>
       <c r="H218" s="3" t="s">
         <v>53</v>
       </c>
@@ -10128,31 +10122,31 @@
         <v>1</v>
       </c>
       <c r="J218" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>618</v>
+      </c>
+      <c r="B219" t="s">
+        <v>594</v>
+      </c>
+      <c r="C219" t="s">
+        <v>595</v>
+      </c>
+      <c r="D219" t="s">
         <v>619</v>
       </c>
-      <c r="B219" t="s">
-        <v>595</v>
-      </c>
-      <c r="C219" t="s">
-        <v>596</v>
-      </c>
-      <c r="D219" t="s">
+      <c r="E219" t="s">
         <v>620</v>
       </c>
-      <c r="E219" t="s">
-        <v>621</v>
-      </c>
       <c r="F219" t="s">
+        <v>598</v>
+      </c>
+      <c r="G219" t="s">
         <v>599</v>
       </c>
-      <c r="G219" t="s">
-        <v>600</v>
-      </c>
       <c r="H219" s="3" t="s">
         <v>53</v>
       </c>
@@ -10160,31 +10154,31 @@
         <v>1</v>
       </c>
       <c r="J219" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>621</v>
+      </c>
+      <c r="B220" t="s">
+        <v>594</v>
+      </c>
+      <c r="C220" t="s">
+        <v>595</v>
+      </c>
+      <c r="D220" t="s">
         <v>622</v>
       </c>
-      <c r="B220" t="s">
-        <v>595</v>
-      </c>
-      <c r="C220" t="s">
-        <v>596</v>
-      </c>
-      <c r="D220" t="s">
+      <c r="E220" t="s">
         <v>623</v>
       </c>
-      <c r="E220" t="s">
-        <v>624</v>
-      </c>
       <c r="F220" t="s">
+        <v>598</v>
+      </c>
+      <c r="G220" t="s">
         <v>599</v>
       </c>
-      <c r="G220" t="s">
-        <v>600</v>
-      </c>
       <c r="H220" s="3" t="s">
         <v>53</v>
       </c>
@@ -10192,31 +10186,31 @@
         <v>1</v>
       </c>
       <c r="J220" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
+        <v>624</v>
+      </c>
+      <c r="B221" t="s">
+        <v>594</v>
+      </c>
+      <c r="C221" t="s">
+        <v>595</v>
+      </c>
+      <c r="D221" t="s">
         <v>625</v>
       </c>
-      <c r="B221" t="s">
-        <v>595</v>
-      </c>
-      <c r="C221" t="s">
-        <v>596</v>
-      </c>
-      <c r="D221" t="s">
+      <c r="E221" t="s">
         <v>626</v>
       </c>
-      <c r="E221" t="s">
-        <v>627</v>
-      </c>
       <c r="F221" t="s">
+        <v>598</v>
+      </c>
+      <c r="G221" t="s">
         <v>599</v>
       </c>
-      <c r="G221" t="s">
-        <v>600</v>
-      </c>
       <c r="H221" s="3" t="s">
         <v>53</v>
       </c>
@@ -10224,31 +10218,31 @@
         <v>1</v>
       </c>
       <c r="J221" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
+        <v>627</v>
+      </c>
+      <c r="B222" t="s">
+        <v>594</v>
+      </c>
+      <c r="C222" t="s">
+        <v>595</v>
+      </c>
+      <c r="D222" t="s">
         <v>628</v>
       </c>
-      <c r="B222" t="s">
-        <v>595</v>
-      </c>
-      <c r="C222" t="s">
-        <v>596</v>
-      </c>
-      <c r="D222" t="s">
+      <c r="E222" t="s">
         <v>629</v>
       </c>
-      <c r="E222" t="s">
-        <v>630</v>
-      </c>
       <c r="F222" t="s">
+        <v>598</v>
+      </c>
+      <c r="G222" t="s">
         <v>599</v>
       </c>
-      <c r="G222" t="s">
-        <v>600</v>
-      </c>
       <c r="H222" s="3" t="s">
         <v>53</v>
       </c>
@@ -10256,31 +10250,31 @@
         <v>1</v>
       </c>
       <c r="J222" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
+        <v>630</v>
+      </c>
+      <c r="B223" t="s">
+        <v>594</v>
+      </c>
+      <c r="C223" t="s">
+        <v>595</v>
+      </c>
+      <c r="D223" t="s">
         <v>631</v>
       </c>
-      <c r="B223" t="s">
-        <v>595</v>
-      </c>
-      <c r="C223" t="s">
-        <v>596</v>
-      </c>
-      <c r="D223" t="s">
+      <c r="E223" t="s">
         <v>632</v>
       </c>
-      <c r="E223" t="s">
-        <v>633</v>
-      </c>
       <c r="F223" t="s">
+        <v>598</v>
+      </c>
+      <c r="G223" t="s">
         <v>599</v>
       </c>
-      <c r="G223" t="s">
-        <v>600</v>
-      </c>
       <c r="H223" s="3" t="s">
         <v>53</v>
       </c>
@@ -10288,31 +10282,31 @@
         <v>1</v>
       </c>
       <c r="J223" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
+        <v>633</v>
+      </c>
+      <c r="B224" t="s">
+        <v>594</v>
+      </c>
+      <c r="C224" t="s">
+        <v>595</v>
+      </c>
+      <c r="D224" t="s">
         <v>634</v>
       </c>
-      <c r="B224" t="s">
-        <v>595</v>
-      </c>
-      <c r="C224" t="s">
-        <v>596</v>
-      </c>
-      <c r="D224" t="s">
+      <c r="E224" t="s">
         <v>635</v>
       </c>
-      <c r="E224" t="s">
-        <v>636</v>
-      </c>
       <c r="F224" t="s">
+        <v>598</v>
+      </c>
+      <c r="G224" t="s">
         <v>599</v>
       </c>
-      <c r="G224" t="s">
-        <v>600</v>
-      </c>
       <c r="H224" s="3" t="s">
         <v>53</v>
       </c>
@@ -10320,31 +10314,31 @@
         <v>1</v>
       </c>
       <c r="J224" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>636</v>
+      </c>
+      <c r="B225" t="s">
+        <v>594</v>
+      </c>
+      <c r="C225" t="s">
+        <v>595</v>
+      </c>
+      <c r="D225" t="s">
         <v>637</v>
       </c>
-      <c r="B225" t="s">
-        <v>595</v>
-      </c>
-      <c r="C225" t="s">
-        <v>596</v>
-      </c>
-      <c r="D225" t="s">
+      <c r="E225" t="s">
         <v>638</v>
       </c>
-      <c r="E225" t="s">
-        <v>639</v>
-      </c>
       <c r="F225" t="s">
+        <v>598</v>
+      </c>
+      <c r="G225" t="s">
         <v>599</v>
       </c>
-      <c r="G225" t="s">
-        <v>600</v>
-      </c>
       <c r="H225" s="3" t="s">
         <v>53</v>
       </c>
@@ -10352,31 +10346,31 @@
         <v>1</v>
       </c>
       <c r="J225" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
+        <v>639</v>
+      </c>
+      <c r="B226" t="s">
+        <v>594</v>
+      </c>
+      <c r="C226" t="s">
+        <v>595</v>
+      </c>
+      <c r="D226" t="s">
         <v>640</v>
       </c>
-      <c r="B226" t="s">
-        <v>595</v>
-      </c>
-      <c r="C226" t="s">
-        <v>596</v>
-      </c>
-      <c r="D226" t="s">
+      <c r="E226" t="s">
         <v>641</v>
       </c>
-      <c r="E226" t="s">
-        <v>642</v>
-      </c>
       <c r="F226" t="s">
+        <v>598</v>
+      </c>
+      <c r="G226" t="s">
         <v>599</v>
       </c>
-      <c r="G226" t="s">
-        <v>600</v>
-      </c>
       <c r="H226" s="3" t="s">
         <v>53</v>
       </c>
@@ -10384,31 +10378,31 @@
         <v>1</v>
       </c>
       <c r="J226" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>642</v>
+      </c>
+      <c r="B227" t="s">
+        <v>594</v>
+      </c>
+      <c r="C227" t="s">
+        <v>595</v>
+      </c>
+      <c r="D227" t="s">
         <v>643</v>
       </c>
-      <c r="B227" t="s">
-        <v>595</v>
-      </c>
-      <c r="C227" t="s">
-        <v>596</v>
-      </c>
-      <c r="D227" t="s">
+      <c r="E227" t="s">
         <v>644</v>
       </c>
-      <c r="E227" t="s">
-        <v>645</v>
-      </c>
       <c r="F227" t="s">
+        <v>598</v>
+      </c>
+      <c r="G227" t="s">
         <v>599</v>
       </c>
-      <c r="G227" t="s">
-        <v>600</v>
-      </c>
       <c r="H227" s="3" t="s">
         <v>53</v>
       </c>
@@ -10416,31 +10410,31 @@
         <v>1</v>
       </c>
       <c r="J227" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
+        <v>645</v>
+      </c>
+      <c r="B228" t="s">
+        <v>594</v>
+      </c>
+      <c r="C228" t="s">
+        <v>595</v>
+      </c>
+      <c r="D228" t="s">
         <v>646</v>
       </c>
-      <c r="B228" t="s">
-        <v>595</v>
-      </c>
-      <c r="C228" t="s">
-        <v>596</v>
-      </c>
-      <c r="D228" t="s">
+      <c r="E228" t="s">
         <v>647</v>
       </c>
-      <c r="E228" t="s">
-        <v>648</v>
-      </c>
       <c r="F228" t="s">
+        <v>598</v>
+      </c>
+      <c r="G228" t="s">
         <v>599</v>
       </c>
-      <c r="G228" t="s">
-        <v>600</v>
-      </c>
       <c r="H228" s="3" t="s">
         <v>53</v>
       </c>
@@ -10448,31 +10442,31 @@
         <v>1</v>
       </c>
       <c r="J228" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>648</v>
+      </c>
+      <c r="B229" t="s">
+        <v>594</v>
+      </c>
+      <c r="C229" t="s">
+        <v>595</v>
+      </c>
+      <c r="D229" t="s">
         <v>649</v>
       </c>
-      <c r="B229" t="s">
-        <v>595</v>
-      </c>
-      <c r="C229" t="s">
-        <v>596</v>
-      </c>
-      <c r="D229" t="s">
+      <c r="E229" t="s">
         <v>650</v>
       </c>
-      <c r="E229" t="s">
-        <v>651</v>
-      </c>
       <c r="F229" t="s">
+        <v>598</v>
+      </c>
+      <c r="G229" t="s">
         <v>599</v>
       </c>
-      <c r="G229" t="s">
-        <v>600</v>
-      </c>
       <c r="H229" s="3" t="s">
         <v>53</v>
       </c>
@@ -10480,31 +10474,31 @@
         <v>1</v>
       </c>
       <c r="J229" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>651</v>
+      </c>
+      <c r="B230" t="s">
+        <v>594</v>
+      </c>
+      <c r="C230" t="s">
+        <v>595</v>
+      </c>
+      <c r="D230" t="s">
         <v>652</v>
       </c>
-      <c r="B230" t="s">
-        <v>595</v>
-      </c>
-      <c r="C230" t="s">
-        <v>596</v>
-      </c>
-      <c r="D230" t="s">
+      <c r="E230" t="s">
         <v>653</v>
       </c>
-      <c r="E230" t="s">
-        <v>654</v>
-      </c>
       <c r="F230" t="s">
+        <v>598</v>
+      </c>
+      <c r="G230" t="s">
         <v>599</v>
       </c>
-      <c r="G230" t="s">
-        <v>600</v>
-      </c>
       <c r="H230" s="3" t="s">
         <v>53</v>
       </c>
@@ -10512,31 +10506,31 @@
         <v>1</v>
       </c>
       <c r="J230" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>654</v>
+      </c>
+      <c r="B231" t="s">
+        <v>594</v>
+      </c>
+      <c r="C231" t="s">
+        <v>595</v>
+      </c>
+      <c r="D231" t="s">
         <v>655</v>
       </c>
-      <c r="B231" t="s">
-        <v>595</v>
-      </c>
-      <c r="C231" t="s">
-        <v>596</v>
-      </c>
-      <c r="D231" t="s">
+      <c r="E231" t="s">
         <v>656</v>
       </c>
-      <c r="E231" t="s">
-        <v>657</v>
-      </c>
       <c r="F231" t="s">
+        <v>598</v>
+      </c>
+      <c r="G231" t="s">
         <v>599</v>
       </c>
-      <c r="G231" t="s">
-        <v>600</v>
-      </c>
       <c r="H231" s="3" t="s">
         <v>53</v>
       </c>
@@ -10544,31 +10538,31 @@
         <v>1</v>
       </c>
       <c r="J231" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>657</v>
+      </c>
+      <c r="B232" t="s">
+        <v>594</v>
+      </c>
+      <c r="C232" t="s">
+        <v>595</v>
+      </c>
+      <c r="D232" t="s">
         <v>658</v>
       </c>
-      <c r="B232" t="s">
-        <v>595</v>
-      </c>
-      <c r="C232" t="s">
-        <v>596</v>
-      </c>
-      <c r="D232" t="s">
+      <c r="E232" t="s">
         <v>659</v>
       </c>
-      <c r="E232" t="s">
-        <v>660</v>
-      </c>
       <c r="F232" t="s">
+        <v>598</v>
+      </c>
+      <c r="G232" t="s">
         <v>599</v>
       </c>
-      <c r="G232" t="s">
-        <v>600</v>
-      </c>
       <c r="H232" s="3" t="s">
         <v>53</v>
       </c>
@@ -10576,31 +10570,31 @@
         <v>1</v>
       </c>
       <c r="J232" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>660</v>
+      </c>
+      <c r="B233" t="s">
+        <v>594</v>
+      </c>
+      <c r="C233" t="s">
+        <v>595</v>
+      </c>
+      <c r="D233" t="s">
         <v>661</v>
       </c>
-      <c r="B233" t="s">
-        <v>595</v>
-      </c>
-      <c r="C233" t="s">
-        <v>596</v>
-      </c>
-      <c r="D233" t="s">
+      <c r="E233" t="s">
         <v>662</v>
       </c>
-      <c r="E233" t="s">
-        <v>663</v>
-      </c>
       <c r="F233" t="s">
+        <v>598</v>
+      </c>
+      <c r="G233" t="s">
         <v>599</v>
       </c>
-      <c r="G233" t="s">
-        <v>600</v>
-      </c>
       <c r="H233" s="3" t="s">
         <v>53</v>
       </c>
@@ -10608,31 +10602,31 @@
         <v>1</v>
       </c>
       <c r="J233" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
+        <v>663</v>
+      </c>
+      <c r="B234" t="s">
+        <v>594</v>
+      </c>
+      <c r="C234" t="s">
+        <v>595</v>
+      </c>
+      <c r="D234" t="s">
         <v>664</v>
       </c>
-      <c r="B234" t="s">
-        <v>595</v>
-      </c>
-      <c r="C234" t="s">
-        <v>596</v>
-      </c>
-      <c r="D234" t="s">
+      <c r="E234" t="s">
         <v>665</v>
       </c>
-      <c r="E234" t="s">
-        <v>666</v>
-      </c>
       <c r="F234" t="s">
+        <v>598</v>
+      </c>
+      <c r="G234" t="s">
         <v>599</v>
       </c>
-      <c r="G234" t="s">
-        <v>600</v>
-      </c>
       <c r="H234" s="3" t="s">
         <v>53</v>
       </c>
@@ -10640,31 +10634,31 @@
         <v>1</v>
       </c>
       <c r="J234" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
+        <v>666</v>
+      </c>
+      <c r="B235" t="s">
+        <v>594</v>
+      </c>
+      <c r="C235" t="s">
+        <v>595</v>
+      </c>
+      <c r="D235" t="s">
         <v>667</v>
       </c>
-      <c r="B235" t="s">
-        <v>595</v>
-      </c>
-      <c r="C235" t="s">
-        <v>596</v>
-      </c>
-      <c r="D235" t="s">
+      <c r="E235" t="s">
         <v>668</v>
       </c>
-      <c r="E235" t="s">
-        <v>669</v>
-      </c>
       <c r="F235" t="s">
+        <v>598</v>
+      </c>
+      <c r="G235" t="s">
         <v>599</v>
       </c>
-      <c r="G235" t="s">
-        <v>600</v>
-      </c>
       <c r="H235" s="3" t="s">
         <v>53</v>
       </c>
@@ -10672,31 +10666,31 @@
         <v>1</v>
       </c>
       <c r="J235" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
+        <v>669</v>
+      </c>
+      <c r="B236" t="s">
+        <v>594</v>
+      </c>
+      <c r="C236" t="s">
+        <v>595</v>
+      </c>
+      <c r="D236" t="s">
         <v>670</v>
       </c>
-      <c r="B236" t="s">
-        <v>595</v>
-      </c>
-      <c r="C236" t="s">
-        <v>596</v>
-      </c>
-      <c r="D236" t="s">
+      <c r="E236" t="s">
         <v>671</v>
       </c>
-      <c r="E236" t="s">
-        <v>672</v>
-      </c>
       <c r="F236" t="s">
+        <v>598</v>
+      </c>
+      <c r="G236" t="s">
         <v>599</v>
       </c>
-      <c r="G236" t="s">
-        <v>600</v>
-      </c>
       <c r="H236" s="3" t="s">
         <v>53</v>
       </c>
@@ -10704,39 +10698,39 @@
         <v>1</v>
       </c>
       <c r="J236" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
+        <v>672</v>
+      </c>
+      <c r="B237" t="s">
+        <v>594</v>
+      </c>
+      <c r="C237" t="s">
+        <v>595</v>
+      </c>
+      <c r="D237" t="s">
         <v>673</v>
       </c>
-      <c r="B237" t="s">
-        <v>595</v>
-      </c>
-      <c r="C237" t="s">
-        <v>596</v>
-      </c>
-      <c r="D237" t="s">
+      <c r="E237" t="s">
         <v>674</v>
       </c>
-      <c r="E237" t="s">
+      <c r="F237" t="s">
+        <v>598</v>
+      </c>
+      <c r="G237" t="s">
+        <v>599</v>
+      </c>
+      <c r="H237" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I237">
+        <v>1</v>
+      </c>
+      <c r="J237" t="s">
         <v>675</v>
-      </c>
-      <c r="F237" t="s">
-        <v>599</v>
-      </c>
-      <c r="G237" t="s">
-        <v>600</v>
-      </c>
-      <c r="H237" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I237">
-        <v>1</v>
-      </c>
-      <c r="J237" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
@@ -10744,10 +10738,10 @@
         <v>676</v>
       </c>
       <c r="B238" t="s">
+        <v>594</v>
+      </c>
+      <c r="C238" t="s">
         <v>595</v>
-      </c>
-      <c r="C238" t="s">
-        <v>596</v>
       </c>
       <c r="D238" t="s">
         <v>677</v>
@@ -10756,11 +10750,11 @@
         <v>678</v>
       </c>
       <c r="F238" t="s">
+        <v>598</v>
+      </c>
+      <c r="G238" t="s">
         <v>599</v>
       </c>
-      <c r="G238" t="s">
-        <v>600</v>
-      </c>
       <c r="H238" s="3" t="s">
         <v>53</v>
       </c>
@@ -10768,7 +10762,7 @@
         <v>1</v>
       </c>
       <c r="J238" t="s">
-        <v>527</v>
+        <v>675</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
@@ -10776,10 +10770,10 @@
         <v>679</v>
       </c>
       <c r="B239" t="s">
+        <v>594</v>
+      </c>
+      <c r="C239" t="s">
         <v>595</v>
-      </c>
-      <c r="C239" t="s">
-        <v>596</v>
       </c>
       <c r="D239" t="s">
         <v>680</v>
@@ -10788,11 +10782,11 @@
         <v>681</v>
       </c>
       <c r="F239" t="s">
+        <v>598</v>
+      </c>
+      <c r="G239" t="s">
         <v>599</v>
       </c>
-      <c r="G239" t="s">
-        <v>600</v>
-      </c>
       <c r="H239" s="3" t="s">
         <v>53</v>
       </c>
@@ -10800,7 +10794,7 @@
         <v>1</v>
       </c>
       <c r="J239" t="s">
-        <v>527</v>
+        <v>675</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
@@ -10808,10 +10802,10 @@
         <v>682</v>
       </c>
       <c r="B240" t="s">
+        <v>594</v>
+      </c>
+      <c r="C240" t="s">
         <v>595</v>
-      </c>
-      <c r="C240" t="s">
-        <v>596</v>
       </c>
       <c r="D240" t="s">
         <v>683</v>
@@ -10820,11 +10814,11 @@
         <v>684</v>
       </c>
       <c r="F240" t="s">
+        <v>598</v>
+      </c>
+      <c r="G240" t="s">
         <v>599</v>
       </c>
-      <c r="G240" t="s">
-        <v>600</v>
-      </c>
       <c r="H240" s="3" t="s">
         <v>53</v>
       </c>
@@ -10832,7 +10826,7 @@
         <v>1</v>
       </c>
       <c r="J240" t="s">
-        <v>527</v>
+        <v>675</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
@@ -10840,10 +10834,10 @@
         <v>685</v>
       </c>
       <c r="B241" t="s">
+        <v>594</v>
+      </c>
+      <c r="C241" t="s">
         <v>595</v>
-      </c>
-      <c r="C241" t="s">
-        <v>596</v>
       </c>
       <c r="D241" t="s">
         <v>686</v>
@@ -10852,11 +10846,11 @@
         <v>687</v>
       </c>
       <c r="F241" t="s">
+        <v>598</v>
+      </c>
+      <c r="G241" t="s">
         <v>599</v>
       </c>
-      <c r="G241" t="s">
-        <v>600</v>
-      </c>
       <c r="H241" s="3" t="s">
         <v>53</v>
       </c>
@@ -10864,7 +10858,7 @@
         <v>1</v>
       </c>
       <c r="J241" t="s">
-        <v>527</v>
+        <v>675</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
@@ -10896,12 +10890,12 @@
         <v>1</v>
       </c>
       <c r="J242" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B243" t="s">
         <v>689</v>
@@ -10910,10 +10904,10 @@
         <v>690</v>
       </c>
       <c r="D243" t="s">
+        <v>696</v>
+      </c>
+      <c r="E243" t="s">
         <v>697</v>
-      </c>
-      <c r="E243" t="s">
-        <v>698</v>
       </c>
       <c r="F243" t="s">
         <v>693</v>
@@ -10928,12 +10922,12 @@
         <v>1</v>
       </c>
       <c r="J243" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B244" t="s">
         <v>689</v>
@@ -10942,10 +10936,10 @@
         <v>690</v>
       </c>
       <c r="D244" t="s">
+        <v>699</v>
+      </c>
+      <c r="E244" t="s">
         <v>700</v>
-      </c>
-      <c r="E244" t="s">
-        <v>701</v>
       </c>
       <c r="F244" t="s">
         <v>693</v>
@@ -10960,12 +10954,12 @@
         <v>1</v>
       </c>
       <c r="J244" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B245" t="s">
         <v>689</v>
@@ -10974,17 +10968,17 @@
         <v>690</v>
       </c>
       <c r="D245" t="s">
+        <v>702</v>
+      </c>
+      <c r="E245" t="s">
         <v>703</v>
       </c>
-      <c r="E245" t="s">
+      <c r="F245" t="s">
         <v>704</v>
       </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
         <v>705</v>
       </c>
-      <c r="G245" t="s">
-        <v>706</v>
-      </c>
       <c r="H245" s="3" t="s">
         <v>53</v>
       </c>
@@ -10992,12 +10986,12 @@
         <v>1</v>
       </c>
       <c r="J245" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B246" t="s">
         <v>689</v>
@@ -11006,17 +11000,17 @@
         <v>690</v>
       </c>
       <c r="D246" t="s">
+        <v>707</v>
+      </c>
+      <c r="E246" t="s">
         <v>708</v>
       </c>
-      <c r="E246" t="s">
-        <v>709</v>
-      </c>
       <c r="F246" t="s">
+        <v>704</v>
+      </c>
+      <c r="G246" t="s">
         <v>705</v>
       </c>
-      <c r="G246" t="s">
-        <v>706</v>
-      </c>
       <c r="H246" s="3" t="s">
         <v>53</v>
       </c>
@@ -11024,12 +11018,12 @@
         <v>1</v>
       </c>
       <c r="J246" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B247" t="s">
         <v>689</v>
@@ -11038,10 +11032,10 @@
         <v>690</v>
       </c>
       <c r="D247" t="s">
+        <v>710</v>
+      </c>
+      <c r="E247" t="s">
         <v>711</v>
-      </c>
-      <c r="E247" t="s">
-        <v>712</v>
       </c>
       <c r="F247" t="s">
         <v>693</v>
@@ -11056,12 +11050,12 @@
         <v>1</v>
       </c>
       <c r="J247" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B248" t="s">
         <v>689</v>
@@ -11070,10 +11064,10 @@
         <v>690</v>
       </c>
       <c r="D248" t="s">
+        <v>713</v>
+      </c>
+      <c r="E248" t="s">
         <v>714</v>
-      </c>
-      <c r="E248" t="s">
-        <v>715</v>
       </c>
       <c r="F248" t="s">
         <v>693</v>
@@ -11088,12 +11082,12 @@
         <v>1</v>
       </c>
       <c r="J248" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B249" t="s">
         <v>689</v>
@@ -11102,10 +11096,10 @@
         <v>690</v>
       </c>
       <c r="D249" t="s">
+        <v>716</v>
+      </c>
+      <c r="E249" t="s">
         <v>717</v>
-      </c>
-      <c r="E249" t="s">
-        <v>718</v>
       </c>
       <c r="F249" t="s">
         <v>693</v>
@@ -11120,12 +11114,12 @@
         <v>1</v>
       </c>
       <c r="J249" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B250" t="s">
         <v>689</v>
@@ -11134,17 +11128,17 @@
         <v>690</v>
       </c>
       <c r="D250" t="s">
+        <v>719</v>
+      </c>
+      <c r="E250" t="s">
         <v>720</v>
       </c>
-      <c r="E250" t="s">
-        <v>721</v>
-      </c>
       <c r="F250" t="s">
+        <v>704</v>
+      </c>
+      <c r="G250" t="s">
         <v>705</v>
       </c>
-      <c r="G250" t="s">
-        <v>706</v>
-      </c>
       <c r="H250" s="3" t="s">
         <v>53</v>
       </c>
@@ -11152,12 +11146,12 @@
         <v>1</v>
       </c>
       <c r="J250" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B251" t="s">
         <v>689</v>
@@ -11166,17 +11160,17 @@
         <v>690</v>
       </c>
       <c r="D251" t="s">
+        <v>722</v>
+      </c>
+      <c r="E251" t="s">
         <v>723</v>
       </c>
-      <c r="E251" t="s">
-        <v>724</v>
-      </c>
       <c r="F251" t="s">
+        <v>704</v>
+      </c>
+      <c r="G251" t="s">
         <v>705</v>
       </c>
-      <c r="G251" t="s">
-        <v>706</v>
-      </c>
       <c r="H251" s="3" t="s">
         <v>53</v>
       </c>
@@ -11184,12 +11178,12 @@
         <v>1</v>
       </c>
       <c r="J251" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B252" t="s">
         <v>689</v>
@@ -11198,7 +11192,7 @@
         <v>690</v>
       </c>
       <c r="D252" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E252" t="s">
         <v>692</v>
@@ -11216,12 +11210,12 @@
         <v>1</v>
       </c>
       <c r="J252" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B253" t="s">
         <v>689</v>
@@ -11230,10 +11224,10 @@
         <v>690</v>
       </c>
       <c r="D253" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E253" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F253" t="s">
         <v>693</v>
@@ -11248,12 +11242,12 @@
         <v>1</v>
       </c>
       <c r="J253" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B254" t="s">
         <v>689</v>
@@ -11262,10 +11256,10 @@
         <v>690</v>
       </c>
       <c r="D254" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E254" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F254" t="s">
         <v>693</v>
@@ -11280,12 +11274,12 @@
         <v>1</v>
       </c>
       <c r="J254" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B255" t="s">
         <v>689</v>
@@ -11294,17 +11288,17 @@
         <v>690</v>
       </c>
       <c r="D255" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E255" t="s">
+        <v>703</v>
+      </c>
+      <c r="F255" t="s">
         <v>704</v>
       </c>
-      <c r="F255" t="s">
+      <c r="G255" t="s">
         <v>705</v>
       </c>
-      <c r="G255" t="s">
-        <v>706</v>
-      </c>
       <c r="H255" s="3" t="s">
         <v>53</v>
       </c>
@@ -11312,12 +11306,12 @@
         <v>1</v>
       </c>
       <c r="J255" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B256" t="s">
         <v>689</v>
@@ -11326,17 +11320,17 @@
         <v>690</v>
       </c>
       <c r="D256" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E256" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F256" t="s">
+        <v>704</v>
+      </c>
+      <c r="G256" t="s">
         <v>705</v>
       </c>
-      <c r="G256" t="s">
-        <v>706</v>
-      </c>
       <c r="H256" s="3" t="s">
         <v>53</v>
       </c>
@@ -11344,12 +11338,12 @@
         <v>1</v>
       </c>
       <c r="J256" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B257" t="s">
         <v>689</v>
@@ -11358,10 +11352,10 @@
         <v>690</v>
       </c>
       <c r="D257" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E257" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F257" t="s">
         <v>693</v>
@@ -11376,12 +11370,12 @@
         <v>1</v>
       </c>
       <c r="J257" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B258" t="s">
         <v>689</v>
@@ -11390,10 +11384,10 @@
         <v>690</v>
       </c>
       <c r="D258" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E258" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F258" t="s">
         <v>693</v>
@@ -11408,12 +11402,12 @@
         <v>1</v>
       </c>
       <c r="J258" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B259" t="s">
         <v>689</v>
@@ -11422,10 +11416,10 @@
         <v>690</v>
       </c>
       <c r="D259" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E259" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F259" t="s">
         <v>693</v>
@@ -11440,12 +11434,12 @@
         <v>1</v>
       </c>
       <c r="J259" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B260" t="s">
         <v>689</v>
@@ -11454,17 +11448,17 @@
         <v>690</v>
       </c>
       <c r="D260" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E260" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F260" t="s">
+        <v>704</v>
+      </c>
+      <c r="G260" t="s">
         <v>705</v>
       </c>
-      <c r="G260" t="s">
-        <v>706</v>
-      </c>
       <c r="H260" s="3" t="s">
         <v>53</v>
       </c>
@@ -11472,12 +11466,12 @@
         <v>1</v>
       </c>
       <c r="J260" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B261" t="s">
         <v>689</v>
@@ -11486,17 +11480,17 @@
         <v>690</v>
       </c>
       <c r="D261" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E261" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F261" t="s">
+        <v>704</v>
+      </c>
+      <c r="G261" t="s">
         <v>705</v>
       </c>
-      <c r="G261" t="s">
-        <v>706</v>
-      </c>
       <c r="H261" s="3" t="s">
         <v>53</v>
       </c>
@@ -11504,12 +11498,12 @@
         <v>1</v>
       </c>
       <c r="J261" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B262" t="s">
         <v>689</v>
@@ -11518,7 +11512,7 @@
         <v>690</v>
       </c>
       <c r="D262" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E262" t="s">
         <v>692</v>
@@ -11536,12 +11530,12 @@
         <v>1</v>
       </c>
       <c r="J262" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B263" t="s">
         <v>689</v>
@@ -11550,10 +11544,10 @@
         <v>690</v>
       </c>
       <c r="D263" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E263" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F263" t="s">
         <v>693</v>
@@ -11568,12 +11562,12 @@
         <v>1</v>
       </c>
       <c r="J263" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B264" t="s">
         <v>689</v>
@@ -11582,10 +11576,10 @@
         <v>690</v>
       </c>
       <c r="D264" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E264" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F264" t="s">
         <v>693</v>
@@ -11600,12 +11594,12 @@
         <v>1</v>
       </c>
       <c r="J264" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B265" t="s">
         <v>689</v>
@@ -11614,17 +11608,17 @@
         <v>690</v>
       </c>
       <c r="D265" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E265" t="s">
+        <v>703</v>
+      </c>
+      <c r="F265" t="s">
         <v>704</v>
       </c>
-      <c r="F265" t="s">
+      <c r="G265" t="s">
         <v>705</v>
       </c>
-      <c r="G265" t="s">
-        <v>706</v>
-      </c>
       <c r="H265" s="3" t="s">
         <v>53</v>
       </c>
@@ -11632,12 +11626,12 @@
         <v>1</v>
       </c>
       <c r="J265" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B266" t="s">
         <v>689</v>
@@ -11646,17 +11640,17 @@
         <v>690</v>
       </c>
       <c r="D266" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E266" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F266" t="s">
+        <v>704</v>
+      </c>
+      <c r="G266" t="s">
         <v>705</v>
       </c>
-      <c r="G266" t="s">
-        <v>706</v>
-      </c>
       <c r="H266" s="3" t="s">
         <v>53</v>
       </c>
@@ -11664,12 +11658,12 @@
         <v>1</v>
       </c>
       <c r="J266" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B267" t="s">
         <v>689</v>
@@ -11678,10 +11672,10 @@
         <v>690</v>
       </c>
       <c r="D267" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E267" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F267" t="s">
         <v>693</v>
@@ -11696,12 +11690,12 @@
         <v>1</v>
       </c>
       <c r="J267" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B268" t="s">
         <v>689</v>
@@ -11710,10 +11704,10 @@
         <v>690</v>
       </c>
       <c r="D268" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E268" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F268" t="s">
         <v>693</v>
@@ -11728,12 +11722,12 @@
         <v>1</v>
       </c>
       <c r="J268" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B269" t="s">
         <v>689</v>
@@ -11742,10 +11736,10 @@
         <v>690</v>
       </c>
       <c r="D269" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E269" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F269" t="s">
         <v>693</v>
@@ -11760,12 +11754,12 @@
         <v>1</v>
       </c>
       <c r="J269" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B270" t="s">
         <v>689</v>
@@ -11774,17 +11768,17 @@
         <v>690</v>
       </c>
       <c r="D270" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E270" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F270" t="s">
+        <v>704</v>
+      </c>
+      <c r="G270" t="s">
         <v>705</v>
       </c>
-      <c r="G270" t="s">
-        <v>706</v>
-      </c>
       <c r="H270" s="3" t="s">
         <v>53</v>
       </c>
@@ -11792,12 +11786,12 @@
         <v>1</v>
       </c>
       <c r="J270" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B271" t="s">
         <v>689</v>
@@ -11806,17 +11800,17 @@
         <v>690</v>
       </c>
       <c r="D271" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E271" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F271" t="s">
+        <v>704</v>
+      </c>
+      <c r="G271" t="s">
         <v>705</v>
       </c>
-      <c r="G271" t="s">
-        <v>706</v>
-      </c>
       <c r="H271" s="3" t="s">
         <v>53</v>
       </c>
@@ -11824,31 +11818,31 @@
         <v>1</v>
       </c>
       <c r="J271" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
+        <v>764</v>
+      </c>
+      <c r="B272" t="s">
         <v>765</v>
       </c>
-      <c r="B272" t="s">
+      <c r="C272" t="s">
         <v>766</v>
       </c>
-      <c r="C272" t="s">
+      <c r="D272" t="s">
         <v>767</v>
       </c>
-      <c r="D272" t="s">
+      <c r="E272" t="s">
         <v>768</v>
       </c>
-      <c r="E272" t="s">
+      <c r="F272" t="s">
         <v>769</v>
       </c>
-      <c r="F272" t="s">
+      <c r="G272" t="s">
         <v>770</v>
       </c>
-      <c r="G272" t="s">
-        <v>771</v>
-      </c>
       <c r="H272" s="3" t="s">
         <v>53</v>
       </c>
@@ -11856,31 +11850,31 @@
         <v>1</v>
       </c>
       <c r="J272" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>771</v>
+      </c>
+      <c r="B273" t="s">
+        <v>765</v>
+      </c>
+      <c r="C273" t="s">
+        <v>766</v>
+      </c>
+      <c r="D273" t="s">
+        <v>772</v>
+      </c>
+      <c r="E273" t="s">
         <v>773</v>
       </c>
-      <c r="B273" t="s">
-        <v>766</v>
-      </c>
-      <c r="C273" t="s">
-        <v>767</v>
-      </c>
-      <c r="D273" t="s">
-        <v>774</v>
-      </c>
-      <c r="E273" t="s">
-        <v>775</v>
-      </c>
       <c r="F273" t="s">
+        <v>769</v>
+      </c>
+      <c r="G273" t="s">
         <v>770</v>
       </c>
-      <c r="G273" t="s">
-        <v>771</v>
-      </c>
       <c r="H273" s="3" t="s">
         <v>53</v>
       </c>
@@ -11888,31 +11882,31 @@
         <v>1</v>
       </c>
       <c r="J273" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
+        <v>774</v>
+      </c>
+      <c r="B274" t="s">
+        <v>765</v>
+      </c>
+      <c r="C274" t="s">
+        <v>766</v>
+      </c>
+      <c r="D274" t="s">
+        <v>775</v>
+      </c>
+      <c r="E274" t="s">
         <v>776</v>
       </c>
-      <c r="B274" t="s">
-        <v>766</v>
-      </c>
-      <c r="C274" t="s">
-        <v>767</v>
-      </c>
-      <c r="D274" t="s">
-        <v>777</v>
-      </c>
-      <c r="E274" t="s">
-        <v>778</v>
-      </c>
       <c r="F274" t="s">
+        <v>769</v>
+      </c>
+      <c r="G274" t="s">
         <v>770</v>
       </c>
-      <c r="G274" t="s">
-        <v>771</v>
-      </c>
       <c r="H274" s="3" t="s">
         <v>53</v>
       </c>
@@ -11920,31 +11914,31 @@
         <v>1</v>
       </c>
       <c r="J274" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B275" t="s">
+        <v>765</v>
+      </c>
+      <c r="C275" t="s">
         <v>766</v>
       </c>
-      <c r="C275" t="s">
-        <v>767</v>
-      </c>
       <c r="D275" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="E275" t="s">
+        <v>768</v>
+      </c>
+      <c r="F275" t="s">
         <v>769</v>
       </c>
-      <c r="F275" t="s">
+      <c r="G275" t="s">
         <v>770</v>
       </c>
-      <c r="G275" t="s">
-        <v>771</v>
-      </c>
       <c r="H275" s="3" t="s">
         <v>53</v>
       </c>
@@ -11952,31 +11946,31 @@
         <v>1</v>
       </c>
       <c r="J275" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B276" t="s">
+        <v>765</v>
+      </c>
+      <c r="C276" t="s">
         <v>766</v>
       </c>
-      <c r="C276" t="s">
-        <v>767</v>
-      </c>
       <c r="D276" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="E276" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F276" t="s">
+        <v>769</v>
+      </c>
+      <c r="G276" t="s">
         <v>770</v>
       </c>
-      <c r="G276" t="s">
-        <v>771</v>
-      </c>
       <c r="H276" s="3" t="s">
         <v>53</v>
       </c>
@@ -11984,31 +11978,31 @@
         <v>1</v>
       </c>
       <c r="J276" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B277" t="s">
+        <v>765</v>
+      </c>
+      <c r="C277" t="s">
         <v>766</v>
       </c>
-      <c r="C277" t="s">
-        <v>767</v>
-      </c>
       <c r="D277" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="E277" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="F277" t="s">
+        <v>769</v>
+      </c>
+      <c r="G277" t="s">
         <v>770</v>
       </c>
-      <c r="G277" t="s">
-        <v>771</v>
-      </c>
       <c r="H277" s="3" t="s">
         <v>53</v>
       </c>
@@ -12016,31 +12010,31 @@
         <v>1</v>
       </c>
       <c r="J277" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B278" t="s">
+        <v>765</v>
+      </c>
+      <c r="C278" t="s">
         <v>766</v>
       </c>
-      <c r="C278" t="s">
-        <v>767</v>
-      </c>
       <c r="D278" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="E278" t="s">
+        <v>768</v>
+      </c>
+      <c r="F278" t="s">
         <v>769</v>
       </c>
-      <c r="F278" t="s">
+      <c r="G278" t="s">
         <v>770</v>
       </c>
-      <c r="G278" t="s">
-        <v>771</v>
-      </c>
       <c r="H278" s="3" t="s">
         <v>53</v>
       </c>
@@ -12048,31 +12042,31 @@
         <v>1</v>
       </c>
       <c r="J278" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B279" t="s">
+        <v>765</v>
+      </c>
+      <c r="C279" t="s">
         <v>766</v>
       </c>
-      <c r="C279" t="s">
-        <v>767</v>
-      </c>
       <c r="D279" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="E279" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F279" t="s">
+        <v>769</v>
+      </c>
+      <c r="G279" t="s">
         <v>770</v>
       </c>
-      <c r="G279" t="s">
-        <v>771</v>
-      </c>
       <c r="H279" s="3" t="s">
         <v>53</v>
       </c>
@@ -12080,31 +12074,31 @@
         <v>1</v>
       </c>
       <c r="J279" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B280" t="s">
+        <v>765</v>
+      </c>
+      <c r="C280" t="s">
         <v>766</v>
       </c>
-      <c r="C280" t="s">
-        <v>767</v>
-      </c>
       <c r="D280" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="E280" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="F280" t="s">
+        <v>769</v>
+      </c>
+      <c r="G280" t="s">
         <v>770</v>
       </c>
-      <c r="G280" t="s">
-        <v>771</v>
-      </c>
       <c r="H280" s="3" t="s">
         <v>53</v>
       </c>
@@ -12112,31 +12106,31 @@
         <v>1</v>
       </c>
       <c r="J280" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B281" t="s">
+        <v>765</v>
+      </c>
+      <c r="C281" t="s">
         <v>766</v>
       </c>
-      <c r="C281" t="s">
-        <v>767</v>
-      </c>
       <c r="D281" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="E281" t="s">
+        <v>768</v>
+      </c>
+      <c r="F281" t="s">
         <v>769</v>
       </c>
-      <c r="F281" t="s">
+      <c r="G281" t="s">
         <v>770</v>
       </c>
-      <c r="G281" t="s">
-        <v>771</v>
-      </c>
       <c r="H281" s="3" t="s">
         <v>53</v>
       </c>
@@ -12144,31 +12138,31 @@
         <v>1</v>
       </c>
       <c r="J281" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B282" t="s">
+        <v>765</v>
+      </c>
+      <c r="C282" t="s">
         <v>766</v>
       </c>
-      <c r="C282" t="s">
-        <v>767</v>
-      </c>
       <c r="D282" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E282" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F282" t="s">
+        <v>769</v>
+      </c>
+      <c r="G282" t="s">
         <v>770</v>
       </c>
-      <c r="G282" t="s">
-        <v>771</v>
-      </c>
       <c r="H282" s="3" t="s">
         <v>53</v>
       </c>
@@ -12176,31 +12170,31 @@
         <v>1</v>
       </c>
       <c r="J282" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B283" t="s">
+        <v>765</v>
+      </c>
+      <c r="C283" t="s">
         <v>766</v>
       </c>
-      <c r="C283" t="s">
-        <v>767</v>
-      </c>
       <c r="D283" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="E283" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="F283" t="s">
+        <v>769</v>
+      </c>
+      <c r="G283" t="s">
         <v>770</v>
       </c>
-      <c r="G283" t="s">
-        <v>771</v>
-      </c>
       <c r="H283" s="3" t="s">
         <v>53</v>
       </c>
@@ -12208,31 +12202,31 @@
         <v>1</v>
       </c>
       <c r="J283" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B284" t="s">
+        <v>765</v>
+      </c>
+      <c r="C284" t="s">
         <v>766</v>
       </c>
-      <c r="C284" t="s">
-        <v>767</v>
-      </c>
       <c r="D284" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="E284" t="s">
+        <v>768</v>
+      </c>
+      <c r="F284" t="s">
         <v>769</v>
       </c>
-      <c r="F284" t="s">
+      <c r="G284" t="s">
         <v>770</v>
       </c>
-      <c r="G284" t="s">
-        <v>771</v>
-      </c>
       <c r="H284" s="3" t="s">
         <v>53</v>
       </c>
@@ -12240,31 +12234,31 @@
         <v>1</v>
       </c>
       <c r="J284" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B285" t="s">
+        <v>765</v>
+      </c>
+      <c r="C285" t="s">
         <v>766</v>
       </c>
-      <c r="C285" t="s">
-        <v>767</v>
-      </c>
       <c r="D285" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="E285" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F285" t="s">
+        <v>769</v>
+      </c>
+      <c r="G285" t="s">
         <v>770</v>
       </c>
-      <c r="G285" t="s">
-        <v>771</v>
-      </c>
       <c r="H285" s="3" t="s">
         <v>53</v>
       </c>
@@ -12272,31 +12266,31 @@
         <v>1</v>
       </c>
       <c r="J285" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B286" t="s">
+        <v>765</v>
+      </c>
+      <c r="C286" t="s">
         <v>766</v>
       </c>
-      <c r="C286" t="s">
-        <v>767</v>
-      </c>
       <c r="D286" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="E286" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="F286" t="s">
+        <v>769</v>
+      </c>
+      <c r="G286" t="s">
         <v>770</v>
       </c>
-      <c r="G286" t="s">
-        <v>771</v>
-      </c>
       <c r="H286" s="3" t="s">
         <v>53</v>
       </c>
@@ -12304,31 +12298,31 @@
         <v>1</v>
       </c>
       <c r="J286" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B287" t="s">
+        <v>765</v>
+      </c>
+      <c r="C287" t="s">
         <v>766</v>
       </c>
-      <c r="C287" t="s">
-        <v>767</v>
-      </c>
       <c r="D287" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="E287" t="s">
+        <v>768</v>
+      </c>
+      <c r="F287" t="s">
         <v>769</v>
       </c>
-      <c r="F287" t="s">
+      <c r="G287" t="s">
         <v>770</v>
       </c>
-      <c r="G287" t="s">
-        <v>771</v>
-      </c>
       <c r="H287" s="3" t="s">
         <v>53</v>
       </c>
@@ -12336,31 +12330,31 @@
         <v>1</v>
       </c>
       <c r="J287" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B288" t="s">
+        <v>765</v>
+      </c>
+      <c r="C288" t="s">
         <v>766</v>
       </c>
-      <c r="C288" t="s">
-        <v>767</v>
-      </c>
       <c r="D288" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="E288" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F288" t="s">
+        <v>769</v>
+      </c>
+      <c r="G288" t="s">
         <v>770</v>
       </c>
-      <c r="G288" t="s">
-        <v>771</v>
-      </c>
       <c r="H288" s="3" t="s">
         <v>53</v>
       </c>
@@ -12368,31 +12362,31 @@
         <v>1</v>
       </c>
       <c r="J288" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B289" t="s">
+        <v>765</v>
+      </c>
+      <c r="C289" t="s">
         <v>766</v>
       </c>
-      <c r="C289" t="s">
-        <v>767</v>
-      </c>
       <c r="D289" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E289" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="F289" t="s">
+        <v>769</v>
+      </c>
+      <c r="G289" t="s">
         <v>770</v>
       </c>
-      <c r="G289" t="s">
-        <v>771</v>
-      </c>
       <c r="H289" s="3" t="s">
         <v>53</v>
       </c>
@@ -12400,31 +12394,31 @@
         <v>1</v>
       </c>
       <c r="J289" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B290" t="s">
+        <v>765</v>
+      </c>
+      <c r="C290" t="s">
         <v>766</v>
       </c>
-      <c r="C290" t="s">
-        <v>767</v>
-      </c>
       <c r="D290" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E290" t="s">
+        <v>768</v>
+      </c>
+      <c r="F290" t="s">
         <v>769</v>
       </c>
-      <c r="F290" t="s">
+      <c r="G290" t="s">
         <v>770</v>
       </c>
-      <c r="G290" t="s">
-        <v>771</v>
-      </c>
       <c r="H290" s="3" t="s">
         <v>53</v>
       </c>
@@ -12432,31 +12426,31 @@
         <v>1</v>
       </c>
       <c r="J290" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B291" t="s">
+        <v>765</v>
+      </c>
+      <c r="C291" t="s">
         <v>766</v>
       </c>
-      <c r="C291" t="s">
-        <v>767</v>
-      </c>
       <c r="D291" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="E291" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F291" t="s">
+        <v>769</v>
+      </c>
+      <c r="G291" t="s">
         <v>770</v>
       </c>
-      <c r="G291" t="s">
-        <v>771</v>
-      </c>
       <c r="H291" s="3" t="s">
         <v>53</v>
       </c>
@@ -12464,31 +12458,31 @@
         <v>1</v>
       </c>
       <c r="J291" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B292" t="s">
+        <v>765</v>
+      </c>
+      <c r="C292" t="s">
         <v>766</v>
       </c>
-      <c r="C292" t="s">
-        <v>767</v>
-      </c>
       <c r="D292" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="E292" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="F292" t="s">
+        <v>769</v>
+      </c>
+      <c r="G292" t="s">
         <v>770</v>
       </c>
-      <c r="G292" t="s">
-        <v>771</v>
-      </c>
       <c r="H292" s="3" t="s">
         <v>53</v>
       </c>
@@ -12496,31 +12490,31 @@
         <v>1</v>
       </c>
       <c r="J292" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B293" t="s">
+        <v>765</v>
+      </c>
+      <c r="C293" t="s">
         <v>766</v>
       </c>
-      <c r="C293" t="s">
-        <v>767</v>
-      </c>
       <c r="D293" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="E293" t="s">
+        <v>768</v>
+      </c>
+      <c r="F293" t="s">
         <v>769</v>
       </c>
-      <c r="F293" t="s">
+      <c r="G293" t="s">
         <v>770</v>
       </c>
-      <c r="G293" t="s">
-        <v>771</v>
-      </c>
       <c r="H293" s="3" t="s">
         <v>53</v>
       </c>
@@ -12528,31 +12522,31 @@
         <v>1</v>
       </c>
       <c r="J293" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B294" t="s">
+        <v>765</v>
+      </c>
+      <c r="C294" t="s">
         <v>766</v>
       </c>
-      <c r="C294" t="s">
-        <v>767</v>
-      </c>
       <c r="D294" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="E294" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F294" t="s">
+        <v>769</v>
+      </c>
+      <c r="G294" t="s">
         <v>770</v>
       </c>
-      <c r="G294" t="s">
-        <v>771</v>
-      </c>
       <c r="H294" s="3" t="s">
         <v>53</v>
       </c>
@@ -12560,31 +12554,31 @@
         <v>1</v>
       </c>
       <c r="J294" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B295" t="s">
+        <v>765</v>
+      </c>
+      <c r="C295" t="s">
         <v>766</v>
       </c>
-      <c r="C295" t="s">
-        <v>767</v>
-      </c>
       <c r="D295" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E295" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="F295" t="s">
+        <v>769</v>
+      </c>
+      <c r="G295" t="s">
         <v>770</v>
       </c>
-      <c r="G295" t="s">
-        <v>771</v>
-      </c>
       <c r="H295" s="3" t="s">
         <v>53</v>
       </c>
@@ -12592,31 +12586,31 @@
         <v>1</v>
       </c>
       <c r="J295" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B296" t="s">
+        <v>765</v>
+      </c>
+      <c r="C296" t="s">
         <v>766</v>
       </c>
-      <c r="C296" t="s">
-        <v>767</v>
-      </c>
       <c r="D296" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="E296" t="s">
+        <v>768</v>
+      </c>
+      <c r="F296" t="s">
         <v>769</v>
       </c>
-      <c r="F296" t="s">
+      <c r="G296" t="s">
         <v>770</v>
       </c>
-      <c r="G296" t="s">
-        <v>771</v>
-      </c>
       <c r="H296" s="3" t="s">
         <v>53</v>
       </c>
@@ -12624,31 +12618,31 @@
         <v>1</v>
       </c>
       <c r="J296" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B297" t="s">
+        <v>765</v>
+      </c>
+      <c r="C297" t="s">
         <v>766</v>
       </c>
-      <c r="C297" t="s">
-        <v>767</v>
-      </c>
       <c r="D297" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="E297" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F297" t="s">
+        <v>769</v>
+      </c>
+      <c r="G297" t="s">
         <v>770</v>
       </c>
-      <c r="G297" t="s">
-        <v>771</v>
-      </c>
       <c r="H297" s="3" t="s">
         <v>53</v>
       </c>
@@ -12656,31 +12650,31 @@
         <v>1</v>
       </c>
       <c r="J297" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B298" t="s">
+        <v>765</v>
+      </c>
+      <c r="C298" t="s">
         <v>766</v>
       </c>
-      <c r="C298" t="s">
-        <v>767</v>
-      </c>
       <c r="D298" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E298" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="F298" t="s">
+        <v>769</v>
+      </c>
+      <c r="G298" t="s">
         <v>770</v>
       </c>
-      <c r="G298" t="s">
-        <v>771</v>
-      </c>
       <c r="H298" s="3" t="s">
         <v>53</v>
       </c>
@@ -12688,31 +12682,31 @@
         <v>1</v>
       </c>
       <c r="J298" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B299" t="s">
+        <v>765</v>
+      </c>
+      <c r="C299" t="s">
         <v>766</v>
       </c>
-      <c r="C299" t="s">
-        <v>767</v>
-      </c>
       <c r="D299" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E299" t="s">
+        <v>768</v>
+      </c>
+      <c r="F299" t="s">
         <v>769</v>
       </c>
-      <c r="F299" t="s">
+      <c r="G299" t="s">
         <v>770</v>
       </c>
-      <c r="G299" t="s">
-        <v>771</v>
-      </c>
       <c r="H299" s="3" t="s">
         <v>53</v>
       </c>
@@ -12720,31 +12714,31 @@
         <v>1</v>
       </c>
       <c r="J299" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B300" t="s">
+        <v>765</v>
+      </c>
+      <c r="C300" t="s">
         <v>766</v>
       </c>
-      <c r="C300" t="s">
-        <v>767</v>
-      </c>
       <c r="D300" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E300" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F300" t="s">
+        <v>769</v>
+      </c>
+      <c r="G300" t="s">
         <v>770</v>
       </c>
-      <c r="G300" t="s">
-        <v>771</v>
-      </c>
       <c r="H300" s="3" t="s">
         <v>53</v>
       </c>
@@ -12752,31 +12746,31 @@
         <v>1</v>
       </c>
       <c r="J300" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B301" t="s">
+        <v>765</v>
+      </c>
+      <c r="C301" t="s">
         <v>766</v>
       </c>
-      <c r="C301" t="s">
-        <v>767</v>
-      </c>
       <c r="D301" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="E301" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="F301" t="s">
+        <v>769</v>
+      </c>
+      <c r="G301" t="s">
         <v>770</v>
       </c>
-      <c r="G301" t="s">
-        <v>771</v>
-      </c>
       <c r="H301" s="3" t="s">
         <v>53</v>
       </c>
@@ -12784,7 +12778,7 @@
         <v>1</v>
       </c>
       <c r="J301" t="s">
-        <v>772</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>

--- a/validation-tests/validation-test-report.xlsx
+++ b/validation-tests/validation-test-report.xlsx
@@ -62,7 +62,7 @@
     <t>EXECUTION TIME</t>
   </si>
   <si>
-    <t>0.01 seconds</t>
+    <t>0.02 seconds</t>
   </si>
   <si>
     <t>Automated validation engine</t>
@@ -71,7 +71,7 @@
     <t>EXECUTION TIMESTAMP</t>
   </si>
   <si>
-    <t>7/8/2026, 10:21:09 am</t>
+    <t>7/8/2026, 10:47:59 am</t>
   </si>
   <si>
     <t>CI/CD Pipeline Run</t>
@@ -176,7 +176,7 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.684Z</t>
+    <t>2026-08-07T05:17:59.309Z</t>
   </si>
   <si>
     <t>VAL-SEC-002</t>
@@ -188,7 +188,7 @@
     <t>email='user.name+tag@gmail.com'</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.685Z</t>
+    <t>2026-08-07T05:17:59.311Z</t>
   </si>
   <si>
     <t>VAL-SEC-003</t>
@@ -248,9 +248,6 @@
     <t>Email Format Syntax &amp; RFC 5322 Rule #8</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.686Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-009</t>
   </si>
   <si>
@@ -311,6 +308,9 @@
     <t>Email Format Syntax &amp; RFC 5322 Rule #18</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.312Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-019</t>
   </si>
   <si>
@@ -434,7 +434,7 @@
     <t>Evaluated: valid=true, score=4/4, feedback='Strong'</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.687Z</t>
+    <t>2026-08-07T05:17:59.313Z</t>
   </si>
   <si>
     <t>VAL-SEC-037</t>
@@ -488,9 +488,6 @@
     <t>password_sample_6 (length=18)</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.688Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-042</t>
   </si>
   <si>
@@ -545,6 +542,9 @@
     <t>password_sample_12 (length=18)</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.314Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-048</t>
   </si>
   <si>
@@ -689,9 +689,6 @@
     <t>password_sample_28 (length=18)</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.689Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-064</t>
   </si>
   <si>
@@ -776,7 +773,7 @@
     <t>Sanitizer: blocked_attack=true, sanitized_output='Goa OR 1=1'</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.690Z</t>
+    <t>2026-08-07T05:17:59.316Z</t>
   </si>
   <si>
     <t>VAL-SEC-072</t>
@@ -803,9 +800,6 @@
     <t>Sanitizer: blocked_attack=true, sanitized_output='Tokyo UNION SELECT null, username, password FROM users--'</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.691Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-074</t>
   </si>
   <si>
@@ -818,6 +812,9 @@
     <t>Sanitizer: blocked_attack=false, sanitized_output='Maldives'</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.317Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-075</t>
   </si>
   <si>
@@ -968,9 +965,6 @@
     <t>SQL Injection Attack Pattern Defense #26</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.692Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-097</t>
   </si>
   <si>
@@ -1136,6 +1130,9 @@
     <t>XSS Script Injection Neutralization #11</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.318Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-117</t>
   </si>
   <si>
@@ -1166,9 +1163,6 @@
     <t>XSS Script Injection Neutralization #16</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.693Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-122</t>
   </si>
   <si>
@@ -1217,6 +1211,9 @@
     <t>XSS Script Injection Neutralization #24</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.319Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-130</t>
   </si>
   <si>
@@ -1304,6 +1301,9 @@
     <t>Luhn verification: valid_card=false</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.320Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-142</t>
   </si>
   <si>
@@ -1376,9 +1376,6 @@
     <t>Payment Card Luhn Mod-10 Checksum #12</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.694Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-153</t>
   </si>
   <si>
@@ -1409,6 +1406,9 @@
     <t>Payment Card Luhn Mod-10 Checksum #17</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.321Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-158</t>
   </si>
   <si>
@@ -1517,6 +1517,9 @@
     <t>Payment Card Luhn Mod-10 Checksum #35</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.322Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-176</t>
   </si>
   <si>
@@ -1583,9 +1586,6 @@
     <t>checkIn='2026-09-07', checkOut='2026-09-10'</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.695Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-182</t>
   </si>
   <si>
@@ -1766,6 +1766,9 @@
     <t>Booking Stay Date Range Rule #29</t>
   </si>
   <si>
+    <t>2026-08-07T05:17:59.323Z</t>
+  </si>
+  <si>
     <t>VAL-SEC-205</t>
   </si>
   <si>
@@ -1802,9 +1805,6 @@
     <t>Booking Stay Date Range Rule #35</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.696Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-211</t>
   </si>
   <si>
@@ -2117,9 +2117,6 @@
     <t>mime_type='image/png', file_size=3.0MB</t>
   </si>
   <si>
-    <t>2026-08-07T04:51:09.697Z</t>
-  </si>
-  <si>
     <t>VAL-SEC-243</t>
   </si>
   <si>
@@ -2262,6 +2259,9 @@
   </si>
   <si>
     <t>File Upload MIME Whitelist &amp; 15MB Size Cap #21</t>
+  </si>
+  <si>
+    <t>2026-08-07T05:17:59.324Z</t>
   </si>
   <si>
     <t>VAL-SEC-262</t>
@@ -3446,12 +3446,12 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
         <v>47</v>
@@ -3460,7 +3460,7 @@
         <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
         <v>57</v>
@@ -3478,12 +3478,12 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
         <v>47</v>
@@ -3492,7 +3492,7 @@
         <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
         <v>61</v>
@@ -3510,12 +3510,12 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>47</v>
@@ -3524,7 +3524,7 @@
         <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
         <v>64</v>
@@ -3542,12 +3542,12 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
         <v>47</v>
@@ -3556,7 +3556,7 @@
         <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
         <v>69</v>
@@ -3574,12 +3574,12 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>47</v>
@@ -3588,7 +3588,7 @@
         <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
         <v>72</v>
@@ -3606,12 +3606,12 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
         <v>47</v>
@@ -3620,7 +3620,7 @@
         <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
         <v>75</v>
@@ -3638,12 +3638,12 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
         <v>47</v>
@@ -3652,7 +3652,7 @@
         <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
         <v>50</v>
@@ -3670,12 +3670,12 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s">
         <v>47</v>
@@ -3684,7 +3684,7 @@
         <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
         <v>57</v>
@@ -3702,12 +3702,12 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B18" t="s">
         <v>47</v>
@@ -3716,7 +3716,7 @@
         <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
         <v>61</v>
@@ -3734,12 +3734,12 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
@@ -3748,7 +3748,7 @@
         <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E19" t="s">
         <v>64</v>
@@ -3766,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -3798,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -3830,7 +3830,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -3862,7 +3862,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -3894,7 +3894,7 @@
         <v>1</v>
       </c>
       <c r="J23" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -3926,7 +3926,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -3958,7 +3958,7 @@
         <v>1</v>
       </c>
       <c r="J25" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -3990,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -4022,7 +4022,7 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -4054,7 +4054,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -4086,7 +4086,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -4118,7 +4118,7 @@
         <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -4150,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -4182,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -4214,7 +4214,7 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -4246,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -4278,7 +4278,7 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -4310,7 +4310,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -4502,12 +4502,12 @@
         <v>1</v>
       </c>
       <c r="J42" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" t="s">
         <v>134</v>
@@ -4516,10 +4516,10 @@
         <v>135</v>
       </c>
       <c r="D43" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" t="s">
         <v>160</v>
-      </c>
-      <c r="E43" t="s">
-        <v>161</v>
       </c>
       <c r="F43" t="s">
         <v>138</v>
@@ -4534,12 +4534,12 @@
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B44" t="s">
         <v>134</v>
@@ -4548,10 +4548,10 @@
         <v>135</v>
       </c>
       <c r="D44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" t="s">
         <v>163</v>
-      </c>
-      <c r="E44" t="s">
-        <v>164</v>
       </c>
       <c r="F44" t="s">
         <v>138</v>
@@ -4566,12 +4566,12 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" t="s">
         <v>134</v>
@@ -4580,10 +4580,10 @@
         <v>135</v>
       </c>
       <c r="D45" t="s">
+        <v>165</v>
+      </c>
+      <c r="E45" t="s">
         <v>166</v>
-      </c>
-      <c r="E45" t="s">
-        <v>167</v>
       </c>
       <c r="F45" t="s">
         <v>138</v>
@@ -4598,12 +4598,12 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" t="s">
         <v>134</v>
@@ -4612,10 +4612,10 @@
         <v>135</v>
       </c>
       <c r="D46" t="s">
+        <v>168</v>
+      </c>
+      <c r="E46" t="s">
         <v>169</v>
-      </c>
-      <c r="E46" t="s">
-        <v>170</v>
       </c>
       <c r="F46" t="s">
         <v>138</v>
@@ -4630,12 +4630,12 @@
         <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B47" t="s">
         <v>134</v>
@@ -4644,10 +4644,10 @@
         <v>135</v>
       </c>
       <c r="D47" t="s">
+        <v>171</v>
+      </c>
+      <c r="E47" t="s">
         <v>172</v>
-      </c>
-      <c r="E47" t="s">
-        <v>173</v>
       </c>
       <c r="F47" t="s">
         <v>138</v>
@@ -4662,12 +4662,12 @@
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B48" t="s">
         <v>134</v>
@@ -4676,10 +4676,10 @@
         <v>135</v>
       </c>
       <c r="D48" t="s">
+        <v>174</v>
+      </c>
+      <c r="E48" t="s">
         <v>175</v>
-      </c>
-      <c r="E48" t="s">
-        <v>176</v>
       </c>
       <c r="F48" t="s">
         <v>138</v>
@@ -4694,7 +4694,7 @@
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -4726,7 +4726,7 @@
         <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -4758,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="J50" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -4790,7 +4790,7 @@
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -4822,7 +4822,7 @@
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -4854,7 +4854,7 @@
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -4886,7 +4886,7 @@
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -4918,7 +4918,7 @@
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -4950,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -4982,7 +4982,7 @@
         <v>1</v>
       </c>
       <c r="J57" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -5014,7 +5014,7 @@
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -5046,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="J59" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -5078,7 +5078,7 @@
         <v>1</v>
       </c>
       <c r="J60" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -5110,7 +5110,7 @@
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -5142,7 +5142,7 @@
         <v>1</v>
       </c>
       <c r="J62" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -5174,7 +5174,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -5206,12 +5206,12 @@
         <v>1</v>
       </c>
       <c r="J64" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B65" t="s">
         <v>134</v>
@@ -5220,10 +5220,10 @@
         <v>135</v>
       </c>
       <c r="D65" t="s">
+        <v>226</v>
+      </c>
+      <c r="E65" t="s">
         <v>227</v>
-      </c>
-      <c r="E65" t="s">
-        <v>228</v>
       </c>
       <c r="F65" t="s">
         <v>138</v>
@@ -5238,12 +5238,12 @@
         <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B66" t="s">
         <v>134</v>
@@ -5252,10 +5252,10 @@
         <v>135</v>
       </c>
       <c r="D66" t="s">
+        <v>229</v>
+      </c>
+      <c r="E66" t="s">
         <v>230</v>
-      </c>
-      <c r="E66" t="s">
-        <v>231</v>
       </c>
       <c r="F66" t="s">
         <v>138</v>
@@ -5270,12 +5270,12 @@
         <v>1</v>
       </c>
       <c r="J66" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B67" t="s">
         <v>134</v>
@@ -5284,10 +5284,10 @@
         <v>135</v>
       </c>
       <c r="D67" t="s">
+        <v>232</v>
+      </c>
+      <c r="E67" t="s">
         <v>233</v>
-      </c>
-      <c r="E67" t="s">
-        <v>234</v>
       </c>
       <c r="F67" t="s">
         <v>138</v>
@@ -5302,12 +5302,12 @@
         <v>1</v>
       </c>
       <c r="J67" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B68" t="s">
         <v>134</v>
@@ -5316,10 +5316,10 @@
         <v>135</v>
       </c>
       <c r="D68" t="s">
+        <v>235</v>
+      </c>
+      <c r="E68" t="s">
         <v>236</v>
-      </c>
-      <c r="E68" t="s">
-        <v>237</v>
       </c>
       <c r="F68" t="s">
         <v>138</v>
@@ -5334,12 +5334,12 @@
         <v>1</v>
       </c>
       <c r="J68" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B69" t="s">
         <v>134</v>
@@ -5348,10 +5348,10 @@
         <v>135</v>
       </c>
       <c r="D69" t="s">
+        <v>238</v>
+      </c>
+      <c r="E69" t="s">
         <v>239</v>
-      </c>
-      <c r="E69" t="s">
-        <v>240</v>
       </c>
       <c r="F69" t="s">
         <v>138</v>
@@ -5366,12 +5366,12 @@
         <v>1</v>
       </c>
       <c r="J69" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B70" t="s">
         <v>134</v>
@@ -5380,10 +5380,10 @@
         <v>135</v>
       </c>
       <c r="D70" t="s">
+        <v>241</v>
+      </c>
+      <c r="E70" t="s">
         <v>242</v>
-      </c>
-      <c r="E70" t="s">
-        <v>243</v>
       </c>
       <c r="F70" t="s">
         <v>138</v>
@@ -5398,12 +5398,12 @@
         <v>1</v>
       </c>
       <c r="J70" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B71" t="s">
         <v>134</v>
@@ -5412,10 +5412,10 @@
         <v>135</v>
       </c>
       <c r="D71" t="s">
+        <v>244</v>
+      </c>
+      <c r="E71" t="s">
         <v>245</v>
-      </c>
-      <c r="E71" t="s">
-        <v>246</v>
       </c>
       <c r="F71" t="s">
         <v>138</v>
@@ -5430,63 +5430,63 @@
         <v>1</v>
       </c>
       <c r="J71" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>246</v>
+      </c>
+      <c r="B72" t="s">
         <v>247</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>248</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>249</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>250</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>251</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>252</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I72">
+        <v>2</v>
+      </c>
+      <c r="J72" t="s">
         <v>253</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I72">
-        <v>1</v>
-      </c>
-      <c r="J72" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>254</v>
+      </c>
+      <c r="B73" t="s">
+        <v>247</v>
+      </c>
+      <c r="C73" t="s">
+        <v>248</v>
+      </c>
+      <c r="D73" t="s">
         <v>255</v>
       </c>
-      <c r="B73" t="s">
-        <v>248</v>
-      </c>
-      <c r="C73" t="s">
-        <v>249</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>256</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
+        <v>251</v>
+      </c>
+      <c r="G73" t="s">
         <v>257</v>
       </c>
-      <c r="F73" t="s">
-        <v>252</v>
-      </c>
-      <c r="G73" t="s">
-        <v>258</v>
-      </c>
       <c r="H73" s="3" t="s">
         <v>53</v>
       </c>
@@ -5494,31 +5494,31 @@
         <v>1</v>
       </c>
       <c r="J73" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>258</v>
+      </c>
+      <c r="B74" t="s">
+        <v>247</v>
+      </c>
+      <c r="C74" t="s">
+        <v>248</v>
+      </c>
+      <c r="D74" t="s">
         <v>259</v>
       </c>
-      <c r="B74" t="s">
-        <v>248</v>
-      </c>
-      <c r="C74" t="s">
-        <v>249</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>260</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
+        <v>251</v>
+      </c>
+      <c r="G74" t="s">
         <v>261</v>
       </c>
-      <c r="F74" t="s">
-        <v>252</v>
-      </c>
-      <c r="G74" t="s">
-        <v>262</v>
-      </c>
       <c r="H74" s="3" t="s">
         <v>53</v>
       </c>
@@ -5526,63 +5526,63 @@
         <v>1</v>
       </c>
       <c r="J74" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>262</v>
+      </c>
+      <c r="B75" t="s">
+        <v>247</v>
+      </c>
+      <c r="C75" t="s">
+        <v>248</v>
+      </c>
+      <c r="D75" t="s">
+        <v>263</v>
+      </c>
+      <c r="E75" t="s">
         <v>264</v>
       </c>
-      <c r="B75" t="s">
-        <v>248</v>
-      </c>
-      <c r="C75" t="s">
-        <v>249</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="F75" t="s">
+        <v>251</v>
+      </c>
+      <c r="G75" t="s">
         <v>265</v>
       </c>
-      <c r="E75" t="s">
+      <c r="H75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+      <c r="J75" t="s">
         <v>266</v>
-      </c>
-      <c r="F75" t="s">
-        <v>252</v>
-      </c>
-      <c r="G75" t="s">
-        <v>267</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I75">
-        <v>1</v>
-      </c>
-      <c r="J75" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>267</v>
+      </c>
+      <c r="B76" t="s">
+        <v>247</v>
+      </c>
+      <c r="C76" t="s">
+        <v>248</v>
+      </c>
+      <c r="D76" t="s">
         <v>268</v>
       </c>
-      <c r="B76" t="s">
-        <v>248</v>
-      </c>
-      <c r="C76" t="s">
-        <v>249</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>269</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
+        <v>251</v>
+      </c>
+      <c r="G76" t="s">
         <v>270</v>
       </c>
-      <c r="F76" t="s">
-        <v>252</v>
-      </c>
-      <c r="G76" t="s">
-        <v>271</v>
-      </c>
       <c r="H76" s="3" t="s">
         <v>53</v>
       </c>
@@ -5590,31 +5590,31 @@
         <v>1</v>
       </c>
       <c r="J76" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>271</v>
+      </c>
+      <c r="B77" t="s">
+        <v>247</v>
+      </c>
+      <c r="C77" t="s">
+        <v>248</v>
+      </c>
+      <c r="D77" t="s">
         <v>272</v>
       </c>
-      <c r="B77" t="s">
-        <v>248</v>
-      </c>
-      <c r="C77" t="s">
-        <v>249</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>273</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
+        <v>251</v>
+      </c>
+      <c r="G77" t="s">
         <v>274</v>
       </c>
-      <c r="F77" t="s">
-        <v>252</v>
-      </c>
-      <c r="G77" t="s">
-        <v>275</v>
-      </c>
       <c r="H77" s="3" t="s">
         <v>53</v>
       </c>
@@ -5622,31 +5622,31 @@
         <v>1</v>
       </c>
       <c r="J77" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>275</v>
+      </c>
+      <c r="B78" t="s">
+        <v>247</v>
+      </c>
+      <c r="C78" t="s">
+        <v>248</v>
+      </c>
+      <c r="D78" t="s">
         <v>276</v>
       </c>
-      <c r="B78" t="s">
-        <v>248</v>
-      </c>
-      <c r="C78" t="s">
-        <v>249</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>277</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
+        <v>251</v>
+      </c>
+      <c r="G78" t="s">
         <v>278</v>
       </c>
-      <c r="F78" t="s">
-        <v>252</v>
-      </c>
-      <c r="G78" t="s">
-        <v>279</v>
-      </c>
       <c r="H78" s="3" t="s">
         <v>53</v>
       </c>
@@ -5654,31 +5654,31 @@
         <v>1</v>
       </c>
       <c r="J78" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>279</v>
+      </c>
+      <c r="B79" t="s">
+        <v>247</v>
+      </c>
+      <c r="C79" t="s">
+        <v>248</v>
+      </c>
+      <c r="D79" t="s">
         <v>280</v>
       </c>
-      <c r="B79" t="s">
-        <v>248</v>
-      </c>
-      <c r="C79" t="s">
-        <v>249</v>
-      </c>
-      <c r="D79" t="s">
-        <v>281</v>
-      </c>
       <c r="E79" t="s">
+        <v>250</v>
+      </c>
+      <c r="F79" t="s">
         <v>251</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>252</v>
       </c>
-      <c r="G79" t="s">
-        <v>253</v>
-      </c>
       <c r="H79" s="3" t="s">
         <v>53</v>
       </c>
@@ -5686,31 +5686,31 @@
         <v>1</v>
       </c>
       <c r="J79" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>281</v>
+      </c>
+      <c r="B80" t="s">
+        <v>247</v>
+      </c>
+      <c r="C80" t="s">
+        <v>248</v>
+      </c>
+      <c r="D80" t="s">
         <v>282</v>
       </c>
-      <c r="B80" t="s">
-        <v>248</v>
-      </c>
-      <c r="C80" t="s">
-        <v>249</v>
-      </c>
-      <c r="D80" t="s">
-        <v>283</v>
-      </c>
       <c r="E80" t="s">
+        <v>256</v>
+      </c>
+      <c r="F80" t="s">
+        <v>251</v>
+      </c>
+      <c r="G80" t="s">
         <v>257</v>
       </c>
-      <c r="F80" t="s">
-        <v>252</v>
-      </c>
-      <c r="G80" t="s">
-        <v>258</v>
-      </c>
       <c r="H80" s="3" t="s">
         <v>53</v>
       </c>
@@ -5718,31 +5718,31 @@
         <v>1</v>
       </c>
       <c r="J80" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>283</v>
+      </c>
+      <c r="B81" t="s">
+        <v>247</v>
+      </c>
+      <c r="C81" t="s">
+        <v>248</v>
+      </c>
+      <c r="D81" t="s">
         <v>284</v>
       </c>
-      <c r="B81" t="s">
-        <v>248</v>
-      </c>
-      <c r="C81" t="s">
-        <v>249</v>
-      </c>
-      <c r="D81" t="s">
-        <v>285</v>
-      </c>
       <c r="E81" t="s">
+        <v>260</v>
+      </c>
+      <c r="F81" t="s">
+        <v>251</v>
+      </c>
+      <c r="G81" t="s">
         <v>261</v>
       </c>
-      <c r="F81" t="s">
-        <v>252</v>
-      </c>
-      <c r="G81" t="s">
-        <v>262</v>
-      </c>
       <c r="H81" s="3" t="s">
         <v>53</v>
       </c>
@@ -5750,63 +5750,63 @@
         <v>1</v>
       </c>
       <c r="J81" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>285</v>
+      </c>
+      <c r="B82" t="s">
+        <v>247</v>
+      </c>
+      <c r="C82" t="s">
+        <v>248</v>
+      </c>
+      <c r="D82" t="s">
         <v>286</v>
       </c>
-      <c r="B82" t="s">
-        <v>248</v>
-      </c>
-      <c r="C82" t="s">
-        <v>249</v>
-      </c>
-      <c r="D82" t="s">
-        <v>287</v>
-      </c>
       <c r="E82" t="s">
+        <v>264</v>
+      </c>
+      <c r="F82" t="s">
+        <v>251</v>
+      </c>
+      <c r="G82" t="s">
+        <v>265</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82" t="s">
         <v>266</v>
-      </c>
-      <c r="F82" t="s">
-        <v>252</v>
-      </c>
-      <c r="G82" t="s">
-        <v>267</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I82">
-        <v>1</v>
-      </c>
-      <c r="J82" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>287</v>
+      </c>
+      <c r="B83" t="s">
+        <v>247</v>
+      </c>
+      <c r="C83" t="s">
+        <v>248</v>
+      </c>
+      <c r="D83" t="s">
         <v>288</v>
       </c>
-      <c r="B83" t="s">
-        <v>248</v>
-      </c>
-      <c r="C83" t="s">
-        <v>249</v>
-      </c>
-      <c r="D83" t="s">
-        <v>289</v>
-      </c>
       <c r="E83" t="s">
+        <v>269</v>
+      </c>
+      <c r="F83" t="s">
+        <v>251</v>
+      </c>
+      <c r="G83" t="s">
         <v>270</v>
       </c>
-      <c r="F83" t="s">
-        <v>252</v>
-      </c>
-      <c r="G83" t="s">
-        <v>271</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>53</v>
       </c>
@@ -5814,31 +5814,31 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>289</v>
+      </c>
+      <c r="B84" t="s">
+        <v>247</v>
+      </c>
+      <c r="C84" t="s">
+        <v>248</v>
+      </c>
+      <c r="D84" t="s">
         <v>290</v>
       </c>
-      <c r="B84" t="s">
-        <v>248</v>
-      </c>
-      <c r="C84" t="s">
-        <v>249</v>
-      </c>
-      <c r="D84" t="s">
-        <v>291</v>
-      </c>
       <c r="E84" t="s">
+        <v>273</v>
+      </c>
+      <c r="F84" t="s">
+        <v>251</v>
+      </c>
+      <c r="G84" t="s">
         <v>274</v>
       </c>
-      <c r="F84" t="s">
-        <v>252</v>
-      </c>
-      <c r="G84" t="s">
-        <v>275</v>
-      </c>
       <c r="H84" s="3" t="s">
         <v>53</v>
       </c>
@@ -5846,31 +5846,31 @@
         <v>1</v>
       </c>
       <c r="J84" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>291</v>
+      </c>
+      <c r="B85" t="s">
+        <v>247</v>
+      </c>
+      <c r="C85" t="s">
+        <v>248</v>
+      </c>
+      <c r="D85" t="s">
         <v>292</v>
       </c>
-      <c r="B85" t="s">
-        <v>248</v>
-      </c>
-      <c r="C85" t="s">
-        <v>249</v>
-      </c>
-      <c r="D85" t="s">
-        <v>293</v>
-      </c>
       <c r="E85" t="s">
+        <v>277</v>
+      </c>
+      <c r="F85" t="s">
+        <v>251</v>
+      </c>
+      <c r="G85" t="s">
         <v>278</v>
       </c>
-      <c r="F85" t="s">
-        <v>252</v>
-      </c>
-      <c r="G85" t="s">
-        <v>279</v>
-      </c>
       <c r="H85" s="3" t="s">
         <v>53</v>
       </c>
@@ -5878,31 +5878,31 @@
         <v>1</v>
       </c>
       <c r="J85" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>293</v>
+      </c>
+      <c r="B86" t="s">
+        <v>247</v>
+      </c>
+      <c r="C86" t="s">
+        <v>248</v>
+      </c>
+      <c r="D86" t="s">
         <v>294</v>
       </c>
-      <c r="B86" t="s">
-        <v>248</v>
-      </c>
-      <c r="C86" t="s">
-        <v>249</v>
-      </c>
-      <c r="D86" t="s">
-        <v>295</v>
-      </c>
       <c r="E86" t="s">
+        <v>250</v>
+      </c>
+      <c r="F86" t="s">
         <v>251</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>252</v>
       </c>
-      <c r="G86" t="s">
-        <v>253</v>
-      </c>
       <c r="H86" s="3" t="s">
         <v>53</v>
       </c>
@@ -5910,31 +5910,31 @@
         <v>1</v>
       </c>
       <c r="J86" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>295</v>
+      </c>
+      <c r="B87" t="s">
+        <v>247</v>
+      </c>
+      <c r="C87" t="s">
+        <v>248</v>
+      </c>
+      <c r="D87" t="s">
         <v>296</v>
       </c>
-      <c r="B87" t="s">
-        <v>248</v>
-      </c>
-      <c r="C87" t="s">
-        <v>249</v>
-      </c>
-      <c r="D87" t="s">
-        <v>297</v>
-      </c>
       <c r="E87" t="s">
+        <v>256</v>
+      </c>
+      <c r="F87" t="s">
+        <v>251</v>
+      </c>
+      <c r="G87" t="s">
         <v>257</v>
       </c>
-      <c r="F87" t="s">
-        <v>252</v>
-      </c>
-      <c r="G87" t="s">
-        <v>258</v>
-      </c>
       <c r="H87" s="3" t="s">
         <v>53</v>
       </c>
@@ -5942,31 +5942,31 @@
         <v>1</v>
       </c>
       <c r="J87" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>297</v>
+      </c>
+      <c r="B88" t="s">
+        <v>247</v>
+      </c>
+      <c r="C88" t="s">
+        <v>248</v>
+      </c>
+      <c r="D88" t="s">
         <v>298</v>
       </c>
-      <c r="B88" t="s">
-        <v>248</v>
-      </c>
-      <c r="C88" t="s">
-        <v>249</v>
-      </c>
-      <c r="D88" t="s">
-        <v>299</v>
-      </c>
       <c r="E88" t="s">
+        <v>260</v>
+      </c>
+      <c r="F88" t="s">
+        <v>251</v>
+      </c>
+      <c r="G88" t="s">
         <v>261</v>
       </c>
-      <c r="F88" t="s">
-        <v>252</v>
-      </c>
-      <c r="G88" t="s">
-        <v>262</v>
-      </c>
       <c r="H88" s="3" t="s">
         <v>53</v>
       </c>
@@ -5974,63 +5974,63 @@
         <v>1</v>
       </c>
       <c r="J88" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>299</v>
+      </c>
+      <c r="B89" t="s">
+        <v>247</v>
+      </c>
+      <c r="C89" t="s">
+        <v>248</v>
+      </c>
+      <c r="D89" t="s">
         <v>300</v>
       </c>
-      <c r="B89" t="s">
-        <v>248</v>
-      </c>
-      <c r="C89" t="s">
-        <v>249</v>
-      </c>
-      <c r="D89" t="s">
-        <v>301</v>
-      </c>
       <c r="E89" t="s">
+        <v>264</v>
+      </c>
+      <c r="F89" t="s">
+        <v>251</v>
+      </c>
+      <c r="G89" t="s">
+        <v>265</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89" t="s">
         <v>266</v>
-      </c>
-      <c r="F89" t="s">
-        <v>252</v>
-      </c>
-      <c r="G89" t="s">
-        <v>267</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I89">
-        <v>1</v>
-      </c>
-      <c r="J89" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>301</v>
+      </c>
+      <c r="B90" t="s">
+        <v>247</v>
+      </c>
+      <c r="C90" t="s">
+        <v>248</v>
+      </c>
+      <c r="D90" t="s">
         <v>302</v>
       </c>
-      <c r="B90" t="s">
-        <v>248</v>
-      </c>
-      <c r="C90" t="s">
-        <v>249</v>
-      </c>
-      <c r="D90" t="s">
-        <v>303</v>
-      </c>
       <c r="E90" t="s">
+        <v>269</v>
+      </c>
+      <c r="F90" t="s">
+        <v>251</v>
+      </c>
+      <c r="G90" t="s">
         <v>270</v>
       </c>
-      <c r="F90" t="s">
-        <v>252</v>
-      </c>
-      <c r="G90" t="s">
-        <v>271</v>
-      </c>
       <c r="H90" s="3" t="s">
         <v>53</v>
       </c>
@@ -6038,31 +6038,31 @@
         <v>1</v>
       </c>
       <c r="J90" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>303</v>
+      </c>
+      <c r="B91" t="s">
+        <v>247</v>
+      </c>
+      <c r="C91" t="s">
+        <v>248</v>
+      </c>
+      <c r="D91" t="s">
         <v>304</v>
       </c>
-      <c r="B91" t="s">
-        <v>248</v>
-      </c>
-      <c r="C91" t="s">
-        <v>249</v>
-      </c>
-      <c r="D91" t="s">
-        <v>305</v>
-      </c>
       <c r="E91" t="s">
+        <v>273</v>
+      </c>
+      <c r="F91" t="s">
+        <v>251</v>
+      </c>
+      <c r="G91" t="s">
         <v>274</v>
       </c>
-      <c r="F91" t="s">
-        <v>252</v>
-      </c>
-      <c r="G91" t="s">
-        <v>275</v>
-      </c>
       <c r="H91" s="3" t="s">
         <v>53</v>
       </c>
@@ -6070,31 +6070,31 @@
         <v>1</v>
       </c>
       <c r="J91" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>305</v>
+      </c>
+      <c r="B92" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" t="s">
+        <v>248</v>
+      </c>
+      <c r="D92" t="s">
         <v>306</v>
       </c>
-      <c r="B92" t="s">
-        <v>248</v>
-      </c>
-      <c r="C92" t="s">
-        <v>249</v>
-      </c>
-      <c r="D92" t="s">
-        <v>307</v>
-      </c>
       <c r="E92" t="s">
+        <v>277</v>
+      </c>
+      <c r="F92" t="s">
+        <v>251</v>
+      </c>
+      <c r="G92" t="s">
         <v>278</v>
       </c>
-      <c r="F92" t="s">
-        <v>252</v>
-      </c>
-      <c r="G92" t="s">
-        <v>279</v>
-      </c>
       <c r="H92" s="3" t="s">
         <v>53</v>
       </c>
@@ -6102,31 +6102,31 @@
         <v>1</v>
       </c>
       <c r="J92" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>307</v>
+      </c>
+      <c r="B93" t="s">
+        <v>247</v>
+      </c>
+      <c r="C93" t="s">
+        <v>248</v>
+      </c>
+      <c r="D93" t="s">
         <v>308</v>
       </c>
-      <c r="B93" t="s">
-        <v>248</v>
-      </c>
-      <c r="C93" t="s">
-        <v>249</v>
-      </c>
-      <c r="D93" t="s">
-        <v>309</v>
-      </c>
       <c r="E93" t="s">
+        <v>250</v>
+      </c>
+      <c r="F93" t="s">
         <v>251</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>252</v>
       </c>
-      <c r="G93" t="s">
-        <v>253</v>
-      </c>
       <c r="H93" s="3" t="s">
         <v>53</v>
       </c>
@@ -6134,31 +6134,31 @@
         <v>1</v>
       </c>
       <c r="J93" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>309</v>
+      </c>
+      <c r="B94" t="s">
+        <v>247</v>
+      </c>
+      <c r="C94" t="s">
+        <v>248</v>
+      </c>
+      <c r="D94" t="s">
         <v>310</v>
       </c>
-      <c r="B94" t="s">
-        <v>248</v>
-      </c>
-      <c r="C94" t="s">
-        <v>249</v>
-      </c>
-      <c r="D94" t="s">
-        <v>311</v>
-      </c>
       <c r="E94" t="s">
+        <v>256</v>
+      </c>
+      <c r="F94" t="s">
+        <v>251</v>
+      </c>
+      <c r="G94" t="s">
         <v>257</v>
       </c>
-      <c r="F94" t="s">
-        <v>252</v>
-      </c>
-      <c r="G94" t="s">
-        <v>258</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>53</v>
       </c>
@@ -6166,31 +6166,31 @@
         <v>1</v>
       </c>
       <c r="J94" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>311</v>
+      </c>
+      <c r="B95" t="s">
+        <v>247</v>
+      </c>
+      <c r="C95" t="s">
+        <v>248</v>
+      </c>
+      <c r="D95" t="s">
         <v>312</v>
       </c>
-      <c r="B95" t="s">
-        <v>248</v>
-      </c>
-      <c r="C95" t="s">
-        <v>249</v>
-      </c>
-      <c r="D95" t="s">
-        <v>313</v>
-      </c>
       <c r="E95" t="s">
+        <v>260</v>
+      </c>
+      <c r="F95" t="s">
+        <v>251</v>
+      </c>
+      <c r="G95" t="s">
         <v>261</v>
       </c>
-      <c r="F95" t="s">
-        <v>252</v>
-      </c>
-      <c r="G95" t="s">
-        <v>262</v>
-      </c>
       <c r="H95" s="3" t="s">
         <v>53</v>
       </c>
@@ -6198,63 +6198,63 @@
         <v>1</v>
       </c>
       <c r="J95" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>313</v>
+      </c>
+      <c r="B96" t="s">
+        <v>247</v>
+      </c>
+      <c r="C96" t="s">
+        <v>248</v>
+      </c>
+      <c r="D96" t="s">
         <v>314</v>
       </c>
-      <c r="B96" t="s">
-        <v>248</v>
-      </c>
-      <c r="C96" t="s">
-        <v>249</v>
-      </c>
-      <c r="D96" t="s">
-        <v>315</v>
-      </c>
       <c r="E96" t="s">
+        <v>264</v>
+      </c>
+      <c r="F96" t="s">
+        <v>251</v>
+      </c>
+      <c r="G96" t="s">
+        <v>265</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96" t="s">
         <v>266</v>
-      </c>
-      <c r="F96" t="s">
-        <v>252</v>
-      </c>
-      <c r="G96" t="s">
-        <v>267</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I96">
-        <v>1</v>
-      </c>
-      <c r="J96" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>315</v>
+      </c>
+      <c r="B97" t="s">
+        <v>247</v>
+      </c>
+      <c r="C97" t="s">
+        <v>248</v>
+      </c>
+      <c r="D97" t="s">
         <v>316</v>
       </c>
-      <c r="B97" t="s">
-        <v>248</v>
-      </c>
-      <c r="C97" t="s">
-        <v>249</v>
-      </c>
-      <c r="D97" t="s">
-        <v>317</v>
-      </c>
       <c r="E97" t="s">
+        <v>269</v>
+      </c>
+      <c r="F97" t="s">
+        <v>251</v>
+      </c>
+      <c r="G97" t="s">
         <v>270</v>
       </c>
-      <c r="F97" t="s">
-        <v>252</v>
-      </c>
-      <c r="G97" t="s">
-        <v>271</v>
-      </c>
       <c r="H97" s="3" t="s">
         <v>53</v>
       </c>
@@ -6262,31 +6262,31 @@
         <v>1</v>
       </c>
       <c r="J97" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B98" t="s">
+        <v>247</v>
+      </c>
+      <c r="C98" t="s">
         <v>248</v>
       </c>
-      <c r="C98" t="s">
-        <v>249</v>
-      </c>
       <c r="D98" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E98" t="s">
+        <v>273</v>
+      </c>
+      <c r="F98" t="s">
+        <v>251</v>
+      </c>
+      <c r="G98" t="s">
         <v>274</v>
       </c>
-      <c r="F98" t="s">
-        <v>252</v>
-      </c>
-      <c r="G98" t="s">
-        <v>275</v>
-      </c>
       <c r="H98" s="3" t="s">
         <v>53</v>
       </c>
@@ -6294,31 +6294,31 @@
         <v>1</v>
       </c>
       <c r="J98" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B99" t="s">
+        <v>247</v>
+      </c>
+      <c r="C99" t="s">
         <v>248</v>
       </c>
-      <c r="C99" t="s">
-        <v>249</v>
-      </c>
       <c r="D99" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E99" t="s">
+        <v>277</v>
+      </c>
+      <c r="F99" t="s">
+        <v>251</v>
+      </c>
+      <c r="G99" t="s">
         <v>278</v>
       </c>
-      <c r="F99" t="s">
-        <v>252</v>
-      </c>
-      <c r="G99" t="s">
-        <v>279</v>
-      </c>
       <c r="H99" s="3" t="s">
         <v>53</v>
       </c>
@@ -6326,31 +6326,31 @@
         <v>1</v>
       </c>
       <c r="J99" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B100" t="s">
+        <v>247</v>
+      </c>
+      <c r="C100" t="s">
         <v>248</v>
       </c>
-      <c r="C100" t="s">
-        <v>249</v>
-      </c>
       <c r="D100" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E100" t="s">
+        <v>250</v>
+      </c>
+      <c r="F100" t="s">
         <v>251</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>252</v>
       </c>
-      <c r="G100" t="s">
-        <v>253</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>53</v>
       </c>
@@ -6358,31 +6358,31 @@
         <v>1</v>
       </c>
       <c r="J100" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B101" t="s">
+        <v>247</v>
+      </c>
+      <c r="C101" t="s">
         <v>248</v>
       </c>
-      <c r="C101" t="s">
-        <v>249</v>
-      </c>
       <c r="D101" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E101" t="s">
+        <v>256</v>
+      </c>
+      <c r="F101" t="s">
+        <v>251</v>
+      </c>
+      <c r="G101" t="s">
         <v>257</v>
       </c>
-      <c r="F101" t="s">
-        <v>252</v>
-      </c>
-      <c r="G101" t="s">
-        <v>258</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>53</v>
       </c>
@@ -6390,31 +6390,31 @@
         <v>1</v>
       </c>
       <c r="J101" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B102" t="s">
+        <v>247</v>
+      </c>
+      <c r="C102" t="s">
         <v>248</v>
       </c>
-      <c r="C102" t="s">
-        <v>249</v>
-      </c>
       <c r="D102" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E102" t="s">
+        <v>260</v>
+      </c>
+      <c r="F102" t="s">
+        <v>251</v>
+      </c>
+      <c r="G102" t="s">
         <v>261</v>
       </c>
-      <c r="F102" t="s">
-        <v>252</v>
-      </c>
-      <c r="G102" t="s">
-        <v>262</v>
-      </c>
       <c r="H102" s="3" t="s">
         <v>53</v>
       </c>
@@ -6422,63 +6422,63 @@
         <v>1</v>
       </c>
       <c r="J102" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B103" t="s">
+        <v>247</v>
+      </c>
+      <c r="C103" t="s">
         <v>248</v>
       </c>
-      <c r="C103" t="s">
-        <v>249</v>
-      </c>
       <c r="D103" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E103" t="s">
+        <v>264</v>
+      </c>
+      <c r="F103" t="s">
+        <v>251</v>
+      </c>
+      <c r="G103" t="s">
+        <v>265</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+      <c r="J103" t="s">
         <v>266</v>
-      </c>
-      <c r="F103" t="s">
-        <v>252</v>
-      </c>
-      <c r="G103" t="s">
-        <v>267</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I103">
-        <v>1</v>
-      </c>
-      <c r="J103" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B104" t="s">
+        <v>247</v>
+      </c>
+      <c r="C104" t="s">
         <v>248</v>
       </c>
-      <c r="C104" t="s">
-        <v>249</v>
-      </c>
       <c r="D104" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E104" t="s">
+        <v>269</v>
+      </c>
+      <c r="F104" t="s">
+        <v>251</v>
+      </c>
+      <c r="G104" t="s">
         <v>270</v>
       </c>
-      <c r="F104" t="s">
-        <v>252</v>
-      </c>
-      <c r="G104" t="s">
-        <v>271</v>
-      </c>
       <c r="H104" s="3" t="s">
         <v>53</v>
       </c>
@@ -6486,31 +6486,31 @@
         <v>1</v>
       </c>
       <c r="J104" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B105" t="s">
+        <v>247</v>
+      </c>
+      <c r="C105" t="s">
         <v>248</v>
       </c>
-      <c r="C105" t="s">
-        <v>249</v>
-      </c>
       <c r="D105" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E105" t="s">
+        <v>273</v>
+      </c>
+      <c r="F105" t="s">
+        <v>251</v>
+      </c>
+      <c r="G105" t="s">
         <v>274</v>
       </c>
-      <c r="F105" t="s">
-        <v>252</v>
-      </c>
-      <c r="G105" t="s">
-        <v>275</v>
-      </c>
       <c r="H105" s="3" t="s">
         <v>53</v>
       </c>
@@ -6518,31 +6518,31 @@
         <v>1</v>
       </c>
       <c r="J105" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B106" t="s">
+        <v>247</v>
+      </c>
+      <c r="C106" t="s">
         <v>248</v>
       </c>
-      <c r="C106" t="s">
-        <v>249</v>
-      </c>
       <c r="D106" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E106" t="s">
+        <v>277</v>
+      </c>
+      <c r="F106" t="s">
+        <v>251</v>
+      </c>
+      <c r="G106" t="s">
         <v>278</v>
       </c>
-      <c r="F106" t="s">
-        <v>252</v>
-      </c>
-      <c r="G106" t="s">
-        <v>279</v>
-      </c>
       <c r="H106" s="3" t="s">
         <v>53</v>
       </c>
@@ -6550,31 +6550,31 @@
         <v>1</v>
       </c>
       <c r="J106" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>335</v>
+      </c>
+      <c r="B107" t="s">
+        <v>336</v>
+      </c>
+      <c r="C107" t="s">
         <v>337</v>
       </c>
-      <c r="B107" t="s">
+      <c r="D107" t="s">
         <v>338</v>
       </c>
-      <c r="C107" t="s">
+      <c r="E107" t="s">
         <v>339</v>
       </c>
-      <c r="D107" t="s">
+      <c r="F107" t="s">
         <v>340</v>
       </c>
-      <c r="E107" t="s">
+      <c r="G107" t="s">
         <v>341</v>
       </c>
-      <c r="F107" t="s">
-        <v>342</v>
-      </c>
-      <c r="G107" t="s">
-        <v>343</v>
-      </c>
       <c r="H107" s="3" t="s">
         <v>53</v>
       </c>
@@ -6582,31 +6582,31 @@
         <v>1</v>
       </c>
       <c r="J107" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>342</v>
+      </c>
+      <c r="B108" t="s">
+        <v>336</v>
+      </c>
+      <c r="C108" t="s">
+        <v>337</v>
+      </c>
+      <c r="D108" t="s">
+        <v>343</v>
+      </c>
+      <c r="E108" t="s">
         <v>344</v>
       </c>
-      <c r="B108" t="s">
-        <v>338</v>
-      </c>
-      <c r="C108" t="s">
-        <v>339</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="F108" t="s">
+        <v>340</v>
+      </c>
+      <c r="G108" t="s">
         <v>345</v>
       </c>
-      <c r="E108" t="s">
-        <v>346</v>
-      </c>
-      <c r="F108" t="s">
-        <v>342</v>
-      </c>
-      <c r="G108" t="s">
-        <v>347</v>
-      </c>
       <c r="H108" s="3" t="s">
         <v>53</v>
       </c>
@@ -6614,31 +6614,31 @@
         <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>346</v>
+      </c>
+      <c r="B109" t="s">
+        <v>336</v>
+      </c>
+      <c r="C109" t="s">
+        <v>337</v>
+      </c>
+      <c r="D109" t="s">
+        <v>347</v>
+      </c>
+      <c r="E109" t="s">
         <v>348</v>
       </c>
-      <c r="B109" t="s">
-        <v>338</v>
-      </c>
-      <c r="C109" t="s">
-        <v>339</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="F109" t="s">
+        <v>340</v>
+      </c>
+      <c r="G109" t="s">
         <v>349</v>
       </c>
-      <c r="E109" t="s">
-        <v>350</v>
-      </c>
-      <c r="F109" t="s">
-        <v>342</v>
-      </c>
-      <c r="G109" t="s">
-        <v>351</v>
-      </c>
       <c r="H109" s="3" t="s">
         <v>53</v>
       </c>
@@ -6646,31 +6646,31 @@
         <v>1</v>
       </c>
       <c r="J109" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>350</v>
+      </c>
+      <c r="B110" t="s">
+        <v>336</v>
+      </c>
+      <c r="C110" t="s">
+        <v>337</v>
+      </c>
+      <c r="D110" t="s">
+        <v>351</v>
+      </c>
+      <c r="E110" t="s">
         <v>352</v>
       </c>
-      <c r="B110" t="s">
-        <v>338</v>
-      </c>
-      <c r="C110" t="s">
-        <v>339</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="F110" t="s">
+        <v>340</v>
+      </c>
+      <c r="G110" t="s">
         <v>353</v>
       </c>
-      <c r="E110" t="s">
-        <v>354</v>
-      </c>
-      <c r="F110" t="s">
-        <v>342</v>
-      </c>
-      <c r="G110" t="s">
-        <v>355</v>
-      </c>
       <c r="H110" s="3" t="s">
         <v>53</v>
       </c>
@@ -6678,31 +6678,31 @@
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>354</v>
+      </c>
+      <c r="B111" t="s">
+        <v>336</v>
+      </c>
+      <c r="C111" t="s">
+        <v>337</v>
+      </c>
+      <c r="D111" t="s">
+        <v>355</v>
+      </c>
+      <c r="E111" t="s">
         <v>356</v>
       </c>
-      <c r="B111" t="s">
-        <v>338</v>
-      </c>
-      <c r="C111" t="s">
-        <v>339</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="F111" t="s">
+        <v>340</v>
+      </c>
+      <c r="G111" t="s">
         <v>357</v>
       </c>
-      <c r="E111" t="s">
-        <v>358</v>
-      </c>
-      <c r="F111" t="s">
-        <v>342</v>
-      </c>
-      <c r="G111" t="s">
-        <v>359</v>
-      </c>
       <c r="H111" s="3" t="s">
         <v>53</v>
       </c>
@@ -6710,31 +6710,31 @@
         <v>1</v>
       </c>
       <c r="J111" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>358</v>
+      </c>
+      <c r="B112" t="s">
+        <v>336</v>
+      </c>
+      <c r="C112" t="s">
+        <v>337</v>
+      </c>
+      <c r="D112" t="s">
+        <v>359</v>
+      </c>
+      <c r="E112" t="s">
         <v>360</v>
       </c>
-      <c r="B112" t="s">
-        <v>338</v>
-      </c>
-      <c r="C112" t="s">
-        <v>339</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="F112" t="s">
+        <v>340</v>
+      </c>
+      <c r="G112" t="s">
         <v>361</v>
       </c>
-      <c r="E112" t="s">
-        <v>362</v>
-      </c>
-      <c r="F112" t="s">
-        <v>342</v>
-      </c>
-      <c r="G112" t="s">
-        <v>363</v>
-      </c>
       <c r="H112" s="3" t="s">
         <v>53</v>
       </c>
@@ -6742,31 +6742,31 @@
         <v>1</v>
       </c>
       <c r="J112" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B113" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C113" t="s">
+        <v>337</v>
+      </c>
+      <c r="D113" t="s">
+        <v>363</v>
+      </c>
+      <c r="E113" t="s">
         <v>339</v>
       </c>
-      <c r="D113" t="s">
-        <v>365</v>
-      </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
+        <v>340</v>
+      </c>
+      <c r="G113" t="s">
         <v>341</v>
       </c>
-      <c r="F113" t="s">
-        <v>342</v>
-      </c>
-      <c r="G113" t="s">
-        <v>343</v>
-      </c>
       <c r="H113" s="3" t="s">
         <v>53</v>
       </c>
@@ -6774,30 +6774,30 @@
         <v>1</v>
       </c>
       <c r="J113" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B114" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C114" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D114" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E114" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F114" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G114" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>53</v>
@@ -6806,30 +6806,30 @@
         <v>1</v>
       </c>
       <c r="J114" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B115" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C115" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D115" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E115" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F115" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G115" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>53</v>
@@ -6838,30 +6838,30 @@
         <v>1</v>
       </c>
       <c r="J115" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B116" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C116" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D116" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E116" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F116" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G116" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>53</v>
@@ -6870,62 +6870,62 @@
         <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>370</v>
+      </c>
+      <c r="B117" t="s">
+        <v>336</v>
+      </c>
+      <c r="C117" t="s">
+        <v>337</v>
+      </c>
+      <c r="D117" t="s">
+        <v>371</v>
+      </c>
+      <c r="E117" t="s">
+        <v>356</v>
+      </c>
+      <c r="F117" t="s">
+        <v>340</v>
+      </c>
+      <c r="G117" t="s">
+        <v>357</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117" t="s">
         <v>372</v>
-      </c>
-      <c r="B117" t="s">
-        <v>338</v>
-      </c>
-      <c r="C117" t="s">
-        <v>339</v>
-      </c>
-      <c r="D117" t="s">
-        <v>373</v>
-      </c>
-      <c r="E117" t="s">
-        <v>358</v>
-      </c>
-      <c r="F117" t="s">
-        <v>342</v>
-      </c>
-      <c r="G117" t="s">
-        <v>359</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I117">
-        <v>1</v>
-      </c>
-      <c r="J117" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>373</v>
+      </c>
+      <c r="B118" t="s">
+        <v>336</v>
+      </c>
+      <c r="C118" t="s">
+        <v>337</v>
+      </c>
+      <c r="D118" t="s">
         <v>374</v>
       </c>
-      <c r="B118" t="s">
-        <v>338</v>
-      </c>
-      <c r="C118" t="s">
-        <v>339</v>
-      </c>
-      <c r="D118" t="s">
-        <v>375</v>
-      </c>
       <c r="E118" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F118" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G118" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>53</v>
@@ -6934,31 +6934,31 @@
         <v>1</v>
       </c>
       <c r="J118" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>375</v>
+      </c>
+      <c r="B119" t="s">
+        <v>336</v>
+      </c>
+      <c r="C119" t="s">
+        <v>337</v>
+      </c>
+      <c r="D119" t="s">
         <v>376</v>
       </c>
-      <c r="B119" t="s">
-        <v>338</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="E119" t="s">
         <v>339</v>
       </c>
-      <c r="D119" t="s">
-        <v>377</v>
-      </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
+        <v>340</v>
+      </c>
+      <c r="G119" t="s">
         <v>341</v>
       </c>
-      <c r="F119" t="s">
-        <v>342</v>
-      </c>
-      <c r="G119" t="s">
-        <v>343</v>
-      </c>
       <c r="H119" s="3" t="s">
         <v>53</v>
       </c>
@@ -6966,30 +6966,30 @@
         <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>377</v>
+      </c>
+      <c r="B120" t="s">
+        <v>336</v>
+      </c>
+      <c r="C120" t="s">
+        <v>337</v>
+      </c>
+      <c r="D120" t="s">
         <v>378</v>
       </c>
-      <c r="B120" t="s">
-        <v>338</v>
-      </c>
-      <c r="C120" t="s">
-        <v>339</v>
-      </c>
-      <c r="D120" t="s">
-        <v>379</v>
-      </c>
       <c r="E120" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F120" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G120" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>53</v>
@@ -6998,30 +6998,30 @@
         <v>1</v>
       </c>
       <c r="J120" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>379</v>
+      </c>
+      <c r="B121" t="s">
+        <v>336</v>
+      </c>
+      <c r="C121" t="s">
+        <v>337</v>
+      </c>
+      <c r="D121" t="s">
         <v>380</v>
       </c>
-      <c r="B121" t="s">
-        <v>338</v>
-      </c>
-      <c r="C121" t="s">
-        <v>339</v>
-      </c>
-      <c r="D121" t="s">
-        <v>381</v>
-      </c>
       <c r="E121" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F121" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G121" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>53</v>
@@ -7030,30 +7030,30 @@
         <v>1</v>
       </c>
       <c r="J121" t="s">
-        <v>318</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>381</v>
+      </c>
+      <c r="B122" t="s">
+        <v>336</v>
+      </c>
+      <c r="C122" t="s">
+        <v>337</v>
+      </c>
+      <c r="D122" t="s">
         <v>382</v>
       </c>
-      <c r="B122" t="s">
-        <v>338</v>
-      </c>
-      <c r="C122" t="s">
-        <v>339</v>
-      </c>
-      <c r="D122" t="s">
-        <v>383</v>
-      </c>
       <c r="E122" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F122" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G122" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>53</v>
@@ -7062,30 +7062,30 @@
         <v>1</v>
       </c>
       <c r="J122" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B123" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C123" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E123" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F123" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G123" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H123" s="3" t="s">
         <v>53</v>
@@ -7094,30 +7094,30 @@
         <v>1</v>
       </c>
       <c r="J123" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B124" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C124" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D124" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E124" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F124" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G124" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H124" s="3" t="s">
         <v>53</v>
@@ -7126,31 +7126,31 @@
         <v>1</v>
       </c>
       <c r="J124" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B125" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C125" t="s">
+        <v>337</v>
+      </c>
+      <c r="D125" t="s">
+        <v>388</v>
+      </c>
+      <c r="E125" t="s">
         <v>339</v>
       </c>
-      <c r="D125" t="s">
-        <v>390</v>
-      </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
+        <v>340</v>
+      </c>
+      <c r="G125" t="s">
         <v>341</v>
       </c>
-      <c r="F125" t="s">
-        <v>342</v>
-      </c>
-      <c r="G125" t="s">
-        <v>343</v>
-      </c>
       <c r="H125" s="3" t="s">
         <v>53</v>
       </c>
@@ -7158,30 +7158,30 @@
         <v>1</v>
       </c>
       <c r="J125" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B126" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C126" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D126" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E126" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F126" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G126" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>53</v>
@@ -7190,30 +7190,30 @@
         <v>1</v>
       </c>
       <c r="J126" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B127" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C127" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E127" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F127" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G127" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H127" s="3" t="s">
         <v>53</v>
@@ -7222,30 +7222,30 @@
         <v>1</v>
       </c>
       <c r="J127" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B128" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C128" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D128" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E128" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F128" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G128" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H128" s="3" t="s">
         <v>53</v>
@@ -7254,30 +7254,30 @@
         <v>1</v>
       </c>
       <c r="J128" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B129" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C129" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D129" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E129" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F129" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G129" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H129" s="3" t="s">
         <v>53</v>
@@ -7286,63 +7286,63 @@
         <v>1</v>
       </c>
       <c r="J129" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>397</v>
+      </c>
+      <c r="B130" t="s">
+        <v>336</v>
+      </c>
+      <c r="C130" t="s">
+        <v>337</v>
+      </c>
+      <c r="D130" t="s">
+        <v>398</v>
+      </c>
+      <c r="E130" t="s">
+        <v>360</v>
+      </c>
+      <c r="F130" t="s">
+        <v>340</v>
+      </c>
+      <c r="G130" t="s">
+        <v>361</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="J130" t="s">
         <v>399</v>
-      </c>
-      <c r="B130" t="s">
-        <v>338</v>
-      </c>
-      <c r="C130" t="s">
-        <v>339</v>
-      </c>
-      <c r="D130" t="s">
-        <v>400</v>
-      </c>
-      <c r="E130" t="s">
-        <v>362</v>
-      </c>
-      <c r="F130" t="s">
-        <v>342</v>
-      </c>
-      <c r="G130" t="s">
-        <v>363</v>
-      </c>
-      <c r="H130" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I130">
-        <v>1</v>
-      </c>
-      <c r="J130" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>400</v>
+      </c>
+      <c r="B131" t="s">
+        <v>336</v>
+      </c>
+      <c r="C131" t="s">
+        <v>337</v>
+      </c>
+      <c r="D131" t="s">
         <v>401</v>
       </c>
-      <c r="B131" t="s">
-        <v>338</v>
-      </c>
-      <c r="C131" t="s">
+      <c r="E131" t="s">
         <v>339</v>
       </c>
-      <c r="D131" t="s">
-        <v>402</v>
-      </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G131" t="s">
         <v>341</v>
       </c>
-      <c r="F131" t="s">
-        <v>342</v>
-      </c>
-      <c r="G131" t="s">
-        <v>343</v>
-      </c>
       <c r="H131" s="3" t="s">
         <v>53</v>
       </c>
@@ -7350,30 +7350,30 @@
         <v>1</v>
       </c>
       <c r="J131" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>402</v>
+      </c>
+      <c r="B132" t="s">
+        <v>336</v>
+      </c>
+      <c r="C132" t="s">
+        <v>337</v>
+      </c>
+      <c r="D132" t="s">
         <v>403</v>
       </c>
-      <c r="B132" t="s">
-        <v>338</v>
-      </c>
-      <c r="C132" t="s">
-        <v>339</v>
-      </c>
-      <c r="D132" t="s">
-        <v>404</v>
-      </c>
       <c r="E132" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F132" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G132" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H132" s="3" t="s">
         <v>53</v>
@@ -7382,30 +7382,30 @@
         <v>1</v>
       </c>
       <c r="J132" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>404</v>
+      </c>
+      <c r="B133" t="s">
+        <v>336</v>
+      </c>
+      <c r="C133" t="s">
+        <v>337</v>
+      </c>
+      <c r="D133" t="s">
         <v>405</v>
       </c>
-      <c r="B133" t="s">
-        <v>338</v>
-      </c>
-      <c r="C133" t="s">
-        <v>339</v>
-      </c>
-      <c r="D133" t="s">
-        <v>406</v>
-      </c>
       <c r="E133" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F133" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G133" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H133" s="3" t="s">
         <v>53</v>
@@ -7414,30 +7414,30 @@
         <v>1</v>
       </c>
       <c r="J133" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>406</v>
+      </c>
+      <c r="B134" t="s">
+        <v>336</v>
+      </c>
+      <c r="C134" t="s">
+        <v>337</v>
+      </c>
+      <c r="D134" t="s">
         <v>407</v>
       </c>
-      <c r="B134" t="s">
-        <v>338</v>
-      </c>
-      <c r="C134" t="s">
-        <v>339</v>
-      </c>
-      <c r="D134" t="s">
-        <v>408</v>
-      </c>
       <c r="E134" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F134" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G134" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H134" s="3" t="s">
         <v>53</v>
@@ -7446,30 +7446,30 @@
         <v>1</v>
       </c>
       <c r="J134" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>408</v>
+      </c>
+      <c r="B135" t="s">
+        <v>336</v>
+      </c>
+      <c r="C135" t="s">
+        <v>337</v>
+      </c>
+      <c r="D135" t="s">
         <v>409</v>
       </c>
-      <c r="B135" t="s">
-        <v>338</v>
-      </c>
-      <c r="C135" t="s">
-        <v>339</v>
-      </c>
-      <c r="D135" t="s">
-        <v>410</v>
-      </c>
       <c r="E135" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F135" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G135" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H135" s="3" t="s">
         <v>53</v>
@@ -7478,30 +7478,30 @@
         <v>1</v>
       </c>
       <c r="J135" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>410</v>
+      </c>
+      <c r="B136" t="s">
+        <v>336</v>
+      </c>
+      <c r="C136" t="s">
+        <v>337</v>
+      </c>
+      <c r="D136" t="s">
         <v>411</v>
       </c>
-      <c r="B136" t="s">
-        <v>338</v>
-      </c>
-      <c r="C136" t="s">
-        <v>339</v>
-      </c>
-      <c r="D136" t="s">
-        <v>412</v>
-      </c>
       <c r="E136" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F136" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G136" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H136" s="3" t="s">
         <v>53</v>
@@ -7510,31 +7510,31 @@
         <v>1</v>
       </c>
       <c r="J136" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>412</v>
+      </c>
+      <c r="B137" t="s">
+        <v>336</v>
+      </c>
+      <c r="C137" t="s">
+        <v>337</v>
+      </c>
+      <c r="D137" t="s">
         <v>413</v>
       </c>
-      <c r="B137" t="s">
-        <v>338</v>
-      </c>
-      <c r="C137" t="s">
+      <c r="E137" t="s">
         <v>339</v>
       </c>
-      <c r="D137" t="s">
-        <v>414</v>
-      </c>
-      <c r="E137" t="s">
+      <c r="F137" t="s">
+        <v>340</v>
+      </c>
+      <c r="G137" t="s">
         <v>341</v>
       </c>
-      <c r="F137" t="s">
-        <v>342</v>
-      </c>
-      <c r="G137" t="s">
-        <v>343</v>
-      </c>
       <c r="H137" s="3" t="s">
         <v>53</v>
       </c>
@@ -7542,30 +7542,30 @@
         <v>1</v>
       </c>
       <c r="J137" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>414</v>
+      </c>
+      <c r="B138" t="s">
+        <v>336</v>
+      </c>
+      <c r="C138" t="s">
+        <v>337</v>
+      </c>
+      <c r="D138" t="s">
         <v>415</v>
       </c>
-      <c r="B138" t="s">
-        <v>338</v>
-      </c>
-      <c r="C138" t="s">
-        <v>339</v>
-      </c>
-      <c r="D138" t="s">
-        <v>416</v>
-      </c>
       <c r="E138" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F138" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G138" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H138" s="3" t="s">
         <v>53</v>
@@ -7574,30 +7574,30 @@
         <v>1</v>
       </c>
       <c r="J138" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>416</v>
+      </c>
+      <c r="B139" t="s">
+        <v>336</v>
+      </c>
+      <c r="C139" t="s">
+        <v>337</v>
+      </c>
+      <c r="D139" t="s">
         <v>417</v>
       </c>
-      <c r="B139" t="s">
-        <v>338</v>
-      </c>
-      <c r="C139" t="s">
-        <v>339</v>
-      </c>
-      <c r="D139" t="s">
-        <v>418</v>
-      </c>
       <c r="E139" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F139" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G139" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H139" s="3" t="s">
         <v>53</v>
@@ -7606,30 +7606,30 @@
         <v>1</v>
       </c>
       <c r="J139" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>418</v>
+      </c>
+      <c r="B140" t="s">
+        <v>336</v>
+      </c>
+      <c r="C140" t="s">
+        <v>337</v>
+      </c>
+      <c r="D140" t="s">
         <v>419</v>
       </c>
-      <c r="B140" t="s">
-        <v>338</v>
-      </c>
-      <c r="C140" t="s">
-        <v>339</v>
-      </c>
-      <c r="D140" t="s">
-        <v>420</v>
-      </c>
       <c r="E140" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F140" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G140" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H140" s="3" t="s">
         <v>53</v>
@@ -7638,30 +7638,30 @@
         <v>1</v>
       </c>
       <c r="J140" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>420</v>
+      </c>
+      <c r="B141" t="s">
+        <v>336</v>
+      </c>
+      <c r="C141" t="s">
+        <v>337</v>
+      </c>
+      <c r="D141" t="s">
         <v>421</v>
       </c>
-      <c r="B141" t="s">
-        <v>338</v>
-      </c>
-      <c r="C141" t="s">
-        <v>339</v>
-      </c>
-      <c r="D141" t="s">
-        <v>422</v>
-      </c>
       <c r="E141" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F141" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G141" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H141" s="3" t="s">
         <v>53</v>
@@ -7670,39 +7670,39 @@
         <v>1</v>
       </c>
       <c r="J141" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>422</v>
+      </c>
+      <c r="B142" t="s">
         <v>423</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" t="s">
         <v>424</v>
       </c>
-      <c r="C142" t="s">
+      <c r="D142" t="s">
         <v>425</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>426</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>427</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>428</v>
       </c>
-      <c r="G142" t="s">
+      <c r="H142" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I142">
+        <v>1</v>
+      </c>
+      <c r="J142" t="s">
         <v>429</v>
-      </c>
-      <c r="H142" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I142">
-        <v>1</v>
-      </c>
-      <c r="J142" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -7710,10 +7710,10 @@
         <v>430</v>
       </c>
       <c r="B143" t="s">
+        <v>423</v>
+      </c>
+      <c r="C143" t="s">
         <v>424</v>
-      </c>
-      <c r="C143" t="s">
-        <v>425</v>
       </c>
       <c r="D143" t="s">
         <v>431</v>
@@ -7722,7 +7722,7 @@
         <v>432</v>
       </c>
       <c r="F143" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G143" t="s">
         <v>433</v>
@@ -7734,7 +7734,7 @@
         <v>1</v>
       </c>
       <c r="J143" t="s">
-        <v>384</v>
+        <v>429</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -7742,31 +7742,31 @@
         <v>434</v>
       </c>
       <c r="B144" t="s">
+        <v>423</v>
+      </c>
+      <c r="C144" t="s">
         <v>424</v>
-      </c>
-      <c r="C144" t="s">
-        <v>425</v>
       </c>
       <c r="D144" t="s">
         <v>435</v>
       </c>
       <c r="E144" t="s">
+        <v>426</v>
+      </c>
+      <c r="F144" t="s">
         <v>427</v>
       </c>
-      <c r="F144" t="s">
+      <c r="G144" t="s">
         <v>428</v>
       </c>
-      <c r="G144" t="s">
+      <c r="H144" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I144">
+        <v>1</v>
+      </c>
+      <c r="J144" t="s">
         <v>429</v>
-      </c>
-      <c r="H144" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I144">
-        <v>1</v>
-      </c>
-      <c r="J144" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -7774,10 +7774,10 @@
         <v>436</v>
       </c>
       <c r="B145" t="s">
+        <v>423</v>
+      </c>
+      <c r="C145" t="s">
         <v>424</v>
-      </c>
-      <c r="C145" t="s">
-        <v>425</v>
       </c>
       <c r="D145" t="s">
         <v>437</v>
@@ -7786,7 +7786,7 @@
         <v>432</v>
       </c>
       <c r="F145" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G145" t="s">
         <v>433</v>
@@ -7798,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="J145" t="s">
-        <v>384</v>
+        <v>429</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -7806,31 +7806,31 @@
         <v>438</v>
       </c>
       <c r="B146" t="s">
+        <v>423</v>
+      </c>
+      <c r="C146" t="s">
         <v>424</v>
-      </c>
-      <c r="C146" t="s">
-        <v>425</v>
       </c>
       <c r="D146" t="s">
         <v>439</v>
       </c>
       <c r="E146" t="s">
+        <v>426</v>
+      </c>
+      <c r="F146" t="s">
         <v>427</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>428</v>
       </c>
-      <c r="G146" t="s">
+      <c r="H146" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I146">
+        <v>1</v>
+      </c>
+      <c r="J146" t="s">
         <v>429</v>
-      </c>
-      <c r="H146" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I146">
-        <v>1</v>
-      </c>
-      <c r="J146" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -7838,10 +7838,10 @@
         <v>440</v>
       </c>
       <c r="B147" t="s">
+        <v>423</v>
+      </c>
+      <c r="C147" t="s">
         <v>424</v>
-      </c>
-      <c r="C147" t="s">
-        <v>425</v>
       </c>
       <c r="D147" t="s">
         <v>441</v>
@@ -7850,7 +7850,7 @@
         <v>432</v>
       </c>
       <c r="F147" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G147" t="s">
         <v>433</v>
@@ -7862,7 +7862,7 @@
         <v>1</v>
       </c>
       <c r="J147" t="s">
-        <v>384</v>
+        <v>429</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -7870,31 +7870,31 @@
         <v>442</v>
       </c>
       <c r="B148" t="s">
+        <v>423</v>
+      </c>
+      <c r="C148" t="s">
         <v>424</v>
-      </c>
-      <c r="C148" t="s">
-        <v>425</v>
       </c>
       <c r="D148" t="s">
         <v>443</v>
       </c>
       <c r="E148" t="s">
+        <v>426</v>
+      </c>
+      <c r="F148" t="s">
         <v>427</v>
       </c>
-      <c r="F148" t="s">
+      <c r="G148" t="s">
         <v>428</v>
       </c>
-      <c r="G148" t="s">
+      <c r="H148" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I148">
+        <v>1</v>
+      </c>
+      <c r="J148" t="s">
         <v>429</v>
-      </c>
-      <c r="H148" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I148">
-        <v>1</v>
-      </c>
-      <c r="J148" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -7902,10 +7902,10 @@
         <v>444</v>
       </c>
       <c r="B149" t="s">
+        <v>423</v>
+      </c>
+      <c r="C149" t="s">
         <v>424</v>
-      </c>
-      <c r="C149" t="s">
-        <v>425</v>
       </c>
       <c r="D149" t="s">
         <v>445</v>
@@ -7914,7 +7914,7 @@
         <v>432</v>
       </c>
       <c r="F149" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G149" t="s">
         <v>433</v>
@@ -7926,7 +7926,7 @@
         <v>1</v>
       </c>
       <c r="J149" t="s">
-        <v>384</v>
+        <v>429</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -7934,31 +7934,31 @@
         <v>446</v>
       </c>
       <c r="B150" t="s">
+        <v>423</v>
+      </c>
+      <c r="C150" t="s">
         <v>424</v>
-      </c>
-      <c r="C150" t="s">
-        <v>425</v>
       </c>
       <c r="D150" t="s">
         <v>447</v>
       </c>
       <c r="E150" t="s">
+        <v>426</v>
+      </c>
+      <c r="F150" t="s">
         <v>427</v>
       </c>
-      <c r="F150" t="s">
+      <c r="G150" t="s">
         <v>428</v>
       </c>
-      <c r="G150" t="s">
+      <c r="H150" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I150">
+        <v>1</v>
+      </c>
+      <c r="J150" t="s">
         <v>429</v>
-      </c>
-      <c r="H150" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I150">
-        <v>1</v>
-      </c>
-      <c r="J150" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -7966,10 +7966,10 @@
         <v>448</v>
       </c>
       <c r="B151" t="s">
+        <v>423</v>
+      </c>
+      <c r="C151" t="s">
         <v>424</v>
-      </c>
-      <c r="C151" t="s">
-        <v>425</v>
       </c>
       <c r="D151" t="s">
         <v>449</v>
@@ -7978,7 +7978,7 @@
         <v>432</v>
       </c>
       <c r="F151" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G151" t="s">
         <v>433</v>
@@ -7990,7 +7990,7 @@
         <v>1</v>
       </c>
       <c r="J151" t="s">
-        <v>384</v>
+        <v>429</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -7998,31 +7998,31 @@
         <v>450</v>
       </c>
       <c r="B152" t="s">
+        <v>423</v>
+      </c>
+      <c r="C152" t="s">
         <v>424</v>
-      </c>
-      <c r="C152" t="s">
-        <v>425</v>
       </c>
       <c r="D152" t="s">
         <v>451</v>
       </c>
       <c r="E152" t="s">
+        <v>426</v>
+      </c>
+      <c r="F152" t="s">
         <v>427</v>
       </c>
-      <c r="F152" t="s">
+      <c r="G152" t="s">
         <v>428</v>
       </c>
-      <c r="G152" t="s">
+      <c r="H152" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+      <c r="J152" t="s">
         <v>429</v>
-      </c>
-      <c r="H152" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I152">
-        <v>1</v>
-      </c>
-      <c r="J152" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -8030,10 +8030,10 @@
         <v>452</v>
       </c>
       <c r="B153" t="s">
+        <v>423</v>
+      </c>
+      <c r="C153" t="s">
         <v>424</v>
-      </c>
-      <c r="C153" t="s">
-        <v>425</v>
       </c>
       <c r="D153" t="s">
         <v>453</v>
@@ -8042,7 +8042,7 @@
         <v>432</v>
       </c>
       <c r="F153" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G153" t="s">
         <v>433</v>
@@ -8054,59 +8054,59 @@
         <v>1</v>
       </c>
       <c r="J153" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>454</v>
+      </c>
+      <c r="B154" t="s">
+        <v>423</v>
+      </c>
+      <c r="C154" t="s">
+        <v>424</v>
+      </c>
+      <c r="D154" t="s">
         <v>455</v>
       </c>
-      <c r="B154" t="s">
-        <v>424</v>
-      </c>
-      <c r="C154" t="s">
-        <v>425</v>
-      </c>
-      <c r="D154" t="s">
-        <v>456</v>
-      </c>
       <c r="E154" t="s">
+        <v>426</v>
+      </c>
+      <c r="F154" t="s">
         <v>427</v>
       </c>
-      <c r="F154" t="s">
+      <c r="G154" t="s">
         <v>428</v>
       </c>
-      <c r="G154" t="s">
+      <c r="H154" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I154">
+        <v>1</v>
+      </c>
+      <c r="J154" t="s">
         <v>429</v>
-      </c>
-      <c r="H154" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I154">
-        <v>1</v>
-      </c>
-      <c r="J154" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>456</v>
+      </c>
+      <c r="B155" t="s">
+        <v>423</v>
+      </c>
+      <c r="C155" t="s">
+        <v>424</v>
+      </c>
+      <c r="D155" t="s">
         <v>457</v>
-      </c>
-      <c r="B155" t="s">
-        <v>424</v>
-      </c>
-      <c r="C155" t="s">
-        <v>425</v>
-      </c>
-      <c r="D155" t="s">
-        <v>458</v>
       </c>
       <c r="E155" t="s">
         <v>432</v>
       </c>
       <c r="F155" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G155" t="s">
         <v>433</v>
@@ -8118,59 +8118,59 @@
         <v>1</v>
       </c>
       <c r="J155" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>458</v>
+      </c>
+      <c r="B156" t="s">
+        <v>423</v>
+      </c>
+      <c r="C156" t="s">
+        <v>424</v>
+      </c>
+      <c r="D156" t="s">
         <v>459</v>
       </c>
-      <c r="B156" t="s">
-        <v>424</v>
-      </c>
-      <c r="C156" t="s">
-        <v>425</v>
-      </c>
-      <c r="D156" t="s">
-        <v>460</v>
-      </c>
       <c r="E156" t="s">
+        <v>426</v>
+      </c>
+      <c r="F156" t="s">
         <v>427</v>
       </c>
-      <c r="F156" t="s">
+      <c r="G156" t="s">
         <v>428</v>
       </c>
-      <c r="G156" t="s">
+      <c r="H156" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I156">
+        <v>1</v>
+      </c>
+      <c r="J156" t="s">
         <v>429</v>
-      </c>
-      <c r="H156" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I156">
-        <v>1</v>
-      </c>
-      <c r="J156" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>460</v>
+      </c>
+      <c r="B157" t="s">
+        <v>423</v>
+      </c>
+      <c r="C157" t="s">
+        <v>424</v>
+      </c>
+      <c r="D157" t="s">
         <v>461</v>
-      </c>
-      <c r="B157" t="s">
-        <v>424</v>
-      </c>
-      <c r="C157" t="s">
-        <v>425</v>
-      </c>
-      <c r="D157" t="s">
-        <v>462</v>
       </c>
       <c r="E157" t="s">
         <v>432</v>
       </c>
       <c r="F157" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G157" t="s">
         <v>433</v>
@@ -8182,39 +8182,39 @@
         <v>1</v>
       </c>
       <c r="J157" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>462</v>
+      </c>
+      <c r="B158" t="s">
+        <v>423</v>
+      </c>
+      <c r="C158" t="s">
+        <v>424</v>
+      </c>
+      <c r="D158" t="s">
         <v>463</v>
       </c>
-      <c r="B158" t="s">
-        <v>424</v>
-      </c>
-      <c r="C158" t="s">
-        <v>425</v>
-      </c>
-      <c r="D158" t="s">
+      <c r="E158" t="s">
+        <v>426</v>
+      </c>
+      <c r="F158" t="s">
+        <v>427</v>
+      </c>
+      <c r="G158" t="s">
+        <v>428</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I158">
+        <v>1</v>
+      </c>
+      <c r="J158" t="s">
         <v>464</v>
-      </c>
-      <c r="E158" t="s">
-        <v>427</v>
-      </c>
-      <c r="F158" t="s">
-        <v>428</v>
-      </c>
-      <c r="G158" t="s">
-        <v>429</v>
-      </c>
-      <c r="H158" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I158">
-        <v>1</v>
-      </c>
-      <c r="J158" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -8222,10 +8222,10 @@
         <v>465</v>
       </c>
       <c r="B159" t="s">
+        <v>423</v>
+      </c>
+      <c r="C159" t="s">
         <v>424</v>
-      </c>
-      <c r="C159" t="s">
-        <v>425</v>
       </c>
       <c r="D159" t="s">
         <v>466</v>
@@ -8234,7 +8234,7 @@
         <v>432</v>
       </c>
       <c r="F159" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G159" t="s">
         <v>433</v>
@@ -8246,7 +8246,7 @@
         <v>1</v>
       </c>
       <c r="J159" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -8254,23 +8254,23 @@
         <v>467</v>
       </c>
       <c r="B160" t="s">
+        <v>423</v>
+      </c>
+      <c r="C160" t="s">
         <v>424</v>
-      </c>
-      <c r="C160" t="s">
-        <v>425</v>
       </c>
       <c r="D160" t="s">
         <v>468</v>
       </c>
       <c r="E160" t="s">
+        <v>426</v>
+      </c>
+      <c r="F160" t="s">
         <v>427</v>
       </c>
-      <c r="F160" t="s">
+      <c r="G160" t="s">
         <v>428</v>
       </c>
-      <c r="G160" t="s">
-        <v>429</v>
-      </c>
       <c r="H160" s="3" t="s">
         <v>53</v>
       </c>
@@ -8278,7 +8278,7 @@
         <v>1</v>
       </c>
       <c r="J160" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
@@ -8286,10 +8286,10 @@
         <v>469</v>
       </c>
       <c r="B161" t="s">
+        <v>423</v>
+      </c>
+      <c r="C161" t="s">
         <v>424</v>
-      </c>
-      <c r="C161" t="s">
-        <v>425</v>
       </c>
       <c r="D161" t="s">
         <v>470</v>
@@ -8298,7 +8298,7 @@
         <v>432</v>
       </c>
       <c r="F161" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G161" t="s">
         <v>433</v>
@@ -8310,7 +8310,7 @@
         <v>1</v>
       </c>
       <c r="J161" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -8318,23 +8318,23 @@
         <v>471</v>
       </c>
       <c r="B162" t="s">
+        <v>423</v>
+      </c>
+      <c r="C162" t="s">
         <v>424</v>
-      </c>
-      <c r="C162" t="s">
-        <v>425</v>
       </c>
       <c r="D162" t="s">
         <v>472</v>
       </c>
       <c r="E162" t="s">
+        <v>426</v>
+      </c>
+      <c r="F162" t="s">
         <v>427</v>
       </c>
-      <c r="F162" t="s">
+      <c r="G162" t="s">
         <v>428</v>
       </c>
-      <c r="G162" t="s">
-        <v>429</v>
-      </c>
       <c r="H162" s="3" t="s">
         <v>53</v>
       </c>
@@ -8342,7 +8342,7 @@
         <v>1</v>
       </c>
       <c r="J162" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -8350,10 +8350,10 @@
         <v>473</v>
       </c>
       <c r="B163" t="s">
+        <v>423</v>
+      </c>
+      <c r="C163" t="s">
         <v>424</v>
-      </c>
-      <c r="C163" t="s">
-        <v>425</v>
       </c>
       <c r="D163" t="s">
         <v>474</v>
@@ -8362,7 +8362,7 @@
         <v>432</v>
       </c>
       <c r="F163" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G163" t="s">
         <v>433</v>
@@ -8374,7 +8374,7 @@
         <v>1</v>
       </c>
       <c r="J163" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
@@ -8382,23 +8382,23 @@
         <v>475</v>
       </c>
       <c r="B164" t="s">
+        <v>423</v>
+      </c>
+      <c r="C164" t="s">
         <v>424</v>
-      </c>
-      <c r="C164" t="s">
-        <v>425</v>
       </c>
       <c r="D164" t="s">
         <v>476</v>
       </c>
       <c r="E164" t="s">
+        <v>426</v>
+      </c>
+      <c r="F164" t="s">
         <v>427</v>
       </c>
-      <c r="F164" t="s">
+      <c r="G164" t="s">
         <v>428</v>
       </c>
-      <c r="G164" t="s">
-        <v>429</v>
-      </c>
       <c r="H164" s="3" t="s">
         <v>53</v>
       </c>
@@ -8406,7 +8406,7 @@
         <v>1</v>
       </c>
       <c r="J164" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -8414,10 +8414,10 @@
         <v>477</v>
       </c>
       <c r="B165" t="s">
+        <v>423</v>
+      </c>
+      <c r="C165" t="s">
         <v>424</v>
-      </c>
-      <c r="C165" t="s">
-        <v>425</v>
       </c>
       <c r="D165" t="s">
         <v>478</v>
@@ -8426,7 +8426,7 @@
         <v>432</v>
       </c>
       <c r="F165" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G165" t="s">
         <v>433</v>
@@ -8438,7 +8438,7 @@
         <v>1</v>
       </c>
       <c r="J165" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
@@ -8446,23 +8446,23 @@
         <v>479</v>
       </c>
       <c r="B166" t="s">
+        <v>423</v>
+      </c>
+      <c r="C166" t="s">
         <v>424</v>
-      </c>
-      <c r="C166" t="s">
-        <v>425</v>
       </c>
       <c r="D166" t="s">
         <v>480</v>
       </c>
       <c r="E166" t="s">
+        <v>426</v>
+      </c>
+      <c r="F166" t="s">
         <v>427</v>
       </c>
-      <c r="F166" t="s">
+      <c r="G166" t="s">
         <v>428</v>
       </c>
-      <c r="G166" t="s">
-        <v>429</v>
-      </c>
       <c r="H166" s="3" t="s">
         <v>53</v>
       </c>
@@ -8470,7 +8470,7 @@
         <v>1</v>
       </c>
       <c r="J166" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
@@ -8478,10 +8478,10 @@
         <v>481</v>
       </c>
       <c r="B167" t="s">
+        <v>423</v>
+      </c>
+      <c r="C167" t="s">
         <v>424</v>
-      </c>
-      <c r="C167" t="s">
-        <v>425</v>
       </c>
       <c r="D167" t="s">
         <v>482</v>
@@ -8490,7 +8490,7 @@
         <v>432</v>
       </c>
       <c r="F167" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G167" t="s">
         <v>433</v>
@@ -8502,7 +8502,7 @@
         <v>1</v>
       </c>
       <c r="J167" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
@@ -8510,23 +8510,23 @@
         <v>483</v>
       </c>
       <c r="B168" t="s">
+        <v>423</v>
+      </c>
+      <c r="C168" t="s">
         <v>424</v>
-      </c>
-      <c r="C168" t="s">
-        <v>425</v>
       </c>
       <c r="D168" t="s">
         <v>484</v>
       </c>
       <c r="E168" t="s">
+        <v>426</v>
+      </c>
+      <c r="F168" t="s">
         <v>427</v>
       </c>
-      <c r="F168" t="s">
+      <c r="G168" t="s">
         <v>428</v>
       </c>
-      <c r="G168" t="s">
-        <v>429</v>
-      </c>
       <c r="H168" s="3" t="s">
         <v>53</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>1</v>
       </c>
       <c r="J168" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -8542,10 +8542,10 @@
         <v>485</v>
       </c>
       <c r="B169" t="s">
+        <v>423</v>
+      </c>
+      <c r="C169" t="s">
         <v>424</v>
-      </c>
-      <c r="C169" t="s">
-        <v>425</v>
       </c>
       <c r="D169" t="s">
         <v>486</v>
@@ -8554,7 +8554,7 @@
         <v>432</v>
       </c>
       <c r="F169" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G169" t="s">
         <v>433</v>
@@ -8566,7 +8566,7 @@
         <v>1</v>
       </c>
       <c r="J169" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
@@ -8574,23 +8574,23 @@
         <v>487</v>
       </c>
       <c r="B170" t="s">
+        <v>423</v>
+      </c>
+      <c r="C170" t="s">
         <v>424</v>
-      </c>
-      <c r="C170" t="s">
-        <v>425</v>
       </c>
       <c r="D170" t="s">
         <v>488</v>
       </c>
       <c r="E170" t="s">
+        <v>426</v>
+      </c>
+      <c r="F170" t="s">
         <v>427</v>
       </c>
-      <c r="F170" t="s">
+      <c r="G170" t="s">
         <v>428</v>
       </c>
-      <c r="G170" t="s">
-        <v>429</v>
-      </c>
       <c r="H170" s="3" t="s">
         <v>53</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>1</v>
       </c>
       <c r="J170" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
@@ -8606,10 +8606,10 @@
         <v>489</v>
       </c>
       <c r="B171" t="s">
+        <v>423</v>
+      </c>
+      <c r="C171" t="s">
         <v>424</v>
-      </c>
-      <c r="C171" t="s">
-        <v>425</v>
       </c>
       <c r="D171" t="s">
         <v>490</v>
@@ -8618,7 +8618,7 @@
         <v>432</v>
       </c>
       <c r="F171" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G171" t="s">
         <v>433</v>
@@ -8630,7 +8630,7 @@
         <v>1</v>
       </c>
       <c r="J171" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -8638,23 +8638,23 @@
         <v>491</v>
       </c>
       <c r="B172" t="s">
+        <v>423</v>
+      </c>
+      <c r="C172" t="s">
         <v>424</v>
-      </c>
-      <c r="C172" t="s">
-        <v>425</v>
       </c>
       <c r="D172" t="s">
         <v>492</v>
       </c>
       <c r="E172" t="s">
+        <v>426</v>
+      </c>
+      <c r="F172" t="s">
         <v>427</v>
       </c>
-      <c r="F172" t="s">
+      <c r="G172" t="s">
         <v>428</v>
       </c>
-      <c r="G172" t="s">
-        <v>429</v>
-      </c>
       <c r="H172" s="3" t="s">
         <v>53</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>1</v>
       </c>
       <c r="J172" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
@@ -8670,10 +8670,10 @@
         <v>493</v>
       </c>
       <c r="B173" t="s">
+        <v>423</v>
+      </c>
+      <c r="C173" t="s">
         <v>424</v>
-      </c>
-      <c r="C173" t="s">
-        <v>425</v>
       </c>
       <c r="D173" t="s">
         <v>494</v>
@@ -8682,7 +8682,7 @@
         <v>432</v>
       </c>
       <c r="F173" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G173" t="s">
         <v>433</v>
@@ -8694,7 +8694,7 @@
         <v>1</v>
       </c>
       <c r="J173" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -8702,23 +8702,23 @@
         <v>495</v>
       </c>
       <c r="B174" t="s">
+        <v>423</v>
+      </c>
+      <c r="C174" t="s">
         <v>424</v>
-      </c>
-      <c r="C174" t="s">
-        <v>425</v>
       </c>
       <c r="D174" t="s">
         <v>496</v>
       </c>
       <c r="E174" t="s">
+        <v>426</v>
+      </c>
+      <c r="F174" t="s">
         <v>427</v>
       </c>
-      <c r="F174" t="s">
+      <c r="G174" t="s">
         <v>428</v>
       </c>
-      <c r="G174" t="s">
-        <v>429</v>
-      </c>
       <c r="H174" s="3" t="s">
         <v>53</v>
       </c>
@@ -8726,7 +8726,7 @@
         <v>1</v>
       </c>
       <c r="J174" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -8734,10 +8734,10 @@
         <v>497</v>
       </c>
       <c r="B175" t="s">
+        <v>423</v>
+      </c>
+      <c r="C175" t="s">
         <v>424</v>
-      </c>
-      <c r="C175" t="s">
-        <v>425</v>
       </c>
       <c r="D175" t="s">
         <v>498</v>
@@ -8746,7 +8746,7 @@
         <v>432</v>
       </c>
       <c r="F175" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G175" t="s">
         <v>433</v>
@@ -8758,7 +8758,7 @@
         <v>1</v>
       </c>
       <c r="J175" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -8766,23 +8766,23 @@
         <v>499</v>
       </c>
       <c r="B176" t="s">
+        <v>423</v>
+      </c>
+      <c r="C176" t="s">
         <v>424</v>
-      </c>
-      <c r="C176" t="s">
-        <v>425</v>
       </c>
       <c r="D176" t="s">
         <v>500</v>
       </c>
       <c r="E176" t="s">
+        <v>426</v>
+      </c>
+      <c r="F176" t="s">
         <v>427</v>
       </c>
-      <c r="F176" t="s">
+      <c r="G176" t="s">
         <v>428</v>
       </c>
-      <c r="G176" t="s">
-        <v>429</v>
-      </c>
       <c r="H176" s="3" t="s">
         <v>53</v>
       </c>
@@ -8790,63 +8790,63 @@
         <v>1</v>
       </c>
       <c r="J176" t="s">
-        <v>454</v>
+        <v>501</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>502</v>
+      </c>
+      <c r="B177" t="s">
+        <v>503</v>
+      </c>
+      <c r="C177" t="s">
+        <v>504</v>
+      </c>
+      <c r="D177" t="s">
+        <v>505</v>
+      </c>
+      <c r="E177" t="s">
+        <v>506</v>
+      </c>
+      <c r="F177" t="s">
+        <v>507</v>
+      </c>
+      <c r="G177" t="s">
+        <v>508</v>
+      </c>
+      <c r="H177" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+      <c r="J177" t="s">
         <v>501</v>
-      </c>
-      <c r="B177" t="s">
-        <v>502</v>
-      </c>
-      <c r="C177" t="s">
-        <v>503</v>
-      </c>
-      <c r="D177" t="s">
-        <v>504</v>
-      </c>
-      <c r="E177" t="s">
-        <v>505</v>
-      </c>
-      <c r="F177" t="s">
-        <v>506</v>
-      </c>
-      <c r="G177" t="s">
-        <v>507</v>
-      </c>
-      <c r="H177" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I177">
-        <v>1</v>
-      </c>
-      <c r="J177" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>509</v>
+      </c>
+      <c r="B178" t="s">
+        <v>503</v>
+      </c>
+      <c r="C178" t="s">
+        <v>504</v>
+      </c>
+      <c r="D178" t="s">
+        <v>510</v>
+      </c>
+      <c r="E178" t="s">
+        <v>511</v>
+      </c>
+      <c r="F178" t="s">
+        <v>507</v>
+      </c>
+      <c r="G178" t="s">
         <v>508</v>
       </c>
-      <c r="B178" t="s">
-        <v>502</v>
-      </c>
-      <c r="C178" t="s">
-        <v>503</v>
-      </c>
-      <c r="D178" t="s">
-        <v>509</v>
-      </c>
-      <c r="E178" t="s">
-        <v>510</v>
-      </c>
-      <c r="F178" t="s">
-        <v>506</v>
-      </c>
-      <c r="G178" t="s">
-        <v>507</v>
-      </c>
       <c r="H178" s="3" t="s">
         <v>53</v>
       </c>
@@ -8854,30 +8854,30 @@
         <v>1</v>
       </c>
       <c r="J178" t="s">
-        <v>454</v>
+        <v>501</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B179" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C179" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D179" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E179" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F179" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G179" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H179" s="3" t="s">
         <v>53</v>
@@ -8886,30 +8886,30 @@
         <v>1</v>
       </c>
       <c r="J179" t="s">
-        <v>454</v>
+        <v>501</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B180" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C180" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D180" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E180" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F180" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G180" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>53</v>
@@ -8918,30 +8918,30 @@
         <v>1</v>
       </c>
       <c r="J180" t="s">
-        <v>454</v>
+        <v>501</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B181" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C181" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D181" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E181" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F181" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G181" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H181" s="3" t="s">
         <v>53</v>
@@ -8950,30 +8950,30 @@
         <v>1</v>
       </c>
       <c r="J181" t="s">
-        <v>454</v>
+        <v>501</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B182" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C182" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D182" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E182" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F182" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G182" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H182" s="3" t="s">
         <v>53</v>
@@ -8982,7 +8982,7 @@
         <v>1</v>
       </c>
       <c r="J182" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -8990,10 +8990,10 @@
         <v>524</v>
       </c>
       <c r="B183" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C183" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D183" t="s">
         <v>525</v>
@@ -9002,10 +9002,10 @@
         <v>526</v>
       </c>
       <c r="F183" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G183" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H183" s="3" t="s">
         <v>53</v>
@@ -9014,7 +9014,7 @@
         <v>1</v>
       </c>
       <c r="J183" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -9022,10 +9022,10 @@
         <v>527</v>
       </c>
       <c r="B184" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C184" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D184" t="s">
         <v>528</v>
@@ -9034,10 +9034,10 @@
         <v>529</v>
       </c>
       <c r="F184" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G184" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H184" s="3" t="s">
         <v>53</v>
@@ -9046,7 +9046,7 @@
         <v>1</v>
       </c>
       <c r="J184" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
@@ -9054,10 +9054,10 @@
         <v>530</v>
       </c>
       <c r="B185" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C185" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D185" t="s">
         <v>531</v>
@@ -9066,10 +9066,10 @@
         <v>532</v>
       </c>
       <c r="F185" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G185" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>53</v>
@@ -9078,7 +9078,7 @@
         <v>1</v>
       </c>
       <c r="J185" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
@@ -9086,10 +9086,10 @@
         <v>533</v>
       </c>
       <c r="B186" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C186" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D186" t="s">
         <v>534</v>
@@ -9098,10 +9098,10 @@
         <v>535</v>
       </c>
       <c r="F186" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G186" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>53</v>
@@ -9110,7 +9110,7 @@
         <v>1</v>
       </c>
       <c r="J186" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
@@ -9118,10 +9118,10 @@
         <v>536</v>
       </c>
       <c r="B187" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C187" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D187" t="s">
         <v>537</v>
@@ -9130,10 +9130,10 @@
         <v>538</v>
       </c>
       <c r="F187" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G187" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H187" s="3" t="s">
         <v>53</v>
@@ -9142,7 +9142,7 @@
         <v>1</v>
       </c>
       <c r="J187" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
@@ -9150,10 +9150,10 @@
         <v>539</v>
       </c>
       <c r="B188" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C188" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D188" t="s">
         <v>540</v>
@@ -9162,10 +9162,10 @@
         <v>541</v>
       </c>
       <c r="F188" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G188" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H188" s="3" t="s">
         <v>53</v>
@@ -9174,7 +9174,7 @@
         <v>1</v>
       </c>
       <c r="J188" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
@@ -9182,10 +9182,10 @@
         <v>542</v>
       </c>
       <c r="B189" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C189" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D189" t="s">
         <v>543</v>
@@ -9194,10 +9194,10 @@
         <v>544</v>
       </c>
       <c r="F189" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G189" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>53</v>
@@ -9206,7 +9206,7 @@
         <v>1</v>
       </c>
       <c r="J189" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
@@ -9214,10 +9214,10 @@
         <v>545</v>
       </c>
       <c r="B190" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C190" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D190" t="s">
         <v>546</v>
@@ -9226,10 +9226,10 @@
         <v>547</v>
       </c>
       <c r="F190" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G190" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H190" s="3" t="s">
         <v>53</v>
@@ -9238,7 +9238,7 @@
         <v>1</v>
       </c>
       <c r="J190" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
@@ -9246,10 +9246,10 @@
         <v>548</v>
       </c>
       <c r="B191" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C191" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D191" t="s">
         <v>549</v>
@@ -9258,10 +9258,10 @@
         <v>550</v>
       </c>
       <c r="F191" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G191" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H191" s="3" t="s">
         <v>53</v>
@@ -9270,7 +9270,7 @@
         <v>1</v>
       </c>
       <c r="J191" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
@@ -9278,10 +9278,10 @@
         <v>551</v>
       </c>
       <c r="B192" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C192" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D192" t="s">
         <v>552</v>
@@ -9290,10 +9290,10 @@
         <v>553</v>
       </c>
       <c r="F192" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G192" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H192" s="3" t="s">
         <v>53</v>
@@ -9302,7 +9302,7 @@
         <v>1</v>
       </c>
       <c r="J192" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
@@ -9310,10 +9310,10 @@
         <v>554</v>
       </c>
       <c r="B193" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C193" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D193" t="s">
         <v>555</v>
@@ -9322,10 +9322,10 @@
         <v>556</v>
       </c>
       <c r="F193" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G193" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H193" s="3" t="s">
         <v>53</v>
@@ -9334,7 +9334,7 @@
         <v>1</v>
       </c>
       <c r="J193" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
@@ -9342,10 +9342,10 @@
         <v>557</v>
       </c>
       <c r="B194" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C194" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D194" t="s">
         <v>558</v>
@@ -9354,10 +9354,10 @@
         <v>559</v>
       </c>
       <c r="F194" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G194" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H194" s="3" t="s">
         <v>53</v>
@@ -9366,7 +9366,7 @@
         <v>1</v>
       </c>
       <c r="J194" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
@@ -9374,10 +9374,10 @@
         <v>560</v>
       </c>
       <c r="B195" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C195" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D195" t="s">
         <v>561</v>
@@ -9386,10 +9386,10 @@
         <v>562</v>
       </c>
       <c r="F195" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G195" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H195" s="3" t="s">
         <v>53</v>
@@ -9398,7 +9398,7 @@
         <v>1</v>
       </c>
       <c r="J195" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
@@ -9406,10 +9406,10 @@
         <v>563</v>
       </c>
       <c r="B196" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C196" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D196" t="s">
         <v>564</v>
@@ -9418,10 +9418,10 @@
         <v>565</v>
       </c>
       <c r="F196" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G196" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H196" s="3" t="s">
         <v>53</v>
@@ -9430,7 +9430,7 @@
         <v>1</v>
       </c>
       <c r="J196" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
@@ -9438,22 +9438,22 @@
         <v>566</v>
       </c>
       <c r="B197" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C197" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D197" t="s">
         <v>567</v>
       </c>
       <c r="E197" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F197" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G197" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H197" s="3" t="s">
         <v>53</v>
@@ -9462,7 +9462,7 @@
         <v>1</v>
       </c>
       <c r="J197" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
@@ -9470,22 +9470,22 @@
         <v>568</v>
       </c>
       <c r="B198" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C198" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D198" t="s">
         <v>569</v>
       </c>
       <c r="E198" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F198" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G198" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H198" s="3" t="s">
         <v>53</v>
@@ -9494,7 +9494,7 @@
         <v>1</v>
       </c>
       <c r="J198" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
@@ -9502,22 +9502,22 @@
         <v>570</v>
       </c>
       <c r="B199" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C199" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D199" t="s">
         <v>571</v>
       </c>
       <c r="E199" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F199" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G199" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H199" s="3" t="s">
         <v>53</v>
@@ -9526,7 +9526,7 @@
         <v>1</v>
       </c>
       <c r="J199" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
@@ -9534,22 +9534,22 @@
         <v>572</v>
       </c>
       <c r="B200" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C200" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D200" t="s">
         <v>573</v>
       </c>
       <c r="E200" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F200" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G200" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H200" s="3" t="s">
         <v>53</v>
@@ -9558,7 +9558,7 @@
         <v>1</v>
       </c>
       <c r="J200" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
@@ -9566,22 +9566,22 @@
         <v>574</v>
       </c>
       <c r="B201" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C201" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D201" t="s">
         <v>575</v>
       </c>
       <c r="E201" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F201" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G201" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H201" s="3" t="s">
         <v>53</v>
@@ -9590,7 +9590,7 @@
         <v>1</v>
       </c>
       <c r="J201" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
@@ -9598,22 +9598,22 @@
         <v>576</v>
       </c>
       <c r="B202" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C202" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D202" t="s">
         <v>577</v>
       </c>
       <c r="E202" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F202" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G202" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H202" s="3" t="s">
         <v>53</v>
@@ -9622,7 +9622,7 @@
         <v>1</v>
       </c>
       <c r="J202" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
@@ -9630,10 +9630,10 @@
         <v>578</v>
       </c>
       <c r="B203" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C203" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D203" t="s">
         <v>579</v>
@@ -9642,10 +9642,10 @@
         <v>526</v>
       </c>
       <c r="F203" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G203" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H203" s="3" t="s">
         <v>53</v>
@@ -9654,7 +9654,7 @@
         <v>1</v>
       </c>
       <c r="J203" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
@@ -9662,10 +9662,10 @@
         <v>580</v>
       </c>
       <c r="B204" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C204" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D204" t="s">
         <v>581</v>
@@ -9674,10 +9674,10 @@
         <v>529</v>
       </c>
       <c r="F204" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G204" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H204" s="3" t="s">
         <v>53</v>
@@ -9686,7 +9686,7 @@
         <v>1</v>
       </c>
       <c r="J204" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
@@ -9694,10 +9694,10 @@
         <v>582</v>
       </c>
       <c r="B205" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C205" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D205" t="s">
         <v>583</v>
@@ -9706,10 +9706,10 @@
         <v>532</v>
       </c>
       <c r="F205" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G205" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H205" s="3" t="s">
         <v>53</v>
@@ -9718,30 +9718,30 @@
         <v>1</v>
       </c>
       <c r="J205" t="s">
-        <v>523</v>
+        <v>584</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B206" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C206" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D206" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E206" t="s">
         <v>535</v>
       </c>
       <c r="F206" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G206" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H206" s="3" t="s">
         <v>53</v>
@@ -9750,30 +9750,30 @@
         <v>1</v>
       </c>
       <c r="J206" t="s">
-        <v>523</v>
+        <v>584</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B207" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C207" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D207" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E207" t="s">
         <v>538</v>
       </c>
       <c r="F207" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G207" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H207" s="3" t="s">
         <v>53</v>
@@ -9782,30 +9782,30 @@
         <v>1</v>
       </c>
       <c r="J207" t="s">
-        <v>523</v>
+        <v>584</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B208" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C208" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D208" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E208" t="s">
         <v>541</v>
       </c>
       <c r="F208" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G208" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H208" s="3" t="s">
         <v>53</v>
@@ -9814,30 +9814,30 @@
         <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>523</v>
+        <v>584</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B209" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C209" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D209" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E209" t="s">
         <v>544</v>
       </c>
       <c r="F209" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G209" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H209" s="3" t="s">
         <v>53</v>
@@ -9846,30 +9846,30 @@
         <v>1</v>
       </c>
       <c r="J209" t="s">
-        <v>523</v>
+        <v>584</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B210" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C210" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D210" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E210" t="s">
         <v>547</v>
       </c>
       <c r="F210" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G210" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H210" s="3" t="s">
         <v>53</v>
@@ -9878,30 +9878,30 @@
         <v>1</v>
       </c>
       <c r="J210" t="s">
-        <v>523</v>
+        <v>584</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B211" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C211" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D211" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E211" t="s">
         <v>550</v>
       </c>
       <c r="F211" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G211" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H211" s="3" t="s">
         <v>53</v>
@@ -9910,7 +9910,7 @@
         <v>1</v>
       </c>
       <c r="J211" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
@@ -9942,7 +9942,7 @@
         <v>1</v>
       </c>
       <c r="J212" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
@@ -9974,7 +9974,7 @@
         <v>1</v>
       </c>
       <c r="J213" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
@@ -10006,7 +10006,7 @@
         <v>1</v>
       </c>
       <c r="J214" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
@@ -10038,7 +10038,7 @@
         <v>1</v>
       </c>
       <c r="J215" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
@@ -10070,7 +10070,7 @@
         <v>1</v>
       </c>
       <c r="J216" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
@@ -10102,7 +10102,7 @@
         <v>1</v>
       </c>
       <c r="J217" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
@@ -10134,7 +10134,7 @@
         <v>1</v>
       </c>
       <c r="J218" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
@@ -10166,7 +10166,7 @@
         <v>1</v>
       </c>
       <c r="J219" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
@@ -10198,7 +10198,7 @@
         <v>1</v>
       </c>
       <c r="J220" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
@@ -10230,7 +10230,7 @@
         <v>1</v>
       </c>
       <c r="J221" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
@@ -10262,7 +10262,7 @@
         <v>1</v>
       </c>
       <c r="J222" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
@@ -10294,7 +10294,7 @@
         <v>1</v>
       </c>
       <c r="J223" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
@@ -10326,7 +10326,7 @@
         <v>1</v>
       </c>
       <c r="J224" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
@@ -10358,7 +10358,7 @@
         <v>1</v>
       </c>
       <c r="J225" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
@@ -10390,7 +10390,7 @@
         <v>1</v>
       </c>
       <c r="J226" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
@@ -10422,7 +10422,7 @@
         <v>1</v>
       </c>
       <c r="J227" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
@@ -10454,7 +10454,7 @@
         <v>1</v>
       </c>
       <c r="J228" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
@@ -10486,7 +10486,7 @@
         <v>1</v>
       </c>
       <c r="J229" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
@@ -10518,7 +10518,7 @@
         <v>1</v>
       </c>
       <c r="J230" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
@@ -10550,7 +10550,7 @@
         <v>1</v>
       </c>
       <c r="J231" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
@@ -10582,7 +10582,7 @@
         <v>1</v>
       </c>
       <c r="J232" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
@@ -10614,7 +10614,7 @@
         <v>1</v>
       </c>
       <c r="J233" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
@@ -10646,7 +10646,7 @@
         <v>1</v>
       </c>
       <c r="J234" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
@@ -10678,7 +10678,7 @@
         <v>1</v>
       </c>
       <c r="J235" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
@@ -10710,7 +10710,7 @@
         <v>1</v>
       </c>
       <c r="J236" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
@@ -10742,7 +10742,7 @@
         <v>1</v>
       </c>
       <c r="J237" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
@@ -10774,7 +10774,7 @@
         <v>1</v>
       </c>
       <c r="J238" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
@@ -10806,7 +10806,7 @@
         <v>1</v>
       </c>
       <c r="J239" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
@@ -10838,7 +10838,7 @@
         <v>1</v>
       </c>
       <c r="J240" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
@@ -10870,7 +10870,7 @@
         <v>1</v>
       </c>
       <c r="J241" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
@@ -10902,7 +10902,7 @@
         <v>1</v>
       </c>
       <c r="J242" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
@@ -10934,12 +10934,12 @@
         <v>1</v>
       </c>
       <c r="J243" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B244" t="s">
         <v>692</v>
@@ -10948,10 +10948,10 @@
         <v>693</v>
       </c>
       <c r="D244" t="s">
+        <v>702</v>
+      </c>
+      <c r="E244" t="s">
         <v>703</v>
-      </c>
-      <c r="E244" t="s">
-        <v>704</v>
       </c>
       <c r="F244" t="s">
         <v>696</v>
@@ -10966,12 +10966,12 @@
         <v>1</v>
       </c>
       <c r="J244" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B245" t="s">
         <v>692</v>
@@ -10980,17 +10980,17 @@
         <v>693</v>
       </c>
       <c r="D245" t="s">
+        <v>705</v>
+      </c>
+      <c r="E245" t="s">
         <v>706</v>
       </c>
-      <c r="E245" t="s">
+      <c r="F245" t="s">
         <v>707</v>
       </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
         <v>708</v>
       </c>
-      <c r="G245" t="s">
-        <v>709</v>
-      </c>
       <c r="H245" s="3" t="s">
         <v>53</v>
       </c>
@@ -10998,12 +10998,12 @@
         <v>1</v>
       </c>
       <c r="J245" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B246" t="s">
         <v>692</v>
@@ -11012,17 +11012,17 @@
         <v>693</v>
       </c>
       <c r="D246" t="s">
+        <v>710</v>
+      </c>
+      <c r="E246" t="s">
         <v>711</v>
       </c>
-      <c r="E246" t="s">
-        <v>712</v>
-      </c>
       <c r="F246" t="s">
+        <v>707</v>
+      </c>
+      <c r="G246" t="s">
         <v>708</v>
       </c>
-      <c r="G246" t="s">
-        <v>709</v>
-      </c>
       <c r="H246" s="3" t="s">
         <v>53</v>
       </c>
@@ -11030,12 +11030,12 @@
         <v>1</v>
       </c>
       <c r="J246" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B247" t="s">
         <v>692</v>
@@ -11044,10 +11044,10 @@
         <v>693</v>
       </c>
       <c r="D247" t="s">
+        <v>713</v>
+      </c>
+      <c r="E247" t="s">
         <v>714</v>
-      </c>
-      <c r="E247" t="s">
-        <v>715</v>
       </c>
       <c r="F247" t="s">
         <v>696</v>
@@ -11062,12 +11062,12 @@
         <v>1</v>
       </c>
       <c r="J247" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B248" t="s">
         <v>692</v>
@@ -11076,10 +11076,10 @@
         <v>693</v>
       </c>
       <c r="D248" t="s">
+        <v>716</v>
+      </c>
+      <c r="E248" t="s">
         <v>717</v>
-      </c>
-      <c r="E248" t="s">
-        <v>718</v>
       </c>
       <c r="F248" t="s">
         <v>696</v>
@@ -11094,12 +11094,12 @@
         <v>1</v>
       </c>
       <c r="J248" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B249" t="s">
         <v>692</v>
@@ -11108,10 +11108,10 @@
         <v>693</v>
       </c>
       <c r="D249" t="s">
+        <v>719</v>
+      </c>
+      <c r="E249" t="s">
         <v>720</v>
-      </c>
-      <c r="E249" t="s">
-        <v>721</v>
       </c>
       <c r="F249" t="s">
         <v>696</v>
@@ -11126,12 +11126,12 @@
         <v>1</v>
       </c>
       <c r="J249" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B250" t="s">
         <v>692</v>
@@ -11140,17 +11140,17 @@
         <v>693</v>
       </c>
       <c r="D250" t="s">
+        <v>722</v>
+      </c>
+      <c r="E250" t="s">
         <v>723</v>
       </c>
-      <c r="E250" t="s">
-        <v>724</v>
-      </c>
       <c r="F250" t="s">
+        <v>707</v>
+      </c>
+      <c r="G250" t="s">
         <v>708</v>
       </c>
-      <c r="G250" t="s">
-        <v>709</v>
-      </c>
       <c r="H250" s="3" t="s">
         <v>53</v>
       </c>
@@ -11158,12 +11158,12 @@
         <v>1</v>
       </c>
       <c r="J250" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B251" t="s">
         <v>692</v>
@@ -11172,17 +11172,17 @@
         <v>693</v>
       </c>
       <c r="D251" t="s">
+        <v>725</v>
+      </c>
+      <c r="E251" t="s">
         <v>726</v>
       </c>
-      <c r="E251" t="s">
-        <v>727</v>
-      </c>
       <c r="F251" t="s">
+        <v>707</v>
+      </c>
+      <c r="G251" t="s">
         <v>708</v>
       </c>
-      <c r="G251" t="s">
-        <v>709</v>
-      </c>
       <c r="H251" s="3" t="s">
         <v>53</v>
       </c>
@@ -11190,12 +11190,12 @@
         <v>1</v>
       </c>
       <c r="J251" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B252" t="s">
         <v>692</v>
@@ -11204,7 +11204,7 @@
         <v>693</v>
       </c>
       <c r="D252" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E252" t="s">
         <v>695</v>
@@ -11222,12 +11222,12 @@
         <v>1</v>
       </c>
       <c r="J252" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B253" t="s">
         <v>692</v>
@@ -11236,7 +11236,7 @@
         <v>693</v>
       </c>
       <c r="D253" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E253" t="s">
         <v>700</v>
@@ -11254,12 +11254,12 @@
         <v>1</v>
       </c>
       <c r="J253" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B254" t="s">
         <v>692</v>
@@ -11268,10 +11268,10 @@
         <v>693</v>
       </c>
       <c r="D254" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E254" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F254" t="s">
         <v>696</v>
@@ -11286,12 +11286,12 @@
         <v>1</v>
       </c>
       <c r="J254" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B255" t="s">
         <v>692</v>
@@ -11300,17 +11300,17 @@
         <v>693</v>
       </c>
       <c r="D255" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E255" t="s">
+        <v>706</v>
+      </c>
+      <c r="F255" t="s">
         <v>707</v>
       </c>
-      <c r="F255" t="s">
+      <c r="G255" t="s">
         <v>708</v>
       </c>
-      <c r="G255" t="s">
-        <v>709</v>
-      </c>
       <c r="H255" s="3" t="s">
         <v>53</v>
       </c>
@@ -11318,12 +11318,12 @@
         <v>1</v>
       </c>
       <c r="J255" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B256" t="s">
         <v>692</v>
@@ -11332,17 +11332,17 @@
         <v>693</v>
       </c>
       <c r="D256" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E256" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F256" t="s">
+        <v>707</v>
+      </c>
+      <c r="G256" t="s">
         <v>708</v>
       </c>
-      <c r="G256" t="s">
-        <v>709</v>
-      </c>
       <c r="H256" s="3" t="s">
         <v>53</v>
       </c>
@@ -11350,12 +11350,12 @@
         <v>1</v>
       </c>
       <c r="J256" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B257" t="s">
         <v>692</v>
@@ -11364,10 +11364,10 @@
         <v>693</v>
       </c>
       <c r="D257" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E257" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F257" t="s">
         <v>696</v>
@@ -11382,12 +11382,12 @@
         <v>1</v>
       </c>
       <c r="J257" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B258" t="s">
         <v>692</v>
@@ -11396,10 +11396,10 @@
         <v>693</v>
       </c>
       <c r="D258" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E258" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F258" t="s">
         <v>696</v>
@@ -11414,12 +11414,12 @@
         <v>1</v>
       </c>
       <c r="J258" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B259" t="s">
         <v>692</v>
@@ -11428,10 +11428,10 @@
         <v>693</v>
       </c>
       <c r="D259" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E259" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F259" t="s">
         <v>696</v>
@@ -11446,12 +11446,12 @@
         <v>1</v>
       </c>
       <c r="J259" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B260" t="s">
         <v>692</v>
@@ -11460,17 +11460,17 @@
         <v>693</v>
       </c>
       <c r="D260" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E260" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F260" t="s">
+        <v>707</v>
+      </c>
+      <c r="G260" t="s">
         <v>708</v>
       </c>
-      <c r="G260" t="s">
-        <v>709</v>
-      </c>
       <c r="H260" s="3" t="s">
         <v>53</v>
       </c>
@@ -11478,12 +11478,12 @@
         <v>1</v>
       </c>
       <c r="J260" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B261" t="s">
         <v>692</v>
@@ -11492,17 +11492,17 @@
         <v>693</v>
       </c>
       <c r="D261" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E261" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F261" t="s">
+        <v>707</v>
+      </c>
+      <c r="G261" t="s">
         <v>708</v>
       </c>
-      <c r="G261" t="s">
-        <v>709</v>
-      </c>
       <c r="H261" s="3" t="s">
         <v>53</v>
       </c>
@@ -11510,12 +11510,12 @@
         <v>1</v>
       </c>
       <c r="J261" t="s">
-        <v>701</v>
+        <v>584</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B262" t="s">
         <v>692</v>
@@ -11524,7 +11524,7 @@
         <v>693</v>
       </c>
       <c r="D262" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E262" t="s">
         <v>695</v>
@@ -11542,7 +11542,7 @@
         <v>1</v>
       </c>
       <c r="J262" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
@@ -11574,7 +11574,7 @@
         <v>1</v>
       </c>
       <c r="J263" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
@@ -11591,7 +11591,7 @@
         <v>753</v>
       </c>
       <c r="E264" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F264" t="s">
         <v>696</v>
@@ -11606,7 +11606,7 @@
         <v>1</v>
       </c>
       <c r="J264" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
@@ -11623,14 +11623,14 @@
         <v>755</v>
       </c>
       <c r="E265" t="s">
+        <v>706</v>
+      </c>
+      <c r="F265" t="s">
         <v>707</v>
       </c>
-      <c r="F265" t="s">
+      <c r="G265" t="s">
         <v>708</v>
       </c>
-      <c r="G265" t="s">
-        <v>709</v>
-      </c>
       <c r="H265" s="3" t="s">
         <v>53</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>1</v>
       </c>
       <c r="J265" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
@@ -11655,14 +11655,14 @@
         <v>757</v>
       </c>
       <c r="E266" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F266" t="s">
+        <v>707</v>
+      </c>
+      <c r="G266" t="s">
         <v>708</v>
       </c>
-      <c r="G266" t="s">
-        <v>709</v>
-      </c>
       <c r="H266" s="3" t="s">
         <v>53</v>
       </c>
@@ -11670,7 +11670,7 @@
         <v>1</v>
       </c>
       <c r="J266" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
@@ -11687,7 +11687,7 @@
         <v>759</v>
       </c>
       <c r="E267" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F267" t="s">
         <v>696</v>
@@ -11702,7 +11702,7 @@
         <v>1</v>
       </c>
       <c r="J267" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
@@ -11719,7 +11719,7 @@
         <v>761</v>
       </c>
       <c r="E268" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F268" t="s">
         <v>696</v>
@@ -11734,7 +11734,7 @@
         <v>1</v>
       </c>
       <c r="J268" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
@@ -11751,7 +11751,7 @@
         <v>763</v>
       </c>
       <c r="E269" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F269" t="s">
         <v>696</v>
@@ -11766,7 +11766,7 @@
         <v>1</v>
       </c>
       <c r="J269" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
@@ -11783,14 +11783,14 @@
         <v>765</v>
       </c>
       <c r="E270" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F270" t="s">
+        <v>707</v>
+      </c>
+      <c r="G270" t="s">
         <v>708</v>
       </c>
-      <c r="G270" t="s">
-        <v>709</v>
-      </c>
       <c r="H270" s="3" t="s">
         <v>53</v>
       </c>
@@ -11798,7 +11798,7 @@
         <v>1</v>
       </c>
       <c r="J270" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
@@ -11815,14 +11815,14 @@
         <v>767</v>
       </c>
       <c r="E271" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F271" t="s">
+        <v>707</v>
+      </c>
+      <c r="G271" t="s">
         <v>708</v>
       </c>
-      <c r="G271" t="s">
-        <v>709</v>
-      </c>
       <c r="H271" s="3" t="s">
         <v>53</v>
       </c>
@@ -11830,7 +11830,7 @@
         <v>1</v>
       </c>
       <c r="J271" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
@@ -11862,7 +11862,7 @@
         <v>1</v>
       </c>
       <c r="J272" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
@@ -11894,7 +11894,7 @@
         <v>1</v>
       </c>
       <c r="J273" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
@@ -11926,7 +11926,7 @@
         <v>1</v>
       </c>
       <c r="J274" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
@@ -11958,7 +11958,7 @@
         <v>1</v>
       </c>
       <c r="J275" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.25">
@@ -11990,7 +11990,7 @@
         <v>1</v>
       </c>
       <c r="J276" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.25">
@@ -12022,7 +12022,7 @@
         <v>1</v>
       </c>
       <c r="J277" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.25">
@@ -12054,7 +12054,7 @@
         <v>1</v>
       </c>
       <c r="J278" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.25">
@@ -12086,7 +12086,7 @@
         <v>1</v>
       </c>
       <c r="J279" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.25">
@@ -12118,7 +12118,7 @@
         <v>1</v>
       </c>
       <c r="J280" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.25">
@@ -12150,7 +12150,7 @@
         <v>1</v>
       </c>
       <c r="J281" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.25">
@@ -12182,7 +12182,7 @@
         <v>1</v>
       </c>
       <c r="J282" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.25">
@@ -12214,7 +12214,7 @@
         <v>1</v>
       </c>
       <c r="J283" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.25">
@@ -12246,7 +12246,7 @@
         <v>1</v>
       </c>
       <c r="J284" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
@@ -12278,7 +12278,7 @@
         <v>1</v>
       </c>
       <c r="J285" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
@@ -12310,7 +12310,7 @@
         <v>1</v>
       </c>
       <c r="J286" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
@@ -12342,7 +12342,7 @@
         <v>1</v>
       </c>
       <c r="J287" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
@@ -12374,7 +12374,7 @@
         <v>1</v>
       </c>
       <c r="J288" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.25">
@@ -12406,7 +12406,7 @@
         <v>1</v>
       </c>
       <c r="J289" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
@@ -12438,7 +12438,7 @@
         <v>1</v>
       </c>
       <c r="J290" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.25">
@@ -12470,7 +12470,7 @@
         <v>1</v>
       </c>
       <c r="J291" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.25">
@@ -12502,7 +12502,7 @@
         <v>1</v>
       </c>
       <c r="J292" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
@@ -12534,7 +12534,7 @@
         <v>1</v>
       </c>
       <c r="J293" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
@@ -12566,7 +12566,7 @@
         <v>1</v>
       </c>
       <c r="J294" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.25">
@@ -12598,7 +12598,7 @@
         <v>1</v>
       </c>
       <c r="J295" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
@@ -12630,7 +12630,7 @@
         <v>1</v>
       </c>
       <c r="J296" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
@@ -12662,7 +12662,7 @@
         <v>1</v>
       </c>
       <c r="J297" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
@@ -12694,7 +12694,7 @@
         <v>1</v>
       </c>
       <c r="J298" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
@@ -12726,7 +12726,7 @@
         <v>1</v>
       </c>
       <c r="J299" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
@@ -12758,7 +12758,7 @@
         <v>1</v>
       </c>
       <c r="J300" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
@@ -12790,7 +12790,7 @@
         <v>1</v>
       </c>
       <c r="J301" t="s">
-        <v>701</v>
+        <v>749</v>
       </c>
     </row>
   </sheetData>
